--- a/raw/time_tables/B.Tech 62 (btech-62)/5/1.xlsx
+++ b/raw/time_tables/B.Tech 62 (btech-62)/5/1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6FD08D-CE5C-4048-94CF-C4205740B13B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18FB964-7AFF-450D-8582-9FB073937926}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,15 +775,9 @@
     <t>LAC(16B1NMA531)-CR425/NF2</t>
   </si>
   <si>
-    <t>LABC(16B1NMA533)-FF7/MKB</t>
-  </si>
-  <si>
     <t>LAB(16B1NMA731)-FF8/NF3</t>
   </si>
   <si>
-    <t>LABC(17B1NMA531)-FF9/NF5</t>
-  </si>
-  <si>
     <t>LB(PH531)-CS2/ANU</t>
   </si>
   <si>
@@ -841,9 +835,6 @@
     <t>LAB(16B1NMA731)-CR526/NF3</t>
   </si>
   <si>
-    <t>LABC(17B1NMA531)-FF4/NF5</t>
-  </si>
-  <si>
     <t>LG1,G2(26B12MA311)-FF7/HZR</t>
   </si>
   <si>
@@ -1042,9 +1033,6 @@
     <t>TA17(CI518)-TS17/SHP</t>
   </si>
   <si>
-    <t>TA6(CI518)-TS17/TKT</t>
-  </si>
-  <si>
     <t>TA17(24B31EC311)-F10/ABU</t>
   </si>
   <si>
@@ -1468,9 +1456,6 @@
     <t>TA1(EC312)-TS12/JOY</t>
   </si>
   <si>
-    <t>PA10(EC312)-ACL,BPL/RB,JOY</t>
-  </si>
-  <si>
     <t>PA8(EC312)-ACL,BPL/VNS,JOY</t>
   </si>
   <si>
@@ -1480,9 +1465,6 @@
     <t>LA15-A16(EC312)-CS1/JOY</t>
   </si>
   <si>
-    <t>PA2(EC312)-ACL,BPL/AGT,JYM</t>
-  </si>
-  <si>
     <t>PA1(EC312)-ACL,BPL/JOY,JYM</t>
   </si>
   <si>
@@ -1550,6 +1532,24 @@
   </si>
   <si>
     <t>TG2(26B11MA318)-TS17/MSD</t>
+  </si>
+  <si>
+    <t>LABC(17B1NMA531)-CS2/NF5</t>
+  </si>
+  <si>
+    <t>LABC(17B1NMA531)-LT2/NF5</t>
+  </si>
+  <si>
+    <t>PA10(EC312)-ACL,BPL/RB,JYM</t>
+  </si>
+  <si>
+    <t>PA2(EC312)-ACL,BPL/AGT,JOY</t>
+  </si>
+  <si>
+    <t>LAC(16B1NMA531)-FF7/NF2</t>
+  </si>
+  <si>
+    <t>TA6(CI518)-TR326/TKT</t>
   </si>
 </sst>
 </file>
@@ -2071,7 +2071,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2413,9 +2413,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2473,6 +2479,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2491,9 +2500,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2556,6 +2562,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -2902,7 +2911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K172"/>
+  <dimension ref="A1:K173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.140625" customWidth="1"/>
@@ -2910,7 +2919,7 @@
     <col min="3" max="3" width="24.85546875" customWidth="1"/>
     <col min="4" max="4" width="23.28515625" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
     <col min="7" max="7" width="25.140625" customWidth="1"/>
     <col min="8" max="8" width="21.85546875" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
@@ -2919,19 +2928,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33" customHeight="1">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="166" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="165"/>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="165"/>
-      <c r="H1" s="165"/>
-      <c r="I1" s="165"/>
-      <c r="J1" s="165"/>
-      <c r="K1" s="166"/>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="168"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1"/>
@@ -2993,38 +3002,38 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="32.25" customHeight="1">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="123" t="s">
+      <c r="B5" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="123"/>
+      <c r="C5" s="125"/>
       <c r="D5" s="92" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E5" s="92" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="168" t="s">
+      <c r="F5" s="170" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="92" t="s">
         <v>170</v>
       </c>
       <c r="H5" s="92" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="I5" s="92" t="s">
         <v>177</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="125"/>
     </row>
     <row r="6" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A6" s="159"/>
+      <c r="A6" s="161"/>
       <c r="B6" s="92"/>
       <c r="C6" s="92" t="s">
         <v>158</v>
@@ -3035,7 +3044,7 @@
       <c r="E6" s="92" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="156"/>
+      <c r="F6" s="158"/>
       <c r="G6" s="92" t="s">
         <v>171</v>
       </c>
@@ -3043,7 +3052,7 @@
         <v>174</v>
       </c>
       <c r="I6" s="106" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="J6" s="92" t="s">
         <v>181</v>
@@ -3051,7 +3060,7 @@
       <c r="K6" s="92"/>
     </row>
     <row r="7" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A7" s="159"/>
+      <c r="A7" s="161"/>
       <c r="B7" s="95"/>
       <c r="C7" s="96" t="s">
         <v>159</v>
@@ -3062,7 +3071,7 @@
       <c r="E7" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="F7" s="156"/>
+      <c r="F7" s="158"/>
       <c r="G7" s="92" t="s">
         <v>172</v>
       </c>
@@ -3076,18 +3085,18 @@
       <c r="K7" s="92"/>
     </row>
     <row r="8" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A8" s="159"/>
-      <c r="B8" s="123" t="s">
-        <v>420</v>
-      </c>
-      <c r="C8" s="123"/>
+      <c r="A8" s="161"/>
+      <c r="B8" s="125" t="s">
+        <v>416</v>
+      </c>
+      <c r="C8" s="125"/>
       <c r="D8" s="92" t="s">
         <v>162</v>
       </c>
       <c r="E8" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="F8" s="156"/>
+      <c r="F8" s="158"/>
       <c r="G8" s="93" t="s">
         <v>173</v>
       </c>
@@ -3101,21 +3110,21 @@
       <c r="K8" s="92"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A9" s="159"/>
-      <c r="B9" s="123" t="s">
+      <c r="A9" s="161"/>
+      <c r="B9" s="125" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="123"/>
+      <c r="C9" s="125"/>
       <c r="D9" s="92" t="s">
         <v>163</v>
       </c>
       <c r="E9" s="93" t="s">
-        <v>485</v>
-      </c>
-      <c r="F9" s="156"/>
+        <v>480</v>
+      </c>
+      <c r="F9" s="158"/>
       <c r="G9" s="95"/>
       <c r="H9" s="94" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I9" s="92" t="s">
         <v>180</v>
@@ -3124,213 +3133,213 @@
       <c r="K9" s="92"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A10" s="159"/>
-      <c r="B10" s="123" t="s">
-        <v>413</v>
-      </c>
-      <c r="C10" s="123"/>
+      <c r="A10" s="161"/>
+      <c r="B10" s="125" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" s="125"/>
       <c r="D10" s="92" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E10" s="93" t="s">
-        <v>306</v>
-      </c>
-      <c r="F10" s="156"/>
+        <v>303</v>
+      </c>
+      <c r="F10" s="158"/>
       <c r="G10" s="95"/>
       <c r="H10" s="94" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I10" s="94" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J10" s="92"/>
       <c r="K10" s="92"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A11" s="159"/>
-      <c r="B11" s="123" t="s">
-        <v>435</v>
-      </c>
-      <c r="C11" s="123"/>
+      <c r="A11" s="161"/>
+      <c r="B11" s="125" t="s">
+        <v>431</v>
+      </c>
+      <c r="C11" s="125"/>
       <c r="D11" s="92" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E11" s="94" t="s">
-        <v>315</v>
-      </c>
-      <c r="F11" s="156"/>
-      <c r="G11" s="123" t="s">
-        <v>440</v>
-      </c>
-      <c r="H11" s="123"/>
+        <v>312</v>
+      </c>
+      <c r="F11" s="158"/>
+      <c r="G11" s="125" t="s">
+        <v>436</v>
+      </c>
+      <c r="H11" s="125"/>
       <c r="I11" s="94" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J11" s="92"/>
       <c r="K11" s="92"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A12" s="159"/>
-      <c r="B12" s="123" t="s">
+      <c r="A12" s="161"/>
+      <c r="B12" s="125" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="123"/>
+      <c r="C12" s="125"/>
       <c r="D12" s="94" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E12" s="94" t="s">
-        <v>316</v>
-      </c>
-      <c r="F12" s="156"/>
-      <c r="G12" s="129" t="s">
-        <v>441</v>
-      </c>
-      <c r="H12" s="130"/>
-      <c r="I12" s="169" t="s">
+        <v>313</v>
+      </c>
+      <c r="F12" s="158"/>
+      <c r="G12" s="131" t="s">
+        <v>437</v>
+      </c>
+      <c r="H12" s="132"/>
+      <c r="I12" s="171" t="s">
         <v>140</v>
       </c>
-      <c r="J12" s="170"/>
+      <c r="J12" s="172"/>
       <c r="K12" s="92"/>
     </row>
     <row r="13" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A13" s="159"/>
-      <c r="B13" s="123" t="s">
-        <v>436</v>
-      </c>
-      <c r="C13" s="123"/>
+      <c r="A13" s="161"/>
+      <c r="B13" s="125" t="s">
+        <v>432</v>
+      </c>
+      <c r="C13" s="125"/>
       <c r="D13" s="94" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E13" s="94" t="s">
-        <v>317</v>
-      </c>
-      <c r="F13" s="156"/>
-      <c r="G13" s="169" t="s">
-        <v>480</v>
-      </c>
-      <c r="H13" s="170"/>
-      <c r="I13" s="169" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13" s="158"/>
+      <c r="G13" s="171" t="s">
+        <v>476</v>
+      </c>
+      <c r="H13" s="172"/>
+      <c r="I13" s="171" t="s">
         <v>139</v>
       </c>
-      <c r="J13" s="170"/>
+      <c r="J13" s="172"/>
       <c r="K13" s="92"/>
     </row>
     <row r="14" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A14" s="159"/>
-      <c r="B14" s="123" t="s">
-        <v>437</v>
-      </c>
-      <c r="C14" s="123"/>
+      <c r="A14" s="161"/>
+      <c r="B14" s="125" t="s">
+        <v>433</v>
+      </c>
+      <c r="C14" s="125"/>
       <c r="D14" s="94" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E14" s="94" t="s">
-        <v>433</v>
-      </c>
-      <c r="F14" s="156"/>
-      <c r="G14" s="129" t="s">
-        <v>442</v>
-      </c>
-      <c r="H14" s="130"/>
+        <v>429</v>
+      </c>
+      <c r="F14" s="158"/>
+      <c r="G14" s="131" t="s">
+        <v>438</v>
+      </c>
+      <c r="H14" s="132"/>
       <c r="I14" s="97"/>
       <c r="J14" s="92"/>
       <c r="K14" s="92"/>
     </row>
     <row r="15" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A15" s="159"/>
-      <c r="B15" s="131" t="s">
-        <v>505</v>
-      </c>
-      <c r="C15" s="131"/>
-      <c r="D15" s="129" t="s">
-        <v>438</v>
-      </c>
-      <c r="E15" s="130"/>
-      <c r="F15" s="156"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="130"/>
+      <c r="A15" s="161"/>
+      <c r="B15" s="133" t="s">
+        <v>499</v>
+      </c>
+      <c r="C15" s="133"/>
+      <c r="D15" s="131" t="s">
+        <v>434</v>
+      </c>
+      <c r="E15" s="132"/>
+      <c r="F15" s="158"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="132"/>
       <c r="I15" s="91"/>
       <c r="J15" s="92"/>
       <c r="K15" s="92"/>
     </row>
     <row r="16" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A16" s="159"/>
-      <c r="B16" s="123" t="s">
+      <c r="A16" s="161"/>
+      <c r="B16" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="123"/>
-      <c r="D16" s="123" t="s">
+      <c r="C16" s="125"/>
+      <c r="D16" s="125" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="123"/>
-      <c r="F16" s="157"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="159"/>
       <c r="G16" s="98"/>
-      <c r="H16" s="123" t="s">
-        <v>443</v>
-      </c>
-      <c r="I16" s="123"/>
+      <c r="H16" s="125" t="s">
+        <v>439</v>
+      </c>
+      <c r="I16" s="125"/>
       <c r="J16" s="92"/>
       <c r="K16" s="92"/>
     </row>
     <row r="17" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A17" s="159"/>
+      <c r="A17" s="161"/>
       <c r="B17" s="98"/>
       <c r="C17" s="98"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="130"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="132"/>
       <c r="F17" s="99" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G17" s="98"/>
-      <c r="H17" s="123"/>
-      <c r="I17" s="123"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="125"/>
       <c r="J17" s="92"/>
       <c r="K17" s="92"/>
     </row>
     <row r="18" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A18" s="159"/>
+      <c r="A18" s="161"/>
       <c r="B18" s="95"/>
       <c r="C18" s="95"/>
-      <c r="D18" s="140" t="s">
+      <c r="D18" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="E18" s="140"/>
+      <c r="E18" s="142"/>
       <c r="F18" s="99" t="s">
         <v>168</v>
       </c>
-      <c r="G18" s="131" t="s">
-        <v>500</v>
-      </c>
-      <c r="H18" s="131"/>
+      <c r="G18" s="133" t="s">
+        <v>494</v>
+      </c>
+      <c r="H18" s="133"/>
       <c r="I18" s="97"/>
       <c r="J18" s="92"/>
       <c r="K18" s="92"/>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
-      <c r="A19" s="159"/>
+      <c r="A19" s="161"/>
       <c r="B19" s="95"/>
       <c r="C19" s="95"/>
-      <c r="D19" s="131" t="s">
-        <v>509</v>
-      </c>
-      <c r="E19" s="131"/>
+      <c r="D19" s="133" t="s">
+        <v>503</v>
+      </c>
+      <c r="E19" s="133"/>
       <c r="F19" s="99" t="s">
         <v>169</v>
       </c>
-      <c r="G19" s="123"/>
-      <c r="H19" s="123"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
       <c r="I19" s="97"/>
       <c r="J19" s="92"/>
       <c r="K19" s="92"/>
     </row>
     <row r="20" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A20" s="160"/>
+      <c r="A20" s="162"/>
       <c r="B20" s="100"/>
       <c r="C20" s="100"/>
-      <c r="D20" s="123" t="s">
+      <c r="D20" s="125" t="s">
         <v>89</v>
       </c>
-      <c r="E20" s="123"/>
+      <c r="E20" s="125"/>
       <c r="F20" s="101"/>
       <c r="G20" s="102"/>
       <c r="H20" s="102"/>
@@ -3352,7 +3361,7 @@
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A22" s="124" t="s">
+      <c r="A22" s="126" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="81" t="s">
@@ -3364,20 +3373,20 @@
       <c r="D22" s="95"/>
       <c r="E22" s="95"/>
       <c r="F22" s="94" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G22" s="92" t="s">
         <v>164</v>
       </c>
       <c r="H22" s="92" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="I22" s="92" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
-      <c r="A23" s="125"/>
+      <c r="A23" s="127"/>
       <c r="B23" s="23" t="s">
         <v>41</v>
       </c>
@@ -3385,7 +3394,7 @@
         <v>192</v>
       </c>
       <c r="D23" s="92" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E23" s="92" t="s">
         <v>206</v>
@@ -3404,7 +3413,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
-      <c r="A24" s="125"/>
+      <c r="A24" s="127"/>
       <c r="B24" s="23" t="s">
         <v>185</v>
       </c>
@@ -3418,7 +3427,7 @@
         <v>208</v>
       </c>
       <c r="F24" s="99" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G24" s="102"/>
       <c r="I24" s="92" t="s">
@@ -3430,7 +3439,7 @@
       <c r="K24" s="108"/>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
-      <c r="A25" s="125"/>
+      <c r="A25" s="127"/>
       <c r="B25" s="23" t="s">
         <v>182</v>
       </c>
@@ -3450,7 +3459,7 @@
         <v>167</v>
       </c>
       <c r="H25" s="94" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="I25" s="92" t="s">
         <v>219</v>
@@ -3459,7 +3468,7 @@
       <c r="K25" s="108"/>
     </row>
     <row r="26" spans="1:11" s="17" customFormat="1" ht="30" customHeight="1">
-      <c r="A26" s="125"/>
+      <c r="A26" s="127"/>
       <c r="B26" s="23" t="s">
         <v>183</v>
       </c>
@@ -3472,14 +3481,14 @@
       <c r="E26" s="92" t="s">
         <v>212</v>
       </c>
-      <c r="F26" s="161" t="s">
-        <v>419</v>
+      <c r="F26" s="163" t="s">
+        <v>415</v>
       </c>
       <c r="G26" s="92" t="s">
         <v>216</v>
       </c>
       <c r="H26" s="94" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I26" s="92" t="s">
         <v>220</v>
@@ -3488,7 +3497,7 @@
       <c r="K26" s="108"/>
     </row>
     <row r="27" spans="1:11" s="17" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="125"/>
+      <c r="A27" s="127"/>
       <c r="B27" s="23" t="s">
         <v>184</v>
       </c>
@@ -3501,21 +3510,21 @@
       <c r="E27" s="94" t="s">
         <v>213</v>
       </c>
-      <c r="F27" s="162"/>
+      <c r="F27" s="164"/>
       <c r="G27" s="92" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H27" s="94" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="I27" s="92" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="J27" s="109"/>
       <c r="K27" s="108"/>
     </row>
     <row r="28" spans="1:11" ht="30" customHeight="1">
-      <c r="A28" s="125"/>
+      <c r="A28" s="127"/>
       <c r="B28" s="23" t="s">
         <v>186</v>
       </c>
@@ -3523,24 +3532,24 @@
         <v>199</v>
       </c>
       <c r="D28" s="94" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E28" s="92" t="s">
-        <v>307</v>
-      </c>
-      <c r="F28" s="162"/>
+        <v>304</v>
+      </c>
+      <c r="F28" s="164"/>
       <c r="G28" s="92" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H28" s="94" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="I28" s="95"/>
       <c r="J28" s="109"/>
       <c r="K28" s="108"/>
     </row>
     <row r="29" spans="1:11" ht="30" customHeight="1">
-      <c r="A29" s="125"/>
+      <c r="A29" s="127"/>
       <c r="B29" s="23" t="s">
         <v>187</v>
       </c>
@@ -3548,14 +3557,14 @@
         <v>200</v>
       </c>
       <c r="D29" s="92" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E29" s="94" t="s">
-        <v>321</v>
-      </c>
-      <c r="F29" s="162"/>
+        <v>318</v>
+      </c>
+      <c r="F29" s="164"/>
       <c r="G29" s="94" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H29" s="98"/>
       <c r="I29" s="95"/>
@@ -3563,7 +3572,7 @@
       <c r="K29" s="108"/>
     </row>
     <row r="30" spans="1:11" ht="30" customHeight="1">
-      <c r="A30" s="125"/>
+      <c r="A30" s="127"/>
       <c r="B30" s="23" t="s">
         <v>188</v>
       </c>
@@ -3571,14 +3580,14 @@
         <v>201</v>
       </c>
       <c r="D30" s="93" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E30" s="94" t="s">
-        <v>323</v>
-      </c>
-      <c r="F30" s="162"/>
+        <v>320</v>
+      </c>
+      <c r="F30" s="164"/>
       <c r="G30" s="94" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H30" s="98"/>
       <c r="I30" s="95"/>
@@ -3586,7 +3595,7 @@
       <c r="K30" s="108"/>
     </row>
     <row r="31" spans="1:11" ht="30" customHeight="1">
-      <c r="A31" s="125"/>
+      <c r="A31" s="127"/>
       <c r="B31" s="23" t="s">
         <v>189</v>
       </c>
@@ -3594,10 +3603,10 @@
         <v>203</v>
       </c>
       <c r="D31" s="94" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E31" s="95"/>
-      <c r="F31" s="162"/>
+      <c r="F31" s="164"/>
       <c r="G31" s="102"/>
       <c r="H31" s="98"/>
       <c r="I31" s="108"/>
@@ -3605,7 +3614,7 @@
       <c r="K31" s="108"/>
     </row>
     <row r="32" spans="1:11" ht="30" customHeight="1">
-      <c r="A32" s="125"/>
+      <c r="A32" s="127"/>
       <c r="B32" s="23" t="s">
         <v>190</v>
       </c>
@@ -3613,20 +3622,20 @@
         <v>202</v>
       </c>
       <c r="D32" s="110" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E32" s="98"/>
-      <c r="F32" s="162"/>
-      <c r="G32" s="140" t="s">
+      <c r="F32" s="164"/>
+      <c r="G32" s="142" t="s">
         <v>143</v>
       </c>
-      <c r="H32" s="140"/>
+      <c r="H32" s="142"/>
       <c r="I32" s="98"/>
       <c r="J32" s="109"/>
       <c r="K32" s="108"/>
     </row>
     <row r="33" spans="1:11" ht="30" customHeight="1">
-      <c r="A33" s="125"/>
+      <c r="A33" s="127"/>
       <c r="B33" s="23" t="s">
         <v>191</v>
       </c>
@@ -3634,70 +3643,70 @@
         <v>198</v>
       </c>
       <c r="D33" s="94" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E33" s="98"/>
-      <c r="F33" s="162"/>
-      <c r="G33" s="140" t="s">
+      <c r="F33" s="164"/>
+      <c r="G33" s="142" t="s">
         <v>142</v>
       </c>
-      <c r="H33" s="140"/>
+      <c r="H33" s="142"/>
       <c r="I33" s="108"/>
       <c r="J33" s="109"/>
       <c r="K33" s="108"/>
     </row>
     <row r="34" spans="1:11" ht="27" customHeight="1">
-      <c r="A34" s="125"/>
+      <c r="A34" s="127"/>
       <c r="B34" s="55"/>
       <c r="C34" s="92" t="s">
         <v>197</v>
       </c>
-      <c r="D34" s="140" t="s">
+      <c r="D34" s="142" t="s">
         <v>141</v>
       </c>
-      <c r="E34" s="140"/>
-      <c r="F34" s="162"/>
-      <c r="G34" s="131" t="s">
-        <v>502</v>
-      </c>
-      <c r="H34" s="131"/>
+      <c r="E34" s="142"/>
+      <c r="F34" s="164"/>
+      <c r="G34" s="133" t="s">
+        <v>496</v>
+      </c>
+      <c r="H34" s="133"/>
       <c r="I34" s="108"/>
       <c r="J34" s="109"/>
       <c r="K34" s="108"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="125"/>
+      <c r="A35" s="127"/>
       <c r="B35" s="55"/>
       <c r="C35" s="92" t="s">
         <v>204</v>
       </c>
       <c r="D35" s="95"/>
       <c r="E35" s="95"/>
-      <c r="F35" s="162"/>
-      <c r="G35" s="148" t="s">
+      <c r="F35" s="164"/>
+      <c r="G35" s="151" t="s">
         <v>148</v>
       </c>
-      <c r="H35" s="148"/>
+      <c r="H35" s="151"/>
       <c r="I35" s="98"/>
       <c r="J35" s="109"/>
       <c r="K35" s="108"/>
     </row>
     <row r="36" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A36" s="167"/>
+      <c r="A36" s="169"/>
       <c r="B36" s="23"/>
       <c r="C36" s="92" t="s">
         <v>205</v>
       </c>
-      <c r="D36" s="123" t="s">
-        <v>445</v>
-      </c>
-      <c r="E36" s="123"/>
-      <c r="F36" s="162"/>
+      <c r="D36" s="125" t="s">
+        <v>441</v>
+      </c>
+      <c r="E36" s="125"/>
+      <c r="F36" s="164"/>
       <c r="G36" s="98"/>
-      <c r="H36" s="140" t="s">
+      <c r="H36" s="142" t="s">
         <v>144</v>
       </c>
-      <c r="I36" s="140"/>
+      <c r="I36" s="142"/>
       <c r="J36" s="105"/>
       <c r="K36" s="92"/>
     </row>
@@ -3705,14 +3714,14 @@
       <c r="A37" s="14"/>
       <c r="B37" s="81"/>
       <c r="C37" s="95"/>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="162"/>
+      <c r="D37" s="125"/>
+      <c r="E37" s="125"/>
+      <c r="F37" s="164"/>
       <c r="G37" s="97"/>
-      <c r="H37" s="135" t="s">
-        <v>447</v>
-      </c>
-      <c r="I37" s="135"/>
+      <c r="H37" s="137" t="s">
+        <v>443</v>
+      </c>
+      <c r="I37" s="137"/>
       <c r="J37" s="105"/>
       <c r="K37" s="105"/>
     </row>
@@ -3720,16 +3729,16 @@
       <c r="A38" s="14"/>
       <c r="B38" s="81"/>
       <c r="C38" s="95"/>
-      <c r="D38" s="123" t="s">
-        <v>446</v>
-      </c>
-      <c r="E38" s="123"/>
-      <c r="F38" s="162"/>
+      <c r="D38" s="125" t="s">
+        <v>442</v>
+      </c>
+      <c r="E38" s="125"/>
+      <c r="F38" s="164"/>
       <c r="G38" s="95"/>
-      <c r="H38" s="123" t="s">
-        <v>448</v>
-      </c>
-      <c r="I38" s="123"/>
+      <c r="H38" s="125" t="s">
+        <v>444</v>
+      </c>
+      <c r="I38" s="125"/>
       <c r="J38" s="105"/>
       <c r="K38" s="105"/>
     </row>
@@ -3737,16 +3746,16 @@
       <c r="A39" s="14"/>
       <c r="B39" s="64"/>
       <c r="C39" s="111"/>
-      <c r="D39" s="141" t="s">
+      <c r="D39" s="143" t="s">
         <v>91</v>
       </c>
-      <c r="E39" s="142"/>
-      <c r="F39" s="163"/>
+      <c r="E39" s="144"/>
+      <c r="F39" s="165"/>
       <c r="G39" s="101"/>
-      <c r="H39" s="129" t="s">
-        <v>451</v>
-      </c>
-      <c r="I39" s="130"/>
+      <c r="H39" s="131" t="s">
+        <v>447</v>
+      </c>
+      <c r="I39" s="132"/>
       <c r="J39" s="105"/>
       <c r="K39" s="105"/>
     </row>
@@ -3754,10 +3763,10 @@
       <c r="A40" s="13"/>
       <c r="B40" s="18"/>
       <c r="C40" s="34"/>
-      <c r="D40" s="138" t="s">
+      <c r="D40" s="140" t="s">
         <v>152</v>
       </c>
-      <c r="E40" s="139"/>
+      <c r="E40" s="141"/>
       <c r="F40" s="81"/>
       <c r="G40" s="81"/>
       <c r="J40" s="82"/>
@@ -3777,7 +3786,7 @@
       <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:11" ht="25.5">
-      <c r="A42" s="136" t="s">
+      <c r="A42" s="138" t="s">
         <v>14</v>
       </c>
       <c r="B42" s="65" t="s">
@@ -3790,25 +3799,25 @@
         <v>164</v>
       </c>
       <c r="E42" s="92" t="s">
-        <v>439</v>
-      </c>
-      <c r="F42" s="137" t="s">
-        <v>418</v>
+        <v>435</v>
+      </c>
+      <c r="F42" s="139" t="s">
+        <v>414</v>
       </c>
       <c r="G42" s="92" t="s">
         <v>177</v>
       </c>
-      <c r="H42" s="123" t="s">
+      <c r="H42" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="I42" s="123"/>
-      <c r="J42" s="145" t="s">
+      <c r="I42" s="125"/>
+      <c r="J42" s="148" t="s">
         <v>28</v>
       </c>
-      <c r="K42" s="130"/>
+      <c r="K42" s="132"/>
     </row>
     <row r="43" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A43" s="136"/>
+      <c r="A43" s="138"/>
       <c r="B43" s="65" t="s">
         <v>223</v>
       </c>
@@ -3821,7 +3830,7 @@
       <c r="E43" s="92" t="s">
         <v>174</v>
       </c>
-      <c r="F43" s="137"/>
+      <c r="F43" s="139"/>
       <c r="G43" s="92" t="s">
         <v>218</v>
       </c>
@@ -3837,7 +3846,7 @@
       <c r="K43" s="92"/>
     </row>
     <row r="44" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A44" s="136"/>
+      <c r="A44" s="138"/>
       <c r="B44" s="65" t="s">
         <v>221</v>
       </c>
@@ -3845,14 +3854,14 @@
         <v>225</v>
       </c>
       <c r="D44" s="112" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="E44" s="94" t="s">
         <v>234</v>
       </c>
-      <c r="F44" s="137"/>
+      <c r="F44" s="139"/>
       <c r="G44" s="93" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H44" s="92" t="s">
         <v>239</v>
@@ -3864,18 +3873,18 @@
       <c r="K44" s="92"/>
     </row>
     <row r="45" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A45" s="136"/>
+      <c r="A45" s="138"/>
       <c r="B45" s="61"/>
       <c r="C45" s="92" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D45" s="92" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E45" s="92" t="s">
         <v>235</v>
       </c>
-      <c r="F45" s="137"/>
+      <c r="F45" s="139"/>
       <c r="G45" s="92" t="s">
         <v>236</v>
       </c>
@@ -3883,13 +3892,13 @@
         <v>240</v>
       </c>
       <c r="I45" s="94" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="J45" s="105"/>
       <c r="K45" s="92"/>
     </row>
     <row r="46" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A46" s="136"/>
+      <c r="A46" s="138"/>
       <c r="B46" s="61"/>
       <c r="C46" s="92" t="s">
         <v>226</v>
@@ -3898,9 +3907,9 @@
         <v>233</v>
       </c>
       <c r="E46" s="92" t="s">
-        <v>450</v>
-      </c>
-      <c r="F46" s="137"/>
+        <v>446</v>
+      </c>
+      <c r="F46" s="139"/>
       <c r="G46" s="92" t="s">
         <v>237</v>
       </c>
@@ -3908,560 +3917,560 @@
       <c r="I46" s="95"/>
     </row>
     <row r="47" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A47" s="136"/>
+      <c r="A47" s="138"/>
       <c r="B47" s="61"/>
       <c r="C47" s="92" t="s">
         <v>227</v>
       </c>
       <c r="D47" s="92" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E47" s="92" t="s">
-        <v>311</v>
-      </c>
-      <c r="F47" s="137"/>
+        <v>308</v>
+      </c>
+      <c r="F47" s="139"/>
       <c r="G47" s="102"/>
       <c r="H47" s="95"/>
       <c r="I47" s="95"/>
     </row>
-    <row r="48" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A48" s="136"/>
-      <c r="B48" s="59"/>
-      <c r="C48" s="92" t="s">
+    <row r="48" spans="1:11" s="17" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A48" s="138"/>
+      <c r="B48" s="61"/>
+      <c r="C48" s="124"/>
+      <c r="D48" s="124"/>
+      <c r="E48" s="94" t="s">
+        <v>510</v>
+      </c>
+      <c r="F48" s="139"/>
+      <c r="G48" s="102"/>
+      <c r="H48" s="95"/>
+      <c r="I48" s="173"/>
+    </row>
+    <row r="49" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A49" s="138"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="92" t="s">
         <v>228</v>
       </c>
-      <c r="D48" s="94" t="s">
+      <c r="D49" s="94" t="s">
+        <v>324</v>
+      </c>
+      <c r="E49" s="107" t="s">
+        <v>498</v>
+      </c>
+      <c r="F49" s="139"/>
+      <c r="G49" s="94" t="s">
         <v>327</v>
       </c>
-      <c r="E48" s="107" t="s">
-        <v>504</v>
-      </c>
-      <c r="F48" s="137"/>
-      <c r="G48" s="94" t="s">
-        <v>330</v>
-      </c>
-      <c r="H48" s="95"/>
-      <c r="I48" s="97"/>
-      <c r="J48" s="105"/>
-      <c r="K48" s="92"/>
-    </row>
-    <row r="49" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A49" s="136"/>
-      <c r="B49" s="83"/>
-      <c r="C49" s="92" t="s">
-        <v>489</v>
-      </c>
-      <c r="D49" s="94" t="s">
-        <v>329</v>
-      </c>
-      <c r="E49" s="94" t="s">
-        <v>328</v>
-      </c>
-      <c r="F49" s="137"/>
-      <c r="G49" s="98"/>
-      <c r="H49" s="140" t="s">
-        <v>487</v>
-      </c>
-      <c r="I49" s="140"/>
+      <c r="H49" s="95"/>
+      <c r="I49" s="97"/>
       <c r="J49" s="105"/>
       <c r="K49" s="92"/>
     </row>
     <row r="50" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A50" s="136"/>
+      <c r="A50" s="138"/>
       <c r="B50" s="83"/>
       <c r="C50" s="92" t="s">
-        <v>229</v>
-      </c>
-      <c r="D50" s="149" t="s">
-        <v>81</v>
-      </c>
-      <c r="E50" s="149"/>
-      <c r="F50" s="137"/>
-      <c r="G50" s="92"/>
-      <c r="H50" s="123" t="s">
-        <v>496</v>
-      </c>
-      <c r="I50" s="123"/>
+        <v>483</v>
+      </c>
+      <c r="D50" s="94" t="s">
+        <v>326</v>
+      </c>
+      <c r="E50" s="94" t="s">
+        <v>325</v>
+      </c>
+      <c r="F50" s="139"/>
+      <c r="G50" s="98"/>
+      <c r="H50" s="142" t="s">
+        <v>508</v>
+      </c>
+      <c r="I50" s="142"/>
       <c r="J50" s="105"/>
       <c r="K50" s="92"/>
     </row>
     <row r="51" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A51" s="136"/>
+      <c r="A51" s="138"/>
       <c r="B51" s="83"/>
       <c r="C51" s="92" t="s">
-        <v>230</v>
-      </c>
-      <c r="D51" s="149" t="s">
-        <v>86</v>
-      </c>
-      <c r="E51" s="149"/>
-      <c r="F51" s="92" t="s">
-        <v>473</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="D51" s="145" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="145"/>
+      <c r="F51" s="139"/>
       <c r="G51" s="92"/>
-      <c r="H51" s="123" t="s">
-        <v>412</v>
-      </c>
-      <c r="I51" s="123"/>
+      <c r="H51" s="125" t="s">
+        <v>490</v>
+      </c>
+      <c r="I51" s="125"/>
       <c r="J51" s="105"/>
       <c r="K51" s="92"/>
     </row>
     <row r="52" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A52" s="136"/>
+      <c r="A52" s="138"/>
       <c r="B52" s="83"/>
       <c r="C52" s="92" t="s">
-        <v>493</v>
-      </c>
-      <c r="D52" s="123" t="s">
-        <v>88</v>
-      </c>
-      <c r="E52" s="123"/>
+        <v>230</v>
+      </c>
+      <c r="D52" s="145" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" s="145"/>
       <c r="F52" s="92" t="s">
-        <v>215</v>
-      </c>
-      <c r="G52" s="95"/>
-      <c r="H52" s="123" t="s">
-        <v>95</v>
-      </c>
-      <c r="I52" s="123"/>
-      <c r="J52" s="92"/>
+        <v>469</v>
+      </c>
+      <c r="G52" s="92"/>
+      <c r="H52" s="125" t="s">
+        <v>408</v>
+      </c>
+      <c r="I52" s="125"/>
+      <c r="J52" s="105"/>
       <c r="K52" s="92"/>
     </row>
     <row r="53" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A53" s="136"/>
+      <c r="A53" s="138"/>
       <c r="B53" s="83"/>
       <c r="C53" s="92" t="s">
-        <v>231</v>
-      </c>
-      <c r="D53" s="123" t="s">
-        <v>155</v>
-      </c>
-      <c r="E53" s="123"/>
-      <c r="F53" s="123" t="s">
-        <v>74</v>
-      </c>
-      <c r="G53" s="123"/>
-      <c r="H53" s="123" t="s">
-        <v>156</v>
-      </c>
-      <c r="I53" s="123"/>
+        <v>487</v>
+      </c>
+      <c r="D53" s="125" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53" s="125"/>
+      <c r="F53" s="92" t="s">
+        <v>215</v>
+      </c>
+      <c r="G53" s="95"/>
+      <c r="H53" s="125" t="s">
+        <v>95</v>
+      </c>
+      <c r="I53" s="125"/>
       <c r="J53" s="92"/>
       <c r="K53" s="92"/>
     </row>
-    <row r="54" spans="1:11" s="17" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A54" s="136"/>
+    <row r="54" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A54" s="138"/>
       <c r="B54" s="83"/>
-      <c r="C54" s="92"/>
-      <c r="D54" s="140" t="s">
-        <v>483</v>
-      </c>
-      <c r="E54" s="140"/>
-      <c r="F54" s="92"/>
-      <c r="G54" s="92"/>
-      <c r="H54" s="92"/>
-      <c r="I54" s="92"/>
+      <c r="C54" s="92" t="s">
+        <v>231</v>
+      </c>
+      <c r="D54" s="125" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" s="125"/>
+      <c r="F54" s="125" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" s="125"/>
+      <c r="H54" s="125" t="s">
+        <v>156</v>
+      </c>
+      <c r="I54" s="125"/>
       <c r="J54" s="92"/>
       <c r="K54" s="92"/>
     </row>
-    <row r="55" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A55" s="136"/>
+    <row r="55" spans="1:11" s="17" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A55" s="138"/>
       <c r="B55" s="83"/>
-      <c r="C55" s="92" t="s">
-        <v>232</v>
-      </c>
-      <c r="D55" s="123" t="s">
-        <v>452</v>
-      </c>
-      <c r="E55" s="123"/>
-      <c r="F55" s="98"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="142" t="s">
+        <v>507</v>
+      </c>
+      <c r="E55" s="142"/>
+      <c r="F55" s="92"/>
       <c r="G55" s="92"/>
-      <c r="H55" s="95"/>
-      <c r="I55" s="95"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="92"/>
       <c r="J55" s="92"/>
       <c r="K55" s="92"/>
     </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="8"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
-    </row>
-    <row r="57" spans="1:11" ht="26.25" thickBot="1">
-      <c r="A57" s="124" t="s">
+    <row r="56" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A56" s="138"/>
+      <c r="B56" s="83"/>
+      <c r="C56" s="92" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="125" t="s">
+        <v>448</v>
+      </c>
+      <c r="E56" s="125"/>
+      <c r="F56" s="98"/>
+      <c r="G56" s="92"/>
+      <c r="H56" s="95"/>
+      <c r="I56" s="95"/>
+      <c r="J56" s="92"/>
+      <c r="K56" s="92"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="8"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+    </row>
+    <row r="58" spans="1:11" ht="26.25" thickBot="1">
+      <c r="A58" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="B57" s="92" t="s">
+      <c r="B58" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="C57" s="92" t="s">
+      <c r="C58" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="D57" s="101"/>
-      <c r="E57" s="101"/>
-      <c r="F57" s="155" t="s">
-        <v>418</v>
-      </c>
-      <c r="G57" s="92" t="s">
+      <c r="D58" s="101"/>
+      <c r="E58" s="101"/>
+      <c r="F58" s="157" t="s">
+        <v>414</v>
+      </c>
+      <c r="G58" s="92" t="s">
+        <v>258</v>
+      </c>
+      <c r="H58" s="93" t="s">
+        <v>259</v>
+      </c>
+      <c r="I58" s="92" t="s">
         <v>260</v>
       </c>
-      <c r="H57" s="93" t="s">
+      <c r="J58" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="K58" s="132"/>
+    </row>
+    <row r="59" spans="1:11" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A59" s="127"/>
+      <c r="B59" s="92"/>
+      <c r="C59" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D59" s="151" t="s">
+        <v>149</v>
+      </c>
+      <c r="E59" s="151"/>
+      <c r="F59" s="158"/>
+      <c r="G59" s="92" t="s">
         <v>261</v>
       </c>
-      <c r="I57" s="92" t="s">
+      <c r="H59" s="92" t="s">
         <v>262</v>
       </c>
-      <c r="J57" s="145" t="s">
-        <v>28</v>
-      </c>
-      <c r="K57" s="130"/>
-    </row>
-    <row r="58" spans="1:11" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A58" s="125"/>
-      <c r="B58" s="92"/>
-      <c r="C58" s="113" t="s">
-        <v>41</v>
-      </c>
-      <c r="D58" s="148" t="s">
-        <v>149</v>
-      </c>
-      <c r="E58" s="148"/>
-      <c r="F58" s="156"/>
-      <c r="G58" s="92" t="s">
+      <c r="I59" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="H58" s="92" t="s">
+      <c r="J59" s="155" t="s">
+        <v>471</v>
+      </c>
+      <c r="K59" s="156"/>
+    </row>
+    <row r="60" spans="1:11" ht="29.25" customHeight="1" thickBot="1">
+      <c r="A60" s="127"/>
+      <c r="B60" s="92" t="s">
+        <v>224</v>
+      </c>
+      <c r="C60" s="113" t="s">
+        <v>185</v>
+      </c>
+      <c r="D60" s="92" t="s">
+        <v>440</v>
+      </c>
+      <c r="E60" s="92" t="s">
+        <v>206</v>
+      </c>
+      <c r="F60" s="158"/>
+      <c r="G60" s="94" t="s">
+        <v>234</v>
+      </c>
+      <c r="H60" s="94" t="s">
         <v>264</v>
       </c>
-      <c r="I58" s="92" t="s">
+      <c r="I60" s="92" t="s">
+        <v>175</v>
+      </c>
+      <c r="J60" s="155" t="s">
+        <v>153</v>
+      </c>
+      <c r="K60" s="156"/>
+    </row>
+    <row r="61" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A61" s="127"/>
+      <c r="B61" s="92" t="s">
+        <v>225</v>
+      </c>
+      <c r="C61" s="113" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" s="92" t="s">
+        <v>207</v>
+      </c>
+      <c r="E61" s="92" t="s">
+        <v>208</v>
+      </c>
+      <c r="F61" s="158"/>
+      <c r="G61" s="92" t="s">
+        <v>219</v>
+      </c>
+      <c r="H61" s="92" t="s">
         <v>265</v>
       </c>
-      <c r="J58" s="153" t="s">
-        <v>475</v>
-      </c>
-      <c r="K58" s="154"/>
-    </row>
-    <row r="59" spans="1:11" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A59" s="125"/>
-      <c r="B59" s="92" t="s">
-        <v>224</v>
-      </c>
-      <c r="C59" s="113" t="s">
-        <v>185</v>
-      </c>
-      <c r="D59" s="92" t="s">
-        <v>444</v>
-      </c>
-      <c r="E59" s="92" t="s">
-        <v>206</v>
-      </c>
-      <c r="F59" s="156"/>
-      <c r="G59" s="94" t="s">
-        <v>234</v>
-      </c>
-      <c r="H59" s="94" t="s">
+      <c r="I61" s="115" t="s">
         <v>266</v>
-      </c>
-      <c r="I59" s="92" t="s">
-        <v>175</v>
-      </c>
-      <c r="J59" s="153" t="s">
-        <v>153</v>
-      </c>
-      <c r="K59" s="154"/>
-    </row>
-    <row r="60" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A60" s="125"/>
-      <c r="B60" s="92" t="s">
-        <v>225</v>
-      </c>
-      <c r="C60" s="113" t="s">
-        <v>182</v>
-      </c>
-      <c r="D60" s="92" t="s">
-        <v>207</v>
-      </c>
-      <c r="E60" s="92" t="s">
-        <v>208</v>
-      </c>
-      <c r="F60" s="156"/>
-      <c r="G60" s="92" t="s">
-        <v>219</v>
-      </c>
-      <c r="H60" s="92" t="s">
-        <v>267</v>
-      </c>
-      <c r="I60" s="115" t="s">
-        <v>268</v>
-      </c>
-      <c r="J60" s="114"/>
-      <c r="K60" s="104"/>
-    </row>
-    <row r="61" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A61" s="125"/>
-      <c r="B61" s="92" t="s">
-        <v>449</v>
-      </c>
-      <c r="C61" s="113" t="s">
-        <v>183</v>
-      </c>
-      <c r="D61" s="112" t="s">
-        <v>492</v>
-      </c>
-      <c r="E61" s="92" t="s">
-        <v>256</v>
-      </c>
-      <c r="F61" s="156"/>
-      <c r="G61" s="94" t="s">
-        <v>335</v>
-      </c>
-      <c r="H61" s="94" t="s">
-        <v>336</v>
-      </c>
-      <c r="I61" s="94" t="s">
-        <v>337</v>
       </c>
       <c r="J61" s="114"/>
       <c r="K61" s="104"/>
     </row>
     <row r="62" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A62" s="125"/>
+      <c r="A62" s="127"/>
       <c r="B62" s="92" t="s">
-        <v>226</v>
+        <v>445</v>
       </c>
       <c r="C62" s="113" t="s">
-        <v>249</v>
-      </c>
-      <c r="D62" s="94" t="s">
-        <v>257</v>
-      </c>
-      <c r="E62" s="102"/>
-      <c r="F62" s="156"/>
+        <v>183</v>
+      </c>
+      <c r="D62" s="112" t="s">
+        <v>486</v>
+      </c>
+      <c r="E62" s="92" t="s">
+        <v>254</v>
+      </c>
+      <c r="F62" s="158"/>
       <c r="G62" s="94" t="s">
-        <v>417</v>
-      </c>
-      <c r="H62" s="140" t="s">
-        <v>484</v>
-      </c>
-      <c r="I62" s="140"/>
+        <v>332</v>
+      </c>
+      <c r="H62" s="94" t="s">
+        <v>333</v>
+      </c>
+      <c r="I62" s="94" t="s">
+        <v>334</v>
+      </c>
       <c r="J62" s="114"/>
       <c r="K62" s="104"/>
     </row>
     <row r="63" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A63" s="125"/>
+      <c r="A63" s="127"/>
       <c r="B63" s="92" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C63" s="113" t="s">
+        <v>249</v>
+      </c>
+      <c r="D63" s="94" t="s">
         <v>255</v>
       </c>
-      <c r="D63" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="E63" s="92" t="s">
-        <v>258</v>
-      </c>
-      <c r="F63" s="156"/>
-      <c r="G63" s="149" t="s">
-        <v>85</v>
-      </c>
-      <c r="H63" s="149"/>
-      <c r="I63" s="92" t="s">
-        <v>454</v>
-      </c>
+      <c r="E63" s="102"/>
+      <c r="F63" s="158"/>
+      <c r="G63" s="94" t="s">
+        <v>413</v>
+      </c>
+      <c r="H63" s="142" t="s">
+        <v>479</v>
+      </c>
+      <c r="I63" s="142"/>
       <c r="J63" s="114"/>
       <c r="K63" s="104"/>
     </row>
     <row r="64" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A64" s="125"/>
+      <c r="A64" s="127"/>
       <c r="B64" s="92" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="C64" s="113" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D64" s="92" t="s">
-        <v>259</v>
-      </c>
-      <c r="E64" s="94" t="s">
-        <v>334</v>
-      </c>
-      <c r="F64" s="156"/>
-      <c r="G64" s="149" t="s">
-        <v>82</v>
-      </c>
-      <c r="H64" s="149"/>
-      <c r="I64" s="95"/>
+        <v>216</v>
+      </c>
+      <c r="E64" s="92" t="s">
+        <v>256</v>
+      </c>
+      <c r="F64" s="158"/>
+      <c r="G64" s="145" t="s">
+        <v>85</v>
+      </c>
+      <c r="H64" s="145"/>
+      <c r="I64" s="92" t="s">
+        <v>450</v>
+      </c>
       <c r="J64" s="114"/>
       <c r="K64" s="104"/>
     </row>
     <row r="65" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A65" s="125"/>
+      <c r="A65" s="127"/>
       <c r="B65" s="92" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C65" s="113" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D65" s="92" t="s">
-        <v>415</v>
-      </c>
-      <c r="E65" s="92" t="s">
-        <v>453</v>
-      </c>
-      <c r="F65" s="156"/>
-      <c r="G65" s="92" t="s">
-        <v>477</v>
-      </c>
-      <c r="H65" s="116"/>
-      <c r="I65" s="116"/>
+        <v>257</v>
+      </c>
+      <c r="E65" s="94" t="s">
+        <v>331</v>
+      </c>
+      <c r="F65" s="158"/>
+      <c r="G65" s="145" t="s">
+        <v>82</v>
+      </c>
+      <c r="H65" s="145"/>
+      <c r="I65" s="95"/>
       <c r="J65" s="114"/>
       <c r="K65" s="104"/>
     </row>
     <row r="66" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A66" s="125"/>
+      <c r="A66" s="127"/>
       <c r="B66" s="92" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C66" s="113" t="s">
-        <v>252</v>
+        <v>509</v>
       </c>
       <c r="D66" s="92" t="s">
-        <v>416</v>
-      </c>
-      <c r="E66" s="95"/>
-      <c r="F66" s="156"/>
-      <c r="G66" s="98"/>
+        <v>411</v>
+      </c>
+      <c r="E66" s="92" t="s">
+        <v>449</v>
+      </c>
+      <c r="F66" s="158"/>
+      <c r="G66" s="92" t="s">
+        <v>473</v>
+      </c>
       <c r="H66" s="116"/>
       <c r="I66" s="116"/>
       <c r="J66" s="114"/>
       <c r="K66" s="104"/>
     </row>
     <row r="67" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A67" s="125"/>
+      <c r="A67" s="127"/>
       <c r="B67" s="92" t="s">
-        <v>494</v>
+        <v>246</v>
       </c>
       <c r="C67" s="113" t="s">
-        <v>253</v>
-      </c>
-      <c r="D67" s="94" t="s">
-        <v>332</v>
+        <v>189</v>
+      </c>
+      <c r="D67" s="92" t="s">
+        <v>412</v>
       </c>
       <c r="E67" s="95"/>
-      <c r="F67" s="157"/>
-      <c r="G67" s="92"/>
-      <c r="H67" s="132" t="s">
-        <v>508</v>
-      </c>
-      <c r="I67" s="133"/>
+      <c r="F67" s="158"/>
+      <c r="G67" s="98"/>
+      <c r="H67" s="116"/>
+      <c r="I67" s="116"/>
       <c r="J67" s="114"/>
       <c r="K67" s="104"/>
     </row>
     <row r="68" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A68" s="125"/>
+      <c r="A68" s="127"/>
       <c r="B68" s="92" t="s">
-        <v>247</v>
+        <v>488</v>
       </c>
       <c r="C68" s="113" t="s">
-        <v>254</v>
+        <v>252</v>
+      </c>
+      <c r="D68" s="94" t="s">
+        <v>329</v>
       </c>
       <c r="E68" s="95"/>
-      <c r="F68" s="92" t="s">
-        <v>214</v>
-      </c>
-      <c r="G68" s="98"/>
-      <c r="H68" s="123" t="s">
-        <v>87</v>
-      </c>
-      <c r="I68" s="123"/>
+      <c r="F68" s="159"/>
+      <c r="G68" s="92"/>
+      <c r="H68" s="134" t="s">
+        <v>502</v>
+      </c>
+      <c r="I68" s="135"/>
       <c r="J68" s="114"/>
       <c r="K68" s="104"/>
     </row>
-    <row r="69" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A69" s="125"/>
+    <row r="69" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A69" s="127"/>
       <c r="B69" s="92" t="s">
-        <v>248</v>
-      </c>
-      <c r="C69" s="94" t="s">
-        <v>510</v>
-      </c>
-      <c r="D69" s="123" t="s">
-        <v>455</v>
-      </c>
-      <c r="E69" s="123"/>
-      <c r="F69" s="115"/>
+        <v>247</v>
+      </c>
+      <c r="C69" s="113" t="s">
+        <v>506</v>
+      </c>
+      <c r="E69" s="95"/>
+      <c r="F69" s="92" t="s">
+        <v>214</v>
+      </c>
       <c r="G69" s="98"/>
-      <c r="H69" s="123" t="s">
-        <v>458</v>
-      </c>
-      <c r="I69" s="123"/>
+      <c r="H69" s="125" t="s">
+        <v>87</v>
+      </c>
+      <c r="I69" s="125"/>
       <c r="J69" s="114"/>
       <c r="K69" s="104"/>
     </row>
-    <row r="70" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A70" s="125"/>
+    <row r="70" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A70" s="127"/>
       <c r="B70" s="92" t="s">
-        <v>490</v>
-      </c>
-      <c r="C70" s="113"/>
-      <c r="D70" s="135" t="s">
-        <v>456</v>
-      </c>
-      <c r="E70" s="135"/>
-      <c r="F70" s="97"/>
-      <c r="G70" s="117"/>
-      <c r="H70" s="123" t="s">
-        <v>459</v>
-      </c>
-      <c r="I70" s="123"/>
+        <v>248</v>
+      </c>
+      <c r="C70" s="94" t="s">
+        <v>504</v>
+      </c>
+      <c r="D70" s="125" t="s">
+        <v>451</v>
+      </c>
+      <c r="E70" s="125"/>
+      <c r="F70" s="115"/>
+      <c r="G70" s="98"/>
+      <c r="H70" s="125" t="s">
+        <v>454</v>
+      </c>
+      <c r="I70" s="125"/>
       <c r="J70" s="114"/>
       <c r="K70" s="104"/>
     </row>
-    <row r="71" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A71" s="125"/>
-      <c r="B71" s="101"/>
+    <row r="71" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A71" s="127"/>
+      <c r="B71" s="92" t="s">
+        <v>484</v>
+      </c>
       <c r="C71" s="113"/>
-      <c r="D71" s="123" t="s">
-        <v>157</v>
-      </c>
-      <c r="E71" s="123"/>
-      <c r="F71" s="118"/>
-      <c r="G71" s="95"/>
-      <c r="H71" s="123" t="s">
-        <v>460</v>
-      </c>
-      <c r="I71" s="123"/>
+      <c r="D71" s="137" t="s">
+        <v>452</v>
+      </c>
+      <c r="E71" s="137"/>
+      <c r="F71" s="97"/>
+      <c r="G71" s="117"/>
+      <c r="H71" s="125" t="s">
+        <v>455</v>
+      </c>
+      <c r="I71" s="125"/>
       <c r="J71" s="114"/>
       <c r="K71" s="104"/>
     </row>
-    <row r="72" spans="1:11" s="17" customFormat="1">
-      <c r="A72" s="125"/>
+    <row r="72" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A72" s="127"/>
       <c r="B72" s="101"/>
       <c r="C72" s="113"/>
-      <c r="D72" s="129" t="s">
-        <v>457</v>
-      </c>
-      <c r="E72" s="130"/>
+      <c r="D72" s="125" t="s">
+        <v>157</v>
+      </c>
+      <c r="E72" s="125"/>
       <c r="F72" s="118"/>
       <c r="G72" s="95"/>
-      <c r="H72" s="98"/>
-      <c r="I72" s="98"/>
+      <c r="H72" s="125" t="s">
+        <v>456</v>
+      </c>
+      <c r="I72" s="125"/>
       <c r="J72" s="114"/>
       <c r="K72" s="104"/>
     </row>
-    <row r="73" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A73" s="125"/>
-      <c r="B73" s="92"/>
+    <row r="73" spans="1:11" s="17" customFormat="1">
+      <c r="A73" s="127"/>
+      <c r="B73" s="101"/>
       <c r="C73" s="113"/>
-      <c r="D73" s="116"/>
-      <c r="E73" s="116"/>
+      <c r="D73" s="131" t="s">
+        <v>453</v>
+      </c>
+      <c r="E73" s="132"/>
       <c r="F73" s="118"/>
       <c r="G73" s="95"/>
       <c r="H73" s="98"/>
@@ -4469,8 +4478,8 @@
       <c r="J73" s="114"/>
       <c r="K73" s="104"/>
     </row>
-    <row r="74" spans="1:11" s="17" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A74" s="125"/>
+    <row r="74" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A74" s="127"/>
       <c r="B74" s="92"/>
       <c r="C74" s="113"/>
       <c r="D74" s="116"/>
@@ -4482,489 +4491,480 @@
       <c r="J74" s="114"/>
       <c r="K74" s="104"/>
     </row>
-    <row r="75" spans="1:11" s="17" customFormat="1">
-      <c r="A75" s="8"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="90"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="32"/>
-      <c r="K75" s="33"/>
-    </row>
-    <row r="76" spans="1:11" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A76" s="126" t="s">
+    <row r="75" spans="1:11" s="17" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A75" s="127"/>
+      <c r="B75" s="92"/>
+      <c r="C75" s="113"/>
+      <c r="D75" s="116"/>
+      <c r="E75" s="116"/>
+      <c r="F75" s="118"/>
+      <c r="G75" s="95"/>
+      <c r="H75" s="98"/>
+      <c r="I75" s="98"/>
+      <c r="J75" s="114"/>
+      <c r="K75" s="104"/>
+    </row>
+    <row r="76" spans="1:11" s="17" customFormat="1">
+      <c r="A76" s="8"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="90"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="32"/>
+      <c r="K76" s="33"/>
+    </row>
+    <row r="77" spans="1:11" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A77" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="B76" s="81" t="s">
+      <c r="B77" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C77" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="56"/>
-      <c r="E76" s="56"/>
-      <c r="F76" s="85"/>
-      <c r="G76" s="23" t="s">
-        <v>461</v>
-      </c>
-      <c r="H76" s="23" t="s">
+      <c r="D77" s="56"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="85"/>
+      <c r="G77" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="H77" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="I76" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="J76" s="146" t="s">
+      <c r="I77" s="35" t="s">
+        <v>286</v>
+      </c>
+      <c r="J77" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="K76" s="147"/>
-    </row>
-    <row r="77" spans="1:11" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A77" s="127"/>
-      <c r="B77" s="23" t="s">
+      <c r="K77" s="150"/>
+    </row>
+    <row r="78" spans="1:11" ht="28.5" customHeight="1" thickBot="1">
+      <c r="A78" s="129"/>
+      <c r="B78" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C78" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="D77" s="88" t="s">
-        <v>423</v>
-      </c>
-      <c r="E77" s="80" t="s">
-        <v>424</v>
-      </c>
-      <c r="F77" s="77"/>
-      <c r="G77" s="23" t="s">
+      <c r="D78" s="88" t="s">
+        <v>419</v>
+      </c>
+      <c r="E78" s="80" t="s">
+        <v>420</v>
+      </c>
+      <c r="F78" s="77"/>
+      <c r="G78" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="H77" s="23" t="s">
+      <c r="H78" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="I77" s="35" t="s">
-        <v>290</v>
-      </c>
-      <c r="J77" s="153" t="s">
+      <c r="I78" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="J78" s="155" t="s">
         <v>154</v>
       </c>
-      <c r="K77" s="154"/>
-    </row>
-    <row r="78" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A78" s="127"/>
-      <c r="B78" s="23" t="s">
+      <c r="K78" s="156"/>
+    </row>
+    <row r="79" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A79" s="129"/>
+      <c r="B79" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C79" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="D78" s="92" t="s">
-        <v>280</v>
-      </c>
-      <c r="E78" s="92" t="s">
-        <v>281</v>
-      </c>
-      <c r="F78" s="119"/>
-      <c r="G78" s="92" t="s">
-        <v>209</v>
-      </c>
-      <c r="H78" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="I78" s="92"/>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15"/>
-    </row>
-    <row r="79" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A79" s="127"/>
-      <c r="B79" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="C79" s="23" t="s">
-        <v>194</v>
-      </c>
       <c r="D79" s="92" t="s">
-        <v>434</v>
+        <v>277</v>
       </c>
       <c r="E79" s="92" t="s">
-        <v>425</v>
+        <v>278</v>
       </c>
       <c r="F79" s="119"/>
       <c r="G79" s="92" t="s">
-        <v>286</v>
+        <v>209</v>
       </c>
       <c r="H79" s="92" t="s">
+        <v>210</v>
+      </c>
+      <c r="I79" s="92"/>
+      <c r="J79" s="15"/>
+      <c r="K79" s="15"/>
+    </row>
+    <row r="80" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A80" s="129"/>
+      <c r="B80" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="D80" s="92" t="s">
+        <v>430</v>
+      </c>
+      <c r="E80" s="92" t="s">
+        <v>421</v>
+      </c>
+      <c r="F80" s="119"/>
+      <c r="G80" s="92" t="s">
+        <v>283</v>
+      </c>
+      <c r="H80" s="92" t="s">
         <v>179</v>
       </c>
-      <c r="I79" s="92"/>
-      <c r="J79" s="16"/>
-      <c r="K79" s="15"/>
-    </row>
-    <row r="80" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A80" s="127"/>
-      <c r="B80" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="C80" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="D80" s="120" t="s">
-        <v>492</v>
-      </c>
-      <c r="E80" s="93" t="s">
-        <v>486</v>
-      </c>
-      <c r="F80" s="119" t="s">
-        <v>419</v>
-      </c>
-      <c r="G80" s="92" t="s">
-        <v>287</v>
-      </c>
-      <c r="H80" s="123"/>
-      <c r="I80" s="123"/>
+      <c r="I80" s="92"/>
       <c r="J80" s="16"/>
       <c r="K80" s="15"/>
     </row>
     <row r="81" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A81" s="127"/>
+      <c r="A81" s="129"/>
       <c r="B81" s="23" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="D81" s="92" t="s">
-        <v>282</v>
-      </c>
-      <c r="E81" s="92" t="s">
-        <v>283</v>
-      </c>
-      <c r="F81" s="119"/>
-      <c r="G81" s="93" t="s">
-        <v>288</v>
-      </c>
-      <c r="H81" s="123" t="s">
-        <v>466</v>
-      </c>
-      <c r="I81" s="123"/>
+        <v>195</v>
+      </c>
+      <c r="D81" s="120" t="s">
+        <v>486</v>
+      </c>
+      <c r="E81" s="93" t="s">
+        <v>481</v>
+      </c>
+      <c r="F81" s="119" t="s">
+        <v>415</v>
+      </c>
+      <c r="G81" s="92" t="s">
+        <v>284</v>
+      </c>
+      <c r="H81" s="125"/>
+      <c r="I81" s="125"/>
       <c r="J81" s="16"/>
       <c r="K81" s="15"/>
     </row>
-    <row r="82" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A82" s="127"/>
+    <row r="82" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A82" s="129"/>
       <c r="B82" s="23" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D82" s="92" t="s">
-        <v>284</v>
-      </c>
-      <c r="E82" s="96" t="s">
+        <v>279</v>
+      </c>
+      <c r="E82" s="92" t="s">
+        <v>280</v>
+      </c>
+      <c r="F82" s="119"/>
+      <c r="G82" s="93" t="s">
         <v>285</v>
       </c>
-      <c r="F82" s="119"/>
-      <c r="G82" s="94" t="s">
-        <v>343</v>
-      </c>
-      <c r="H82" s="123" t="s">
-        <v>467</v>
-      </c>
-      <c r="I82" s="123"/>
+      <c r="H82" s="125" t="s">
+        <v>462</v>
+      </c>
+      <c r="I82" s="125"/>
       <c r="J82" s="16"/>
       <c r="K82" s="15"/>
     </row>
-    <row r="83" spans="1:11" ht="18" customHeight="1">
-      <c r="A83" s="127"/>
+    <row r="83" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A83" s="129"/>
       <c r="B83" s="23" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="D83" s="95"/>
-      <c r="E83" s="94" t="s">
-        <v>422</v>
+        <v>199</v>
+      </c>
+      <c r="D83" s="92" t="s">
+        <v>281</v>
+      </c>
+      <c r="E83" s="96" t="s">
+        <v>282</v>
       </c>
       <c r="F83" s="119"/>
       <c r="G83" s="94" t="s">
-        <v>344</v>
-      </c>
-      <c r="H83" s="97"/>
-      <c r="I83" s="92"/>
+        <v>339</v>
+      </c>
+      <c r="H83" s="125" t="s">
+        <v>463</v>
+      </c>
+      <c r="I83" s="125"/>
       <c r="J83" s="16"/>
       <c r="K83" s="15"/>
     </row>
-    <row r="84" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A84" s="127"/>
+    <row r="84" spans="1:11" ht="18" customHeight="1">
+      <c r="A84" s="129"/>
       <c r="B84" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="D84" s="140" t="s">
-        <v>145</v>
-      </c>
-      <c r="E84" s="140"/>
+        <v>200</v>
+      </c>
+      <c r="D84" s="95"/>
+      <c r="E84" s="94" t="s">
+        <v>418</v>
+      </c>
       <c r="F84" s="119"/>
-      <c r="G84" s="121" t="s">
-        <v>345</v>
-      </c>
-      <c r="H84" s="92"/>
+      <c r="G84" s="94" t="s">
+        <v>340</v>
+      </c>
+      <c r="H84" s="97"/>
       <c r="I84" s="92"/>
       <c r="J84" s="16"/>
       <c r="K84" s="15"/>
     </row>
-    <row r="85" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A85" s="127"/>
+    <row r="85" spans="1:11" ht="26.25" customHeight="1">
+      <c r="A85" s="129"/>
       <c r="B85" s="23" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="D85" s="94" t="s">
-        <v>338</v>
-      </c>
-      <c r="E85" s="94" t="s">
-        <v>339</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="D85" s="142" t="s">
+        <v>145</v>
+      </c>
+      <c r="E85" s="142"/>
       <c r="F85" s="119"/>
-      <c r="G85" s="123" t="s">
-        <v>468</v>
-      </c>
-      <c r="H85" s="123"/>
+      <c r="G85" s="121" t="s">
+        <v>341</v>
+      </c>
+      <c r="H85" s="92"/>
       <c r="I85" s="92"/>
       <c r="J85" s="16"/>
       <c r="K85" s="15"/>
     </row>
     <row r="86" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A86" s="127"/>
+      <c r="A86" s="129"/>
       <c r="B86" s="23" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="D86" s="94" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E86" s="94" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F86" s="119"/>
-      <c r="G86" s="140" t="s">
-        <v>146</v>
-      </c>
-      <c r="H86" s="140"/>
+      <c r="G86" s="125" t="s">
+        <v>464</v>
+      </c>
+      <c r="H86" s="125"/>
       <c r="I86" s="92"/>
       <c r="J86" s="16"/>
       <c r="K86" s="15"/>
     </row>
     <row r="87" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A87" s="127"/>
+      <c r="A87" s="129"/>
       <c r="B87" s="23" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="D87" s="95"/>
-      <c r="E87" s="94" t="s">
-        <v>342</v>
+        <v>202</v>
+      </c>
+      <c r="D87" s="94" t="s">
+        <v>337</v>
       </c>
       <c r="F87" s="119"/>
-      <c r="G87" s="149" t="s">
-        <v>83</v>
-      </c>
-      <c r="H87" s="149"/>
+      <c r="G87" s="142" t="s">
+        <v>146</v>
+      </c>
+      <c r="H87" s="142"/>
       <c r="I87" s="92"/>
       <c r="J87" s="16"/>
       <c r="K87" s="15"/>
     </row>
-    <row r="88" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A88" s="127"/>
-      <c r="B88" s="59"/>
+    <row r="88" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A88" s="129"/>
+      <c r="B88" s="123" t="s">
+        <v>505</v>
+      </c>
       <c r="C88" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="D88" s="123" t="s">
-        <v>462</v>
-      </c>
-      <c r="E88" s="123"/>
+        <v>272</v>
+      </c>
+      <c r="D88" s="95"/>
+      <c r="E88" s="94" t="s">
+        <v>338</v>
+      </c>
       <c r="F88" s="119"/>
-      <c r="G88" s="149" t="s">
-        <v>84</v>
-      </c>
-      <c r="H88" s="149"/>
+      <c r="G88" s="145" t="s">
+        <v>83</v>
+      </c>
+      <c r="H88" s="145"/>
       <c r="I88" s="92"/>
       <c r="J88" s="16"/>
       <c r="K88" s="15"/>
     </row>
     <row r="89" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A89" s="127"/>
-      <c r="B89" s="81"/>
-      <c r="C89" s="79" t="s">
-        <v>279</v>
-      </c>
-      <c r="D89" s="123" t="s">
-        <v>464</v>
-      </c>
-      <c r="E89" s="123"/>
+      <c r="A89" s="129"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D89" s="125" t="s">
+        <v>458</v>
+      </c>
+      <c r="E89" s="125"/>
       <c r="F89" s="119"/>
-      <c r="G89" s="97"/>
-      <c r="H89" s="97"/>
+      <c r="G89" s="145" t="s">
+        <v>84</v>
+      </c>
+      <c r="H89" s="145"/>
       <c r="I89" s="92"/>
       <c r="J89" s="16"/>
       <c r="K89" s="15"/>
     </row>
-    <row r="90" spans="1:11" s="17" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A90" s="127"/>
+    <row r="90" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A90" s="129"/>
       <c r="B90" s="81"/>
       <c r="C90" s="79" t="s">
-        <v>278</v>
-      </c>
-      <c r="D90" s="128" t="s">
-        <v>463</v>
-      </c>
-      <c r="E90" s="128"/>
-      <c r="F90" s="77"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="61"/>
-      <c r="I90" s="23"/>
+        <v>276</v>
+      </c>
+      <c r="D90" s="125" t="s">
+        <v>460</v>
+      </c>
+      <c r="E90" s="125"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="97"/>
+      <c r="H90" s="97"/>
+      <c r="I90" s="92"/>
       <c r="J90" s="16"/>
       <c r="K90" s="15"/>
     </row>
-    <row r="91" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A91" s="127"/>
-      <c r="B91" s="60"/>
-      <c r="C91" s="59"/>
-      <c r="D91" s="134" t="s">
-        <v>503</v>
-      </c>
-      <c r="E91" s="134"/>
+    <row r="91" spans="1:11" s="17" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A91" s="129"/>
+      <c r="B91" s="81"/>
+      <c r="C91" s="79" t="s">
+        <v>275</v>
+      </c>
+      <c r="D91" s="130" t="s">
+        <v>459</v>
+      </c>
+      <c r="E91" s="130"/>
       <c r="F91" s="77"/>
       <c r="G91" s="61"/>
-      <c r="H91" s="78"/>
+      <c r="H91" s="61"/>
       <c r="I91" s="23"/>
       <c r="J91" s="16"/>
       <c r="K91" s="15"/>
     </row>
     <row r="92" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A92" s="127"/>
-      <c r="B92" s="86"/>
+      <c r="A92" s="129"/>
+      <c r="B92" s="60"/>
       <c r="C92" s="59"/>
-      <c r="D92" s="150" t="s">
-        <v>465</v>
-      </c>
-      <c r="E92" s="150"/>
+      <c r="D92" s="136" t="s">
+        <v>497</v>
+      </c>
+      <c r="E92" s="136"/>
       <c r="F92" s="77"/>
       <c r="G92" s="61"/>
-      <c r="H92" s="55"/>
+      <c r="H92" s="78"/>
       <c r="I92" s="23"/>
       <c r="J92" s="16"/>
       <c r="K92" s="15"/>
     </row>
     <row r="93" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A93" s="127"/>
-      <c r="B93" s="60"/>
+      <c r="A93" s="129"/>
+      <c r="B93" s="86"/>
       <c r="C93" s="59"/>
-      <c r="D93" s="89"/>
-      <c r="E93" s="89"/>
-      <c r="F93" s="84"/>
+      <c r="D93" s="152" t="s">
+        <v>461</v>
+      </c>
+      <c r="E93" s="152"/>
+      <c r="F93" s="77"/>
       <c r="G93" s="61"/>
-      <c r="H93" s="36"/>
-      <c r="I93" s="24"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="23"/>
       <c r="J93" s="16"/>
       <c r="K93" s="15"/>
     </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="8"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="9"/>
-      <c r="J94" s="9"/>
-      <c r="K94" s="9"/>
-    </row>
-    <row r="95" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A95" s="126" t="s">
+    <row r="94" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A94" s="129"/>
+      <c r="B94" s="60"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="89"/>
+      <c r="E94" s="89"/>
+      <c r="F94" s="84"/>
+      <c r="G94" s="61"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="16"/>
+      <c r="K94" s="15"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="8"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9"/>
+    </row>
+    <row r="96" spans="1:11" ht="21.75" customHeight="1">
+      <c r="A96" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="B95" s="81" t="s">
+      <c r="B96" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="C95" s="81" t="s">
+      <c r="C96" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="56"/>
-      <c r="E95" s="56"/>
-      <c r="F95" s="151" t="s">
-        <v>501</v>
-      </c>
-      <c r="G95" s="152"/>
-      <c r="H95" s="19"/>
-      <c r="I95" s="143"/>
-      <c r="J95" s="144"/>
-      <c r="K95" s="20"/>
-    </row>
-    <row r="96" spans="1:11" ht="30" customHeight="1">
-      <c r="A96" s="127"/>
-      <c r="B96" s="92" t="s">
-        <v>291</v>
-      </c>
-      <c r="C96" s="92" t="s">
-        <v>292</v>
-      </c>
-      <c r="D96" s="93" t="s">
-        <v>261</v>
-      </c>
-      <c r="E96" s="94" t="s">
-        <v>346</v>
-      </c>
-      <c r="F96" s="101"/>
-      <c r="G96" s="122"/>
+      <c r="D96" s="56"/>
+      <c r="E96" s="56"/>
+      <c r="F96" s="153" t="s">
+        <v>495</v>
+      </c>
+      <c r="G96" s="154"/>
       <c r="H96" s="19"/>
-      <c r="I96" s="22"/>
-      <c r="J96" s="20"/>
+      <c r="I96" s="146"/>
+      <c r="J96" s="147"/>
       <c r="K96" s="20"/>
     </row>
-    <row r="97" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A97" s="127"/>
+    <row r="97" spans="1:11" ht="30" customHeight="1">
+      <c r="A97" s="129"/>
       <c r="B97" s="92" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C97" s="92" t="s">
-        <v>491</v>
+        <v>289</v>
       </c>
       <c r="D97" s="93" t="s">
-        <v>294</v>
-      </c>
-      <c r="E97" s="92"/>
+        <v>259</v>
+      </c>
+      <c r="E97" s="94" t="s">
+        <v>342</v>
+      </c>
       <c r="F97" s="101"/>
-      <c r="G97" s="108"/>
+      <c r="G97" s="122"/>
       <c r="H97" s="19"/>
       <c r="I97" s="22"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
     </row>
-    <row r="98" spans="1:11" ht="30" customHeight="1">
-      <c r="A98" s="127"/>
+    <row r="98" spans="1:11" ht="26.25" customHeight="1">
+      <c r="A98" s="129"/>
       <c r="B98" s="92" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C98" s="92" t="s">
-        <v>296</v>
+        <v>485</v>
       </c>
       <c r="D98" s="93" t="s">
-        <v>428</v>
+        <v>291</v>
       </c>
       <c r="E98" s="92"/>
       <c r="F98" s="101"/>
@@ -4975,15 +4975,17 @@
       <c r="K98" s="20"/>
     </row>
     <row r="99" spans="1:11" ht="30" customHeight="1">
-      <c r="A99" s="127"/>
+      <c r="A99" s="129"/>
       <c r="B99" s="92" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C99" s="92" t="s">
-        <v>298</v>
-      </c>
-      <c r="D99" s="95"/>
-      <c r="E99" s="97"/>
+        <v>293</v>
+      </c>
+      <c r="D99" s="93" t="s">
+        <v>424</v>
+      </c>
+      <c r="E99" s="92"/>
       <c r="F99" s="101"/>
       <c r="G99" s="108"/>
       <c r="H99" s="19"/>
@@ -4991,18 +4993,16 @@
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
     </row>
-    <row r="100" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A100" s="127"/>
+    <row r="100" spans="1:11" ht="30" customHeight="1">
+      <c r="A100" s="129"/>
       <c r="B100" s="92" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C100" s="92" t="s">
-        <v>495</v>
-      </c>
-      <c r="D100" s="137" t="s">
-        <v>488</v>
-      </c>
-      <c r="E100" s="137"/>
+        <v>295</v>
+      </c>
+      <c r="D100" s="95"/>
+      <c r="E100" s="97"/>
       <c r="F100" s="101"/>
       <c r="G100" s="108"/>
       <c r="H100" s="19"/>
@@ -5010,52 +5010,56 @@
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
     </row>
-    <row r="101" spans="1:11" ht="27" customHeight="1">
-      <c r="A101" s="127"/>
+    <row r="101" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A101" s="129"/>
       <c r="B101" s="92" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C101" s="92" t="s">
-        <v>301</v>
-      </c>
-      <c r="D101" s="140" t="s">
-        <v>147</v>
-      </c>
-      <c r="E101" s="140"/>
-      <c r="F101" s="105"/>
-      <c r="G101" s="92"/>
+        <v>489</v>
+      </c>
+      <c r="D101" s="139" t="s">
+        <v>482</v>
+      </c>
+      <c r="E101" s="139"/>
+      <c r="F101" s="101"/>
+      <c r="G101" s="108"/>
       <c r="H101" s="19"/>
       <c r="I101" s="22"/>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
     </row>
-    <row r="102" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A102" s="127"/>
+    <row r="102" spans="1:11" ht="27" customHeight="1">
+      <c r="A102" s="129"/>
       <c r="B102" s="92" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C102" s="92" t="s">
-        <v>303</v>
-      </c>
-      <c r="D102" s="123" t="s">
-        <v>429</v>
-      </c>
-      <c r="E102" s="123"/>
+        <v>298</v>
+      </c>
+      <c r="D102" s="142" t="s">
+        <v>147</v>
+      </c>
+      <c r="E102" s="142"/>
       <c r="F102" s="105"/>
       <c r="G102" s="92"/>
-      <c r="H102" s="18"/>
+      <c r="H102" s="19"/>
       <c r="I102" s="22"/>
-      <c r="J102" s="22"/>
-      <c r="K102" s="22"/>
-    </row>
-    <row r="103" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A103" s="127"/>
+      <c r="J102" s="20"/>
+      <c r="K102" s="20"/>
+    </row>
+    <row r="103" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A103" s="129"/>
       <c r="B103" s="92" t="s">
-        <v>304</v>
-      </c>
-      <c r="C103" s="95"/>
-      <c r="D103" s="102"/>
-      <c r="E103" s="102"/>
+        <v>299</v>
+      </c>
+      <c r="C103" s="92" t="s">
+        <v>300</v>
+      </c>
+      <c r="D103" s="125" t="s">
+        <v>425</v>
+      </c>
+      <c r="E103" s="125"/>
       <c r="F103" s="105"/>
       <c r="G103" s="92"/>
       <c r="H103" s="18"/>
@@ -5063,46 +5067,46 @@
       <c r="J103" s="22"/>
       <c r="K103" s="22"/>
     </row>
-    <row r="104" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A104" s="127"/>
+    <row r="104" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A104" s="129"/>
       <c r="B104" s="92" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C104" s="95"/>
-      <c r="D104" s="123" t="s">
-        <v>470</v>
-      </c>
-      <c r="E104" s="123"/>
+      <c r="D104" s="102"/>
+      <c r="E104" s="102"/>
       <c r="F104" s="105"/>
-      <c r="G104" s="101"/>
+      <c r="G104" s="92"/>
       <c r="H104" s="18"/>
       <c r="I104" s="22"/>
       <c r="J104" s="22"/>
       <c r="K104" s="22"/>
     </row>
-    <row r="105" spans="1:11" ht="15" customHeight="1">
-      <c r="A105" s="127"/>
-      <c r="B105" s="95"/>
-      <c r="C105" s="92"/>
-      <c r="D105" s="129" t="s">
-        <v>497</v>
-      </c>
-      <c r="E105" s="130"/>
+    <row r="105" spans="1:11" ht="17.25" customHeight="1">
+      <c r="A105" s="129"/>
+      <c r="B105" s="92" t="s">
+        <v>302</v>
+      </c>
+      <c r="C105" s="95"/>
+      <c r="D105" s="125" t="s">
+        <v>466</v>
+      </c>
+      <c r="E105" s="125"/>
       <c r="F105" s="105"/>
-      <c r="G105" s="92"/>
+      <c r="G105" s="101"/>
       <c r="H105" s="18"/>
       <c r="I105" s="22"/>
       <c r="J105" s="22"/>
       <c r="K105" s="22"/>
     </row>
     <row r="106" spans="1:11" ht="15" customHeight="1">
-      <c r="A106" s="127"/>
-      <c r="B106" s="92"/>
+      <c r="A106" s="129"/>
+      <c r="B106" s="95"/>
       <c r="C106" s="92"/>
-      <c r="D106" s="129" t="s">
-        <v>498</v>
-      </c>
-      <c r="E106" s="130"/>
+      <c r="D106" s="131" t="s">
+        <v>491</v>
+      </c>
+      <c r="E106" s="132"/>
       <c r="F106" s="105"/>
       <c r="G106" s="92"/>
       <c r="H106" s="18"/>
@@ -5111,11 +5115,13 @@
       <c r="K106" s="22"/>
     </row>
     <row r="107" spans="1:11" ht="15" customHeight="1">
-      <c r="A107" s="127"/>
-      <c r="B107" s="129" t="s">
-        <v>24</v>
-      </c>
-      <c r="C107" s="130"/>
+      <c r="A107" s="129"/>
+      <c r="B107" s="92"/>
+      <c r="C107" s="92"/>
+      <c r="D107" s="131" t="s">
+        <v>492</v>
+      </c>
+      <c r="E107" s="132"/>
       <c r="F107" s="105"/>
       <c r="G107" s="92"/>
       <c r="H107" s="18"/>
@@ -5123,16 +5129,12 @@
       <c r="J107" s="22"/>
       <c r="K107" s="22"/>
     </row>
-    <row r="108" spans="1:11">
-      <c r="A108" s="127"/>
-      <c r="B108" s="123" t="s">
-        <v>471</v>
-      </c>
-      <c r="C108" s="123"/>
-      <c r="D108" s="129" t="s">
-        <v>469</v>
-      </c>
-      <c r="E108" s="130"/>
+    <row r="108" spans="1:11" ht="15" customHeight="1">
+      <c r="A108" s="129"/>
+      <c r="B108" s="131" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" s="132"/>
       <c r="F108" s="105"/>
       <c r="G108" s="92"/>
       <c r="H108" s="18"/>
@@ -5141,13 +5143,15 @@
       <c r="K108" s="22"/>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" s="127"/>
-      <c r="B109" s="123" t="s">
-        <v>150</v>
-      </c>
-      <c r="C109" s="123"/>
-      <c r="D109" s="95"/>
-      <c r="E109" s="92"/>
+      <c r="A109" s="129"/>
+      <c r="B109" s="125" t="s">
+        <v>467</v>
+      </c>
+      <c r="C109" s="125"/>
+      <c r="D109" s="131" t="s">
+        <v>465</v>
+      </c>
+      <c r="E109" s="132"/>
       <c r="F109" s="105"/>
       <c r="G109" s="92"/>
       <c r="H109" s="18"/>
@@ -5156,30 +5160,28 @@
       <c r="K109" s="22"/>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" s="127"/>
-      <c r="B110" s="128" t="s">
-        <v>96</v>
-      </c>
-      <c r="C110" s="128"/>
-      <c r="D110" s="55"/>
-      <c r="E110" s="23"/>
-      <c r="F110" s="87"/>
-      <c r="G110" s="81"/>
+      <c r="A110" s="129"/>
+      <c r="B110" s="125" t="s">
+        <v>150</v>
+      </c>
+      <c r="C110" s="125"/>
+      <c r="D110" s="95"/>
+      <c r="E110" s="92"/>
+      <c r="F110" s="105"/>
+      <c r="G110" s="92"/>
       <c r="H110" s="18"/>
       <c r="I110" s="22"/>
       <c r="J110" s="22"/>
       <c r="K110" s="22"/>
     </row>
-    <row r="111" spans="1:11" s="17" customFormat="1">
-      <c r="A111" s="127"/>
-      <c r="B111" s="134" t="s">
-        <v>506</v>
-      </c>
-      <c r="C111" s="134"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="76" t="s">
-        <v>430</v>
-      </c>
+    <row r="111" spans="1:11">
+      <c r="A111" s="129"/>
+      <c r="B111" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="C111" s="130"/>
+      <c r="D111" s="55"/>
+      <c r="E111" s="23"/>
       <c r="F111" s="87"/>
       <c r="G111" s="81"/>
       <c r="H111" s="18"/>
@@ -5188,13 +5190,15 @@
       <c r="K111" s="22"/>
     </row>
     <row r="112" spans="1:11" s="17" customFormat="1">
-      <c r="A112" s="127"/>
-      <c r="B112" s="128" t="s">
-        <v>472</v>
-      </c>
-      <c r="C112" s="128"/>
+      <c r="A112" s="129"/>
+      <c r="B112" s="136" t="s">
+        <v>500</v>
+      </c>
+      <c r="C112" s="136"/>
       <c r="D112" s="56"/>
-      <c r="E112" s="76"/>
+      <c r="E112" s="76" t="s">
+        <v>426</v>
+      </c>
       <c r="F112" s="87"/>
       <c r="G112" s="81"/>
       <c r="H112" s="18"/>
@@ -5203,11 +5207,11 @@
       <c r="K112" s="22"/>
     </row>
     <row r="113" spans="1:11" s="17" customFormat="1">
-      <c r="A113" s="127"/>
-      <c r="B113" s="128" t="s">
-        <v>151</v>
-      </c>
-      <c r="C113" s="128"/>
+      <c r="A113" s="129"/>
+      <c r="B113" s="130" t="s">
+        <v>468</v>
+      </c>
+      <c r="C113" s="130"/>
       <c r="D113" s="56"/>
       <c r="E113" s="76"/>
       <c r="F113" s="87"/>
@@ -5217,12 +5221,12 @@
       <c r="J113" s="22"/>
       <c r="K113" s="22"/>
     </row>
-    <row r="114" spans="1:11" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A114" s="127"/>
-      <c r="B114" s="134" t="s">
-        <v>507</v>
-      </c>
-      <c r="C114" s="134"/>
+    <row r="114" spans="1:11" s="17" customFormat="1">
+      <c r="A114" s="129"/>
+      <c r="B114" s="130" t="s">
+        <v>151</v>
+      </c>
+      <c r="C114" s="130"/>
       <c r="D114" s="56"/>
       <c r="E114" s="76"/>
       <c r="F114" s="87"/>
@@ -5232,12 +5236,12 @@
       <c r="J114" s="22"/>
       <c r="K114" s="22"/>
     </row>
-    <row r="115" spans="1:11" s="17" customFormat="1">
-      <c r="A115" s="127"/>
-      <c r="B115" s="128" t="s">
-        <v>97</v>
-      </c>
-      <c r="C115" s="128"/>
+    <row r="115" spans="1:11" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="A115" s="129"/>
+      <c r="B115" s="136" t="s">
+        <v>501</v>
+      </c>
+      <c r="C115" s="136"/>
       <c r="D115" s="56"/>
       <c r="E115" s="76"/>
       <c r="F115" s="87"/>
@@ -5247,656 +5251,664 @@
       <c r="J115" s="22"/>
       <c r="K115" s="22"/>
     </row>
-    <row r="116" spans="1:11">
-      <c r="A116" s="8"/>
-      <c r="B116" s="12"/>
-      <c r="C116" s="12"/>
-      <c r="D116" s="12"/>
-      <c r="E116" s="12"/>
-      <c r="F116" s="9"/>
-      <c r="G116" s="12"/>
-      <c r="H116" s="9"/>
-      <c r="I116" s="9"/>
-      <c r="J116" s="12"/>
-      <c r="K116" s="12"/>
-    </row>
-    <row r="117" spans="1:11" s="21" customFormat="1">
-      <c r="A117" s="27"/>
-      <c r="B117" s="28"/>
-      <c r="C117" s="28"/>
-      <c r="D117" s="28"/>
-      <c r="E117" s="29"/>
-      <c r="F117" s="30"/>
-      <c r="G117" s="29"/>
-      <c r="H117" s="30"/>
-      <c r="I117" s="30"/>
-      <c r="J117" s="29"/>
-      <c r="K117" s="29"/>
-    </row>
-    <row r="118" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
-      <c r="B118" s="48" t="s">
-        <v>347</v>
-      </c>
-      <c r="C118" s="48" t="s">
-        <v>348</v>
-      </c>
-      <c r="E118" s="49" t="s">
-        <v>347</v>
-      </c>
-      <c r="F118" s="49" t="s">
-        <v>348</v>
-      </c>
-      <c r="H118" s="49" t="s">
-        <v>347</v>
-      </c>
-      <c r="I118" s="49" t="s">
-        <v>348</v>
-      </c>
+    <row r="116" spans="1:11" s="17" customFormat="1">
+      <c r="A116" s="129"/>
+      <c r="B116" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="C116" s="130"/>
+      <c r="D116" s="56"/>
+      <c r="E116" s="76"/>
+      <c r="F116" s="87"/>
+      <c r="G116" s="81"/>
+      <c r="H116" s="18"/>
+      <c r="I116" s="22"/>
+      <c r="J116" s="22"/>
+      <c r="K116" s="22"/>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" s="8"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="9"/>
+      <c r="I117" s="9"/>
+      <c r="J117" s="12"/>
+      <c r="K117" s="12"/>
+    </row>
+    <row r="118" spans="1:11" s="21" customFormat="1">
+      <c r="A118" s="27"/>
+      <c r="B118" s="28"/>
+      <c r="C118" s="28"/>
+      <c r="D118" s="28"/>
+      <c r="E118" s="29"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="29"/>
+      <c r="H118" s="30"/>
+      <c r="I118" s="30"/>
+      <c r="J118" s="29"/>
+      <c r="K118" s="29"/>
     </row>
     <row r="119" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
-      <c r="B119" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="C119" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="E119" s="50" t="s">
-        <v>366</v>
-      </c>
-      <c r="F119" s="66" t="s">
-        <v>58</v>
-      </c>
-      <c r="H119" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="I119" s="67" t="s">
-        <v>78</v>
+      <c r="B119" s="48" t="s">
+        <v>343</v>
+      </c>
+      <c r="C119" s="48" t="s">
+        <v>344</v>
+      </c>
+      <c r="E119" s="49" t="s">
+        <v>343</v>
+      </c>
+      <c r="F119" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="H119" s="49" t="s">
+        <v>343</v>
+      </c>
+      <c r="I119" s="49" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="120" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B120" s="55" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C120" s="55" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E120" s="50" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F120" s="66" t="s">
-        <v>368</v>
-      </c>
-      <c r="H120" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="H120" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="I120" s="68" t="s">
-        <v>349</v>
+      <c r="I120" s="67" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="121" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B121" s="55" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C121" s="55" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E121" s="50" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="F121" s="66" t="s">
-        <v>59</v>
+        <v>364</v>
       </c>
       <c r="H121" s="39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I121" s="68" t="s">
-        <v>75</v>
+        <v>345</v>
       </c>
     </row>
     <row r="122" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B122" s="55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C122" s="55" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E122" s="50" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="F122" s="66" t="s">
-        <v>371</v>
+        <v>59</v>
       </c>
       <c r="H122" s="39" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I122" s="68" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B123" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="C123" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="E123" s="50" t="s">
+        <v>366</v>
+      </c>
+      <c r="F123" s="66" t="s">
+        <v>367</v>
+      </c>
+      <c r="H123" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="I123" s="68" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="B124" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="C123" s="55" t="s">
+      <c r="C124" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="E123" s="50" t="s">
+      <c r="E124" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="F123" s="66" t="s">
+      <c r="F124" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="H123" s="51"/>
-      <c r="I123" s="69" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B124" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="C124" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="E124" s="50" t="s">
-        <v>372</v>
-      </c>
-      <c r="F124" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="H124" s="41" t="s">
-        <v>351</v>
-      </c>
-      <c r="I124" s="70" t="s">
-        <v>352</v>
+      <c r="H124" s="51"/>
+      <c r="I124" s="69" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
       <c r="B125" s="55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C125" s="55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E125" s="50" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="F125" s="66" t="s">
-        <v>374</v>
+        <v>62</v>
       </c>
       <c r="H125" s="41" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="I125" s="70" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="126" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
       <c r="B126" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C126" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="E126" s="50" t="s">
+        <v>369</v>
+      </c>
+      <c r="F126" s="66" t="s">
+        <v>370</v>
+      </c>
+      <c r="H126" s="41" t="s">
+        <v>349</v>
+      </c>
+      <c r="I126" s="70" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
+      <c r="B127" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="C126" s="55" t="s">
+      <c r="C127" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="E126" s="50" t="s">
-        <v>375</v>
-      </c>
-      <c r="F126" s="66" t="s">
-        <v>376</v>
-      </c>
-      <c r="H126" s="52"/>
-      <c r="I126" s="71" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
-      <c r="B127" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="C127" s="55" t="s">
-        <v>115</v>
-      </c>
       <c r="E127" s="50" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F127" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="H127" s="53"/>
-      <c r="I127" s="68" t="s">
-        <v>356</v>
+        <v>372</v>
+      </c>
+      <c r="H127" s="52"/>
+      <c r="I127" s="71" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B128" s="55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C128" s="55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E128" s="50" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F128" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="H128" s="40" t="s">
-        <v>357</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="H128" s="53"/>
       <c r="I128" s="68" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="129" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B129" s="55" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C129" s="55" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E129" s="50" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F129" s="66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H129" s="40" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="I129" s="68" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="130" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B130" s="55" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C130" s="55" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E130" s="50" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F130" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H130" s="53"/>
+        <v>65</v>
+      </c>
+      <c r="H130" s="40" t="s">
+        <v>355</v>
+      </c>
       <c r="I130" s="68" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="131" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B131" s="55" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C131" s="55" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E131" s="50" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F131" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="H131" s="54" t="s">
-        <v>362</v>
-      </c>
-      <c r="I131" s="72" t="s">
-        <v>363</v>
+        <v>66</v>
+      </c>
+      <c r="H131" s="53"/>
+      <c r="I131" s="68" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="132" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B132" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C132" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="E132" s="50" t="s">
+        <v>377</v>
+      </c>
+      <c r="F132" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="H132" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="I132" s="72" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
+      <c r="B133" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="C132" s="55" t="s">
+      <c r="C133" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="E132" s="50" t="s">
-        <v>382</v>
-      </c>
-      <c r="F132" s="66" t="s">
+      <c r="E133" s="50" t="s">
+        <v>378</v>
+      </c>
+      <c r="F133" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="H132" s="54" t="s">
-        <v>364</v>
-      </c>
-      <c r="I132" s="72" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="133" spans="2:9">
-      <c r="B133" s="55" t="s">
-        <v>126</v>
-      </c>
-      <c r="C133" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="E133" s="50" t="s">
-        <v>383</v>
-      </c>
-      <c r="F133" s="66" t="s">
-        <v>69</v>
-      </c>
-      <c r="H133" s="55" t="s">
-        <v>403</v>
-      </c>
-      <c r="I133" s="66" t="s">
-        <v>404</v>
+      <c r="H133" s="54" t="s">
+        <v>360</v>
+      </c>
+      <c r="I133" s="72" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="55" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C134" s="55" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E134" s="50" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F134" s="66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H134" s="55" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="I134" s="66" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="55" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C135" s="55" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E135" s="50" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="F135" s="66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H135" s="55" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="I135" s="66" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="55" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C136" s="55" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E136" s="50" t="s">
-        <v>72</v>
+        <v>381</v>
       </c>
       <c r="F136" s="66" t="s">
-        <v>386</v>
-      </c>
-      <c r="H136" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="I136" s="56" t="s">
-        <v>409</v>
+        <v>71</v>
+      </c>
+      <c r="H136" s="55" t="s">
+        <v>403</v>
+      </c>
+      <c r="I136" s="66" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="2:9">
       <c r="B137" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="C137" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="E137" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="F137" s="66" t="s">
+        <v>382</v>
+      </c>
+      <c r="H137" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="I137" s="56" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9">
+      <c r="B138" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="C137" s="55" t="s">
+      <c r="C138" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="E137" s="50" t="s">
-        <v>387</v>
-      </c>
-      <c r="F137" s="66" t="s">
-        <v>388</v>
-      </c>
-      <c r="H137" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I137" s="56" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="138" spans="2:9">
-      <c r="B138" s="58" t="s">
+      <c r="E138" s="50" t="s">
+        <v>383</v>
+      </c>
+      <c r="F138" s="66" t="s">
+        <v>384</v>
+      </c>
+      <c r="H138" s="50" t="s">
+        <v>406</v>
+      </c>
+      <c r="I138" s="56" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9">
+      <c r="B139" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="C138" s="58" t="s">
+      <c r="C139" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="E138" s="55" t="s">
-        <v>389</v>
-      </c>
-      <c r="F138" s="66" t="s">
-        <v>390</v>
-      </c>
-      <c r="H138" s="46" t="s">
+      <c r="E139" s="55" t="s">
+        <v>385</v>
+      </c>
+      <c r="F139" s="66" t="s">
+        <v>386</v>
+      </c>
+      <c r="H139" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="I138" s="73" t="s">
+      <c r="I139" s="73" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="139" spans="2:9">
-      <c r="B139" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="C139" s="75" t="s">
-        <v>43</v>
-      </c>
-      <c r="E139" s="55" t="s">
-        <v>391</v>
-      </c>
-      <c r="F139" s="66" t="s">
-        <v>392</v>
-      </c>
-      <c r="H139" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="I139" s="73" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="140" spans="2:9">
       <c r="B140" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="C140" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="E140" s="55" t="s">
+        <v>387</v>
+      </c>
+      <c r="F140" s="66" t="s">
+        <v>388</v>
+      </c>
+      <c r="H140" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="I140" s="73" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="141" spans="2:9">
+      <c r="B141" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C140" s="75" t="s">
+      <c r="C141" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="E140" s="55" t="s">
+      <c r="E141" s="55" t="s">
+        <v>389</v>
+      </c>
+      <c r="F141" s="66" t="s">
+        <v>390</v>
+      </c>
+      <c r="H141" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="I141" s="73" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="142" spans="2:9">
+      <c r="B142" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C142" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="E142" s="55" t="s">
+        <v>391</v>
+      </c>
+      <c r="F142" s="66" t="s">
+        <v>392</v>
+      </c>
+      <c r="H142" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="I142" s="74" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="143" spans="2:9" ht="25.5" customHeight="1">
+      <c r="B143" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C143" s="75" t="s">
+        <v>49</v>
+      </c>
+      <c r="E143" s="55" t="s">
         <v>393</v>
       </c>
-      <c r="F140" s="66" t="s">
+      <c r="F143" s="66" t="s">
         <v>394</v>
       </c>
-      <c r="H140" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="I140" s="73" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="141" spans="2:9">
-      <c r="B141" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="C141" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="E141" s="55" t="s">
+      <c r="H143" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="I143" s="47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" spans="2:9" ht="39" customHeight="1">
+      <c r="B144" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C144" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="E144" s="55" t="s">
         <v>395</v>
       </c>
-      <c r="F141" s="66" t="s">
+      <c r="F144" s="66" t="s">
         <v>396</v>
       </c>
-      <c r="H141" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="I141" s="74" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="142" spans="2:9" ht="25.5" customHeight="1">
-      <c r="B142" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C142" s="75" t="s">
-        <v>49</v>
-      </c>
-      <c r="E142" s="55" t="s">
+      <c r="H144" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="I144" s="47" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="145" spans="2:9" ht="26.25" customHeight="1">
+      <c r="B145" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C145" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="E145" s="55" t="s">
         <v>397</v>
       </c>
-      <c r="F142" s="66" t="s">
+      <c r="F145" s="66" t="s">
         <v>398</v>
       </c>
-      <c r="H142" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="I142" s="47" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="143" spans="2:9" ht="39" customHeight="1">
-      <c r="B143" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C143" s="73" t="s">
-        <v>51</v>
-      </c>
-      <c r="E143" s="55" t="s">
-        <v>399</v>
-      </c>
-      <c r="F143" s="66" t="s">
-        <v>400</v>
-      </c>
-      <c r="H143" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="I143" s="47" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="144" spans="2:9" ht="26.25" customHeight="1">
-      <c r="B144" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="C144" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="E144" s="55" t="s">
-        <v>401</v>
-      </c>
-      <c r="F144" s="66" t="s">
-        <v>402</v>
-      </c>
-      <c r="H144" s="47" t="s">
+      <c r="H145" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="I144" s="47" t="s">
+      <c r="I145" s="47" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="145" spans="4:9">
-      <c r="H145" s="47" t="s">
+    <row r="146" spans="2:9">
+      <c r="H146" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="I145" s="47" t="s">
+      <c r="I146" s="47" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="146" spans="4:9">
-      <c r="G146" s="25"/>
-      <c r="H146" s="62"/>
-      <c r="I146" s="25"/>
-    </row>
-    <row r="147" spans="4:9">
+    <row r="147" spans="2:9">
       <c r="G147" s="25"/>
       <c r="H147" s="62"/>
       <c r="I147" s="25"/>
     </row>
-    <row r="148" spans="4:9">
+    <row r="148" spans="2:9">
       <c r="G148" s="25"/>
-      <c r="H148" s="25"/>
+      <c r="H148" s="62"/>
       <c r="I148" s="25"/>
     </row>
-    <row r="149" spans="4:9">
+    <row r="149" spans="2:9">
       <c r="G149" s="25"/>
       <c r="H149" s="25"/>
       <c r="I149" s="25"/>
     </row>
-    <row r="150" spans="4:9">
-      <c r="F150" s="43"/>
-      <c r="G150" s="42"/>
+    <row r="150" spans="2:9">
+      <c r="G150" s="25"/>
       <c r="H150" s="25"/>
       <c r="I150" s="25"/>
     </row>
-    <row r="151" spans="4:9">
+    <row r="151" spans="2:9">
       <c r="F151" s="43"/>
       <c r="G151" s="42"/>
       <c r="H151" s="25"/>
       <c r="I151" s="25"/>
     </row>
-    <row r="152" spans="4:9">
+    <row r="152" spans="2:9">
       <c r="F152" s="43"/>
       <c r="G152" s="42"/>
       <c r="H152" s="25"/>
       <c r="I152" s="25"/>
     </row>
-    <row r="153" spans="4:9">
+    <row r="153" spans="2:9">
       <c r="F153" s="43"/>
       <c r="G153" s="42"/>
       <c r="H153" s="25"/>
       <c r="I153" s="25"/>
     </row>
-    <row r="154" spans="4:9">
+    <row r="154" spans="2:9">
       <c r="F154" s="43"/>
       <c r="G154" s="42"/>
       <c r="H154" s="25"/>
       <c r="I154" s="25"/>
     </row>
-    <row r="155" spans="4:9">
+    <row r="155" spans="2:9">
       <c r="F155" s="43"/>
       <c r="G155" s="42"/>
       <c r="H155" s="25"/>
       <c r="I155" s="25"/>
     </row>
-    <row r="156" spans="4:9">
+    <row r="156" spans="2:9">
       <c r="F156" s="43"/>
       <c r="G156" s="42"/>
       <c r="H156" s="25"/>
       <c r="I156" s="25"/>
     </row>
-    <row r="157" spans="4:9">
+    <row r="157" spans="2:9">
       <c r="F157" s="43"/>
       <c r="G157" s="42"/>
       <c r="H157" s="25"/>
       <c r="I157" s="25"/>
     </row>
-    <row r="158" spans="4:9">
-      <c r="F158" s="44"/>
+    <row r="158" spans="2:9">
+      <c r="F158" s="43"/>
       <c r="G158" s="42"/>
       <c r="H158" s="25"/>
-    </row>
-    <row r="159" spans="4:9">
-      <c r="D159" s="57"/>
-      <c r="E159" s="59"/>
+      <c r="I158" s="25"/>
+    </row>
+    <row r="159" spans="2:9">
       <c r="F159" s="44"/>
       <c r="G159" s="42"/>
       <c r="H159" s="25"/>
     </row>
-    <row r="160" spans="4:9">
+    <row r="160" spans="2:9">
       <c r="D160" s="57"/>
-      <c r="E160" s="60"/>
-      <c r="F160" s="38"/>
+      <c r="E160" s="59"/>
+      <c r="F160" s="44"/>
       <c r="G160" s="42"/>
       <c r="H160" s="25"/>
     </row>
@@ -5908,7 +5920,7 @@
       <c r="H161" s="25"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="D162" s="63"/>
+      <c r="D162" s="57"/>
       <c r="E162" s="60"/>
       <c r="F162" s="38"/>
       <c r="G162" s="42"/>
@@ -5943,8 +5955,6 @@
       <c r="H166" s="25"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="B167" s="61"/>
-      <c r="C167" s="59"/>
       <c r="D167" s="63"/>
       <c r="E167" s="60"/>
       <c r="F167" s="38"/>
@@ -5952,11 +5962,10 @@
       <c r="H167" s="25"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="38"/>
-      <c r="B168" s="38"/>
-      <c r="C168" s="38"/>
-      <c r="D168" s="42"/>
-      <c r="E168" s="38"/>
+      <c r="B168" s="61"/>
+      <c r="C168" s="59"/>
+      <c r="D168" s="63"/>
+      <c r="E168" s="60"/>
       <c r="F168" s="38"/>
       <c r="G168" s="42"/>
       <c r="H168" s="25"/>
@@ -5975,7 +5984,7 @@
       <c r="A170" s="38"/>
       <c r="B170" s="38"/>
       <c r="C170" s="38"/>
-      <c r="D170" s="38"/>
+      <c r="D170" s="42"/>
       <c r="E170" s="38"/>
       <c r="F170" s="38"/>
       <c r="G170" s="42"/>
@@ -6000,6 +6009,16 @@
       <c r="F172" s="38"/>
       <c r="G172" s="42"/>
       <c r="H172" s="25"/>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="38"/>
+      <c r="B173" s="38"/>
+      <c r="C173" s="38"/>
+      <c r="D173" s="38"/>
+      <c r="E173" s="38"/>
+      <c r="F173" s="38"/>
+      <c r="G173" s="42"/>
+      <c r="H173" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="116">
@@ -6021,8 +6040,8 @@
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J58:K58"/>
     <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J60:K60"/>
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D20:E20"/>
@@ -6042,83 +6061,83 @@
     <mergeCell ref="F26:F39"/>
     <mergeCell ref="J42:K42"/>
     <mergeCell ref="H39:I39"/>
-    <mergeCell ref="F42:F50"/>
-    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="F42:F51"/>
+    <mergeCell ref="H50:I50"/>
     <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="H70:I70"/>
     <mergeCell ref="H51:I51"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="F58:F68"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H81:I81"/>
     <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="D72:E72"/>
     <mergeCell ref="H82:I82"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="D92:E92"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="F57:F67"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D101:E101"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="D109:E109"/>
     <mergeCell ref="B108:C108"/>
-    <mergeCell ref="D104:E104"/>
-    <mergeCell ref="D108:E108"/>
-    <mergeCell ref="B107:C107"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D91:E91"/>
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
     <mergeCell ref="H42:I42"/>
-    <mergeCell ref="A57:A74"/>
-    <mergeCell ref="A76:A93"/>
-    <mergeCell ref="A95:A115"/>
-    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="A58:A75"/>
+    <mergeCell ref="A77:A94"/>
+    <mergeCell ref="A96:A116"/>
+    <mergeCell ref="B114:C114"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="D73:E73"/>
     <mergeCell ref="D70:E70"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="A42:A56"/>
+    <mergeCell ref="D101:E101"/>
+    <mergeCell ref="B113:C113"/>
     <mergeCell ref="B111:C111"/>
-    <mergeCell ref="A42:A55"/>
-    <mergeCell ref="D100:E100"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="D105:E105"/>
     <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D107:E107"/>
   </mergeCells>
   <pageMargins left="0.24" right="0.17" top="0.17" bottom="0.28000000000000003" header="0.17" footer="0.16"/>
   <pageSetup scale="60" orientation="landscape" r:id="rId1"/>

--- a/raw/time_tables/B.Tech 62 (btech-62)/5/1.xlsx
+++ b/raw/time_tables/B.Tech 62 (btech-62)/5/1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18FB964-7AFF-450D-8582-9FB073937926}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508FB2A6-4CF7-40F9-98AC-E9A3D6F5038B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="510">
   <si>
     <t>8-9AM</t>
   </si>
@@ -278,18 +278,9 @@
     <t>PC1(18BT311)/-BT1/RPS,VGU</t>
   </si>
   <si>
-    <t>PB1(15CS312)-CL15/TNV, SYN</t>
-  </si>
-  <si>
     <t>PB9(15CS312)-CL13/ALK,TNV</t>
   </si>
   <si>
-    <t>PB7(15CS313)-CL06/AST, KA</t>
-  </si>
-  <si>
-    <t>PB8(15CS313)-CLO7/PSO, VIK</t>
-  </si>
-  <si>
     <t>PB5(15CS313)-CL09/KP, MEE</t>
   </si>
   <si>
@@ -299,16 +290,7 @@
     <t>PB10-B14,G1,G2(16CS320)-CL06,07/ASK,TRN</t>
   </si>
   <si>
-    <t>PB5-B9(16CS314)-CL08/SHB,ROH</t>
-  </si>
-  <si>
-    <t>PB1-B4, B10(16CS314)-CL21/IC, SHB</t>
-  </si>
-  <si>
     <t>PB1-B9(16CS319)-CL17,18/APJ, HN</t>
-  </si>
-  <si>
-    <t>PB11-B14(16CS314)-CL06/IC, ROH</t>
   </si>
   <si>
     <t>18B11EC312</t>
@@ -472,12 +454,6 @@
     <t>PB1-B4(16CS318)-CL15/AMS, SJA</t>
   </si>
   <si>
-    <t>PB11-B14(16CS312)-CL07/ KM, MSH</t>
-  </si>
-  <si>
-    <t>PB6(15CS313)-CL10/KA, PSO</t>
-  </si>
-  <si>
     <t>Pminor(24B15CS354)-CL23/ AMS</t>
   </si>
   <si>
@@ -487,9 +463,6 @@
     <t>PB14(15CS314)-CL15/SHO, SON</t>
   </si>
   <si>
-    <t>PB1-B4, B10(16CS312)-CL22/KM, SHV</t>
-  </si>
-  <si>
     <t>PA1(CI578)-CL17/TKT,SRG</t>
   </si>
   <si>
@@ -517,9 +490,6 @@
     <t>LB3,B4(CS313)-G5/KP</t>
   </si>
   <si>
-    <t>LB5,B6(CS313)-CS1/ASK</t>
-  </si>
-  <si>
     <t>LC1,C2,C3 (HS311)- CS3/YN</t>
   </si>
   <si>
@@ -607,9 +577,6 @@
     <t>LB(CS314)-CS3/IC</t>
   </si>
   <si>
-    <t>LB(CS315)-CS4/SMS</t>
-  </si>
-  <si>
     <t>LG1,G2(26B12MA312)-FF6/NF8</t>
   </si>
   <si>
@@ -637,9 +604,6 @@
     <t>LC(26BT314)-FF9/KAR</t>
   </si>
   <si>
-    <t>LB7,B8, B14(CS313)-G2/AST</t>
-  </si>
-  <si>
     <t>LB9,B10(CS312)-G5/PK</t>
   </si>
   <si>
@@ -649,9 +613,6 @@
     <t>LB11,B12(CS312)-CS1/TNV</t>
   </si>
   <si>
-    <t>LB11,B12(CS313)-CS1/AKM</t>
-  </si>
-  <si>
     <t>LG1,G2(26B11MA318)-CS3/MSD</t>
   </si>
   <si>
@@ -718,9 +679,6 @@
     <t>LC(26BT313)-CR425/ANM</t>
   </si>
   <si>
-    <t>LB5,B6(CS313)-CS4/ASK</t>
-  </si>
-  <si>
     <t>LA15-A16(24B21EC312)-CS1/MJ</t>
   </si>
   <si>
@@ -781,9 +739,6 @@
     <t>LB(PH531)-CS2/ANU</t>
   </si>
   <si>
-    <t>LA15,A16(HS311)-CS1 /NAM</t>
-  </si>
-  <si>
     <t>LA17-A18(24B31EC311)-CS3/ABU</t>
   </si>
   <si>
@@ -802,9 +757,6 @@
     <t>LA1,A2(HS311)- G2/NAM</t>
   </si>
   <si>
-    <t>LB11,B12(CS313)-G5/AKM</t>
-  </si>
-  <si>
     <t>LG1,G2(26B11MA318)-G5/MSD</t>
   </si>
   <si>
@@ -949,9 +901,6 @@
     <t>TC1 (BT413)- TS12/ASM,AKV</t>
   </si>
   <si>
-    <t>TB7(CS313)-TS17/KP</t>
-  </si>
-  <si>
     <t>TA7(CI518)-F10/AJP</t>
   </si>
   <si>
@@ -970,9 +919,6 @@
     <t>TB3(CS313)-TS12/AMK</t>
   </si>
   <si>
-    <t>TB4(CS313)-TS17/AKM</t>
-  </si>
-  <si>
     <t>TC3(BT311)- TS12/VGU,SBT</t>
   </si>
   <si>
@@ -982,15 +928,6 @@
     <t>TA2(CI518)-TS17/AJP</t>
   </si>
   <si>
-    <t>TB11(CS313)-TS12/AMK</t>
-  </si>
-  <si>
-    <t>TB9(CS313)-F10/AKM</t>
-  </si>
-  <si>
-    <t>TG1(26B11MA318)-F10/MSD</t>
-  </si>
-  <si>
     <t>TC2 (BT413)- TS12/ASM,AKV</t>
   </si>
   <si>
@@ -1000,9 +937,6 @@
     <t>TA5(EC312)-/S17/AGT</t>
   </si>
   <si>
-    <t>TB2(CS313)-TS12/AST</t>
-  </si>
-  <si>
     <t>TA6(EC312)-TS12/MO</t>
   </si>
   <si>
@@ -1267,15 +1201,9 @@
     <t>Lunch</t>
   </si>
   <si>
-    <t>PB5-B9(16CS312)-CL17/MSH, SHV</t>
-  </si>
-  <si>
     <t>TA4(CI518)-F7/APJ</t>
   </si>
   <si>
-    <t>TB8(CS313)-F7/AST</t>
-  </si>
-  <si>
     <t>LA7, A8, A10(CI518)-LT3/AJP</t>
   </si>
   <si>
@@ -1312,15 +1240,6 @@
     <t>LA1, A2(CI518)-CR301/TKT</t>
   </si>
   <si>
-    <t>PB10-B14,G1,G2(16CS319)-CL04/APJ, HN,JAT</t>
-  </si>
-  <si>
-    <t>PB1-B9(16CS311)-CL10,11/AKM,AVR,JAG</t>
-  </si>
-  <si>
-    <t>PB1-B9(16CS313)-CL13,14,15/RCA, SYN,DPA</t>
-  </si>
-  <si>
     <t>PB9,B10(15CS314)-CL18,19/PKU, DEV,SON</t>
   </si>
   <si>
@@ -1351,9 +1270,6 @@
     <t>PG1(15CS314)-CL15/DPA,DEV</t>
   </si>
   <si>
-    <t>PB9,B11(15CS313)-CL10,11/ AST, AMK,VIK</t>
-  </si>
-  <si>
     <t>LB(CS318)-CS1/AMS</t>
   </si>
   <si>
@@ -1372,12 +1288,6 @@
     <t>LA3, A4(CI518)-G6/SHP</t>
   </si>
   <si>
-    <t>PA3,A4(CI578)-CL13,14/AJP,AW,TRN</t>
-  </si>
-  <si>
-    <t>PB1,B2(15CS313)-CL09,10/MEE,AKM,ASK</t>
-  </si>
-  <si>
     <t>PA2(CI578)-CL19/APJ, POS</t>
   </si>
   <si>
@@ -1393,24 +1303,12 @@
     <t>LB7,B8,B14(CS312)-G2/GAS</t>
   </si>
   <si>
-    <t>PB10,B14(15CS313)-CL09,10/KA, AKM,KM</t>
-  </si>
-  <si>
     <t>PB3,B4(15CS314)-CL19,20/PRK, ASH,SON</t>
   </si>
   <si>
     <t>PB1(15CS314)-CL15/PKU, ANB</t>
   </si>
   <si>
-    <t>PA18(CI578)-CL18/SRG, POS</t>
-  </si>
-  <si>
-    <t>PA8(CI578)-CL18/SRG,TRN</t>
-  </si>
-  <si>
-    <t>PA10(CI578)-CL19/AJP, JAT</t>
-  </si>
-  <si>
     <t>PB5(15CS314)-CL06/DPA</t>
   </si>
   <si>
@@ -1423,27 +1321,18 @@
     <t>PB1-B9(16CS317)-CL13,14/AMT,PRV,KRL</t>
   </si>
   <si>
-    <t>PB10-B14(16CS311)-CL21/AKM,AVR,JAG</t>
-  </si>
-  <si>
     <t>Lminor(24B11CS351)-CS3/ NEH</t>
   </si>
   <si>
     <t>Lminor(24B11CS351)-CS1/ NEH</t>
   </si>
   <si>
-    <t>Pminor(24B15CS352)-CL22/ MON</t>
-  </si>
-  <si>
     <t>TA3(CI518)-TR305/APJ</t>
   </si>
   <si>
     <t>LA17, A18(CI518)-FF5/TRN</t>
   </si>
   <si>
-    <t>LB5,B6(CS313)-G9/ASK</t>
-  </si>
-  <si>
     <t>TB5(CS313)-TR307/ASK</t>
   </si>
   <si>
@@ -1504,9 +1393,6 @@
     <t>PA5,A6(CI578)-CL18,19AJP,APJ</t>
   </si>
   <si>
-    <t>Pminor(24B15CS352)-CL21/ MON</t>
-  </si>
-  <si>
     <t>PB10(15CS312)-CL09/TNV</t>
   </si>
   <si>
@@ -1516,24 +1402,9 @@
     <t>TB10(CS313)-TR302/MEE</t>
   </si>
   <si>
-    <t>PB1-B9(16CS315)-CL18/AMK,SMS</t>
-  </si>
-  <si>
     <t>PB1-B9(16CS320)-CL02,03/ASK,TRN</t>
   </si>
   <si>
-    <t>PB10-B14(16CS315)-CL19,20/AMK,SMS</t>
-  </si>
-  <si>
-    <t>PB14(15CS312)-CL22/ UMF</t>
-  </si>
-  <si>
-    <t>PB11,12(15CS312)-CL13,14/JAG,PK,SOS</t>
-  </si>
-  <si>
-    <t>TG2(26B11MA318)-TS17/MSD</t>
-  </si>
-  <si>
     <t>LABC(17B1NMA531)-CS2/NF5</t>
   </si>
   <si>
@@ -1549,7 +1420,145 @@
     <t>LAC(16B1NMA531)-FF7/NF2</t>
   </si>
   <si>
+    <t>Pminor(24B15CS352)-CL23/ MON</t>
+  </si>
+  <si>
+    <t>PB10-B14(16CS312)-CL07/ KM, MSH</t>
+  </si>
+  <si>
+    <t>TB7(CS313)-TR302/KP</t>
+  </si>
+  <si>
+    <t>PB10-B14(16CS311)-CL21/,AVR,JAG</t>
+  </si>
+  <si>
+    <t>PB10,B14(15CS313)-CL09,10/KA,KM</t>
+  </si>
+  <si>
+    <t>PB1-B9(16CS311)-CL10,11/AVR,JAG</t>
+  </si>
+  <si>
+    <t>TB8(CS313)-F7/AMK</t>
+  </si>
+  <si>
+    <t>LB11,B12(CS313)-CS1/AST</t>
+  </si>
+  <si>
+    <t>TB4(CS313)-TR302/JAG</t>
+  </si>
+  <si>
+    <t>TB9(CS313)-TR302/JAG</t>
+  </si>
+  <si>
+    <t>PB5-B9(16CS312)-CL17/MSH</t>
+  </si>
+  <si>
+    <t>PB1-B4(16CS312)-CL22/KM</t>
+  </si>
+  <si>
+    <t>PB6(15CS313)-CL10/KA</t>
+  </si>
+  <si>
+    <t>PB8(15CS313)-CL07/ KA</t>
+  </si>
+  <si>
+    <t>Pminor(24B15CS352)-CL22/ AM</t>
+  </si>
+  <si>
+    <t>PB1-B9(16CS313)-CL13,14,15/RSS, SYN,DPA</t>
+  </si>
+  <si>
+    <t>PA3,A4(CI578)-CL13,14/AJP,TRN</t>
+  </si>
+  <si>
+    <t>PB5-B9(16CS314)-CL08/IC</t>
+  </si>
+  <si>
+    <t>PB1-B4(16CS314)-CL21/IC</t>
+  </si>
+  <si>
+    <t>PB10-B14(16CS314)-CL06/IC</t>
+  </si>
+  <si>
+    <t>PB10-B14(16CS315)-CL19/AMK</t>
+  </si>
+  <si>
+    <t>LB(CS315)-CS4/VIK</t>
+  </si>
+  <si>
+    <t>PB1-B9(16CS315)-CL18,19/AMK,VIK</t>
+  </si>
+  <si>
+    <t>PB11,12(15CS312)-CL13,14/PK,SOS,KRR</t>
+  </si>
+  <si>
+    <t>LB5,B6(CS313)-CS1/AST</t>
+  </si>
+  <si>
+    <t>LB5,B6(CS313)-FF6/AST</t>
+  </si>
+  <si>
+    <t>LB11,B12(CS313)-CR301/AST</t>
+  </si>
+  <si>
+    <t>LB5,B6(CS313)-CR301/AST</t>
+  </si>
+  <si>
+    <t>LB7,B8, B14(CS313)-G2/ASK</t>
+  </si>
+  <si>
+    <t>LB7,B8, B14(CS313)-FF6/ASK</t>
+  </si>
+  <si>
+    <t>PB7(15CS313)-CL06/ASK</t>
+  </si>
+  <si>
+    <t>PB1,B2(15CS313)-CL09,10/MEE,AST</t>
+  </si>
+  <si>
+    <t>PB1,B14(15CS312)-CL22,23/ TNV,SYN,UMF</t>
+  </si>
+  <si>
+    <t>TB2(CS313)-TR326/MEE</t>
+  </si>
+  <si>
+    <t>TB11(CS313)-TR326/AMK</t>
+  </si>
+  <si>
+    <t>PB10-B14,G1,G2(16CS319)-CL04/APJ, HN</t>
+  </si>
+  <si>
+    <t>PB9,B11(15CS313)-CL18,19/ AST, AMK</t>
+  </si>
+  <si>
     <t>TA6(CI518)-TR326/TKT</t>
+  </si>
+  <si>
+    <t>TG1(26B11MA318)-TR305/MSD</t>
+  </si>
+  <si>
+    <t>TG2(26B11MA318)-F10/MSD</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PA18(CI578)-CL18/SRG, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>JAT</t>
+    </r>
+  </si>
+  <si>
+    <t>PA8,A10(CI578)-CL18,19/TRN,AJP,POS</t>
+  </si>
+  <si>
+    <t>LA15,A16(HS311)-F8 /NAM</t>
   </si>
 </sst>
 </file>
@@ -2071,7 +2080,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2325,9 +2334,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2367,9 +2373,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2416,17 +2419,176 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
@@ -2434,137 +2596,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -2928,19 +2967,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33" customHeight="1">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="167"/>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="167"/>
-      <c r="K1" s="168"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="136"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1"/>
@@ -3002,350 +3041,343 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="32.25" customHeight="1">
-      <c r="A5" s="160" t="s">
+      <c r="A5" s="152" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="125" t="s">
+      <c r="B5" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="92" t="s">
-        <v>428</v>
-      </c>
-      <c r="E5" s="92" t="s">
+      <c r="C5" s="143"/>
+      <c r="D5" s="123" t="s">
+        <v>404</v>
+      </c>
+      <c r="E5" s="123" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="140" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="123" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="123" t="s">
+        <v>408</v>
+      </c>
+      <c r="I5" s="123" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" s="143" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="143"/>
+    </row>
+    <row r="6" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A6" s="153"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="123" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="123" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="141"/>
+      <c r="G6" s="123" t="s">
+        <v>161</v>
+      </c>
+      <c r="H6" s="123" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="170" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="92" t="s">
+      <c r="I6" s="123" t="s">
+        <v>456</v>
+      </c>
+      <c r="J6" s="123" t="s">
+        <v>171</v>
+      </c>
+      <c r="K6" s="123"/>
+    </row>
+    <row r="7" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A7" s="153"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="126" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="123" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="141"/>
+      <c r="G7" s="123" t="s">
+        <v>162</v>
+      </c>
+      <c r="H7" s="123" t="s">
+        <v>165</v>
+      </c>
+      <c r="I7" s="123" t="s">
+        <v>168</v>
+      </c>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+    </row>
+    <row r="8" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A8" s="153"/>
+      <c r="B8" s="144" t="s">
+        <v>477</v>
+      </c>
+      <c r="C8" s="144"/>
+      <c r="D8" s="123" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="123" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" s="141"/>
+      <c r="G8" s="92" t="s">
+        <v>163</v>
+      </c>
+      <c r="H8" s="92" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="123" t="s">
+        <v>169</v>
+      </c>
+      <c r="J8" s="123"/>
+      <c r="K8" s="123"/>
+    </row>
+    <row r="9" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A9" s="153"/>
+      <c r="B9" s="143" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="143"/>
+      <c r="D9" s="123" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="92" t="s">
+        <v>443</v>
+      </c>
+      <c r="F9" s="141"/>
+      <c r="G9" s="130" t="s">
+        <v>492</v>
+      </c>
+      <c r="H9" s="128" t="s">
+        <v>298</v>
+      </c>
+      <c r="I9" s="123" t="s">
         <v>170</v>
       </c>
-      <c r="H5" s="92" t="s">
+      <c r="J9" s="123"/>
+      <c r="K9" s="123"/>
+    </row>
+    <row r="10" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A10" s="153"/>
+      <c r="B10" s="143" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10" s="143"/>
+      <c r="D10" s="123" t="s">
+        <v>403</v>
+      </c>
+      <c r="E10" s="92" t="s">
+        <v>287</v>
+      </c>
+      <c r="F10" s="141"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="128" t="s">
+        <v>308</v>
+      </c>
+      <c r="I10" s="128" t="s">
+        <v>299</v>
+      </c>
+      <c r="J10" s="123"/>
+      <c r="K10" s="123"/>
+    </row>
+    <row r="11" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A11" s="153"/>
+      <c r="B11" s="144" t="s">
+        <v>502</v>
+      </c>
+      <c r="C11" s="144"/>
+      <c r="D11" s="123" t="s">
+        <v>388</v>
+      </c>
+      <c r="E11" s="128" t="s">
+        <v>295</v>
+      </c>
+      <c r="F11" s="141"/>
+      <c r="G11" s="143" t="s">
+        <v>409</v>
+      </c>
+      <c r="H11" s="143"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="123"/>
+    </row>
+    <row r="12" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A12" s="153"/>
+      <c r="B12" s="143" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="143"/>
+      <c r="D12" s="128" t="s">
+        <v>293</v>
+      </c>
+      <c r="E12" s="128" t="s">
+        <v>296</v>
+      </c>
+      <c r="F12" s="141"/>
+      <c r="G12" s="155" t="s">
+        <v>410</v>
+      </c>
+      <c r="H12" s="156"/>
+      <c r="I12" s="145" t="s">
+        <v>134</v>
+      </c>
+      <c r="J12" s="146"/>
+      <c r="K12" s="123"/>
+    </row>
+    <row r="13" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A13" s="153"/>
+      <c r="B13" s="144" t="s">
+        <v>472</v>
+      </c>
+      <c r="C13" s="143"/>
+      <c r="E13" s="128" t="s">
+        <v>297</v>
+      </c>
+      <c r="F13" s="141"/>
+      <c r="G13" s="145" t="s">
+        <v>439</v>
+      </c>
+      <c r="H13" s="146"/>
+      <c r="I13" s="145" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="146"/>
+      <c r="K13" s="123"/>
+    </row>
+    <row r="14" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A14" s="153"/>
+      <c r="B14" s="144" t="s">
+        <v>482</v>
+      </c>
+      <c r="C14" s="144"/>
+      <c r="D14" s="128" t="s">
+        <v>294</v>
+      </c>
+      <c r="E14" s="128" t="s">
+        <v>405</v>
+      </c>
+      <c r="F14" s="141"/>
+      <c r="G14" s="155" t="s">
+        <v>411</v>
+      </c>
+      <c r="H14" s="156"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="123"/>
+      <c r="K14" s="123"/>
+    </row>
+    <row r="15" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A15" s="153"/>
+      <c r="B15" s="144" t="s">
+        <v>489</v>
+      </c>
+      <c r="C15" s="144"/>
+      <c r="D15" s="155" t="s">
+        <v>407</v>
+      </c>
+      <c r="E15" s="156"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="155"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="124"/>
+      <c r="J15" s="123"/>
+      <c r="K15" s="123"/>
+    </row>
+    <row r="16" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A16" s="153"/>
+      <c r="B16" s="144" t="s">
+        <v>484</v>
+      </c>
+      <c r="C16" s="144"/>
+      <c r="D16" s="144" t="s">
+        <v>480</v>
+      </c>
+      <c r="E16" s="144"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="143" t="s">
+        <v>412</v>
+      </c>
+      <c r="I16" s="143"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+    </row>
+    <row r="17" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A17" s="153"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="156"/>
+      <c r="F17" s="127" t="s">
         <v>435</v>
       </c>
-      <c r="I5" s="92" t="s">
-        <v>177</v>
-      </c>
-      <c r="J5" s="125" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="125"/>
-    </row>
-    <row r="6" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A6" s="161"/>
-      <c r="B6" s="92"/>
-      <c r="C6" s="92" t="s">
+      <c r="G17" s="97"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+    </row>
+    <row r="18" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A18" s="153"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="147" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" s="147"/>
+      <c r="F18" s="127" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="92" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="92" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="158"/>
-      <c r="G6" s="92" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" s="92" t="s">
-        <v>174</v>
-      </c>
-      <c r="I6" s="106" t="s">
-        <v>493</v>
-      </c>
-      <c r="J6" s="92" t="s">
-        <v>181</v>
-      </c>
-      <c r="K6" s="92"/>
-    </row>
-    <row r="7" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A7" s="161"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="96" t="s">
+      <c r="G18" s="143" t="s">
+        <v>457</v>
+      </c>
+      <c r="H18" s="143"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="123"/>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1">
+      <c r="A19" s="153"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="144" t="s">
+        <v>490</v>
+      </c>
+      <c r="E19" s="144"/>
+      <c r="F19" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="D7" s="92" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="92" t="s">
-        <v>166</v>
-      </c>
-      <c r="F7" s="158"/>
-      <c r="G7" s="92" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="92" t="s">
-        <v>175</v>
-      </c>
-      <c r="I7" s="92" t="s">
-        <v>178</v>
-      </c>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-    </row>
-    <row r="8" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A8" s="161"/>
-      <c r="B8" s="125" t="s">
-        <v>416</v>
-      </c>
-      <c r="C8" s="125"/>
-      <c r="D8" s="92" t="s">
-        <v>162</v>
-      </c>
-      <c r="E8" s="92" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8" s="158"/>
-      <c r="G8" s="93" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="I8" s="92" t="s">
-        <v>179</v>
-      </c>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-    </row>
-    <row r="9" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A9" s="161"/>
-      <c r="B9" s="125" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="125"/>
-      <c r="D9" s="92" t="s">
-        <v>163</v>
-      </c>
-      <c r="E9" s="93" t="s">
-        <v>480</v>
-      </c>
-      <c r="F9" s="158"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="94" t="s">
-        <v>315</v>
-      </c>
-      <c r="I9" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
-    </row>
-    <row r="10" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A10" s="161"/>
-      <c r="B10" s="125" t="s">
-        <v>409</v>
-      </c>
-      <c r="C10" s="125"/>
-      <c r="D10" s="92" t="s">
-        <v>427</v>
-      </c>
-      <c r="E10" s="93" t="s">
-        <v>303</v>
-      </c>
-      <c r="F10" s="158"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="94" t="s">
-        <v>330</v>
-      </c>
-      <c r="I10" s="94" t="s">
-        <v>316</v>
-      </c>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
-    </row>
-    <row r="11" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A11" s="161"/>
-      <c r="B11" s="125" t="s">
-        <v>431</v>
-      </c>
-      <c r="C11" s="125"/>
-      <c r="D11" s="92" t="s">
-        <v>410</v>
-      </c>
-      <c r="E11" s="94" t="s">
-        <v>312</v>
-      </c>
-      <c r="F11" s="158"/>
-      <c r="G11" s="125" t="s">
-        <v>436</v>
-      </c>
-      <c r="H11" s="125"/>
-      <c r="I11" s="94" t="s">
-        <v>317</v>
-      </c>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
-    </row>
-    <row r="12" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A12" s="161"/>
-      <c r="B12" s="125" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="94" t="s">
-        <v>309</v>
-      </c>
-      <c r="E12" s="94" t="s">
-        <v>313</v>
-      </c>
-      <c r="F12" s="158"/>
-      <c r="G12" s="131" t="s">
-        <v>437</v>
-      </c>
-      <c r="H12" s="132"/>
-      <c r="I12" s="171" t="s">
-        <v>140</v>
-      </c>
-      <c r="J12" s="172"/>
-      <c r="K12" s="92"/>
-    </row>
-    <row r="13" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A13" s="161"/>
-      <c r="B13" s="125" t="s">
-        <v>432</v>
-      </c>
-      <c r="C13" s="125"/>
-      <c r="D13" s="94" t="s">
-        <v>310</v>
-      </c>
-      <c r="E13" s="94" t="s">
-        <v>314</v>
-      </c>
-      <c r="F13" s="158"/>
-      <c r="G13" s="171" t="s">
-        <v>476</v>
-      </c>
-      <c r="H13" s="172"/>
-      <c r="I13" s="171" t="s">
-        <v>139</v>
-      </c>
-      <c r="J13" s="172"/>
-      <c r="K13" s="92"/>
-    </row>
-    <row r="14" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A14" s="161"/>
-      <c r="B14" s="125" t="s">
-        <v>433</v>
-      </c>
-      <c r="C14" s="125"/>
-      <c r="D14" s="94" t="s">
-        <v>311</v>
-      </c>
-      <c r="E14" s="94" t="s">
-        <v>429</v>
-      </c>
-      <c r="F14" s="158"/>
-      <c r="G14" s="131" t="s">
-        <v>438</v>
-      </c>
-      <c r="H14" s="132"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="92"/>
-    </row>
-    <row r="15" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A15" s="161"/>
-      <c r="B15" s="133" t="s">
-        <v>499</v>
-      </c>
-      <c r="C15" s="133"/>
-      <c r="D15" s="131" t="s">
-        <v>434</v>
-      </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="158"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="92"/>
-    </row>
-    <row r="16" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A16" s="161"/>
-      <c r="B16" s="125" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="125"/>
-      <c r="D16" s="125" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="125"/>
-      <c r="F16" s="159"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="125" t="s">
-        <v>439</v>
-      </c>
-      <c r="I16" s="125"/>
-      <c r="J16" s="92"/>
-      <c r="K16" s="92"/>
-    </row>
-    <row r="17" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A17" s="161"/>
-      <c r="B17" s="98"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="99" t="s">
-        <v>470</v>
-      </c>
-      <c r="G17" s="98"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="125"/>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-    </row>
-    <row r="18" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A18" s="161"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="142" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" s="142"/>
-      <c r="F18" s="99" t="s">
-        <v>168</v>
-      </c>
-      <c r="G18" s="133" t="s">
-        <v>494</v>
-      </c>
-      <c r="H18" s="133"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
-    </row>
-    <row r="19" spans="1:11" ht="30" customHeight="1">
-      <c r="A19" s="161"/>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="133" t="s">
-        <v>503</v>
-      </c>
-      <c r="E19" s="133"/>
-      <c r="F19" s="99" t="s">
-        <v>169</v>
-      </c>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="92"/>
-      <c r="K19" s="92"/>
+      <c r="G19" s="143"/>
+      <c r="H19" s="143"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="123"/>
     </row>
     <row r="20" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A20" s="162"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="125" t="s">
-        <v>89</v>
-      </c>
-      <c r="E20" s="125"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="102"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
+      <c r="A20" s="154"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="144" t="s">
+        <v>497</v>
+      </c>
+      <c r="E20" s="144"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
     </row>
     <row r="21" spans="1:11" ht="10.5" customHeight="1">
       <c r="A21" s="7"/>
@@ -3361,412 +3393,401 @@
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A22" s="126" t="s">
+      <c r="A22" s="137" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="92" t="s">
+      <c r="C22" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="94" t="s">
-        <v>414</v>
-      </c>
-      <c r="G22" s="92" t="s">
-        <v>164</v>
-      </c>
-      <c r="H22" s="92" t="s">
-        <v>435</v>
-      </c>
-      <c r="I22" s="92" t="s">
-        <v>217</v>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="93" t="s">
+        <v>392</v>
+      </c>
+      <c r="G22" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="H22" s="91" t="s">
+        <v>408</v>
+      </c>
+      <c r="I22" s="91" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
-      <c r="A23" s="127"/>
+      <c r="A23" s="138"/>
       <c r="B23" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="92" t="s">
+      <c r="C23" s="91" t="s">
+        <v>182</v>
+      </c>
+      <c r="D23" s="91" t="s">
+        <v>413</v>
+      </c>
+      <c r="E23" s="129" t="s">
+        <v>495</v>
+      </c>
+      <c r="F23" s="98" t="s">
+        <v>201</v>
+      </c>
+      <c r="G23" s="91" t="s">
+        <v>156</v>
+      </c>
+      <c r="H23" s="91" t="s">
+        <v>164</v>
+      </c>
+      <c r="I23" s="91" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" customHeight="1">
+      <c r="A24" s="138"/>
+      <c r="B24" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="C24" s="91" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="91" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" s="91" t="s">
+        <v>196</v>
+      </c>
+      <c r="F24" s="98" t="s">
+        <v>434</v>
+      </c>
+      <c r="G24" s="132" t="s">
+        <v>197</v>
+      </c>
+      <c r="H24" s="132" t="s">
+        <v>152</v>
+      </c>
+      <c r="J24" s="104" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="106"/>
+    </row>
+    <row r="25" spans="1:11" ht="30" customHeight="1">
+      <c r="A25" s="138"/>
+      <c r="B25" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="91" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" s="122" t="s">
+        <v>474</v>
+      </c>
+      <c r="F25" s="98" t="s">
+        <v>202</v>
+      </c>
+      <c r="G25" s="91" t="s">
+        <v>157</v>
+      </c>
+      <c r="H25" s="93" t="s">
+        <v>440</v>
+      </c>
+      <c r="I25" s="91" t="s">
+        <v>206</v>
+      </c>
+      <c r="J25" s="107"/>
+      <c r="K25" s="106"/>
+    </row>
+    <row r="26" spans="1:11" s="17" customFormat="1" ht="30" customHeight="1">
+      <c r="A26" s="138"/>
+      <c r="B26" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C26" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="91" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="91" t="s">
+        <v>199</v>
+      </c>
+      <c r="F26" s="158" t="s">
+        <v>393</v>
+      </c>
+      <c r="G26" s="91" t="s">
+        <v>203</v>
+      </c>
+      <c r="I26" s="91" t="s">
+        <v>207</v>
+      </c>
+      <c r="J26" s="107"/>
+      <c r="K26" s="106"/>
+    </row>
+    <row r="27" spans="1:11" s="17" customFormat="1" ht="30" customHeight="1">
+      <c r="A27" s="138"/>
+      <c r="B27" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="129" t="s">
+        <v>488</v>
+      </c>
+      <c r="D27" s="93" t="s">
+        <v>399</v>
+      </c>
+      <c r="E27" s="93" t="s">
+        <v>200</v>
+      </c>
+      <c r="F27" s="159"/>
+      <c r="G27" s="91" t="s">
+        <v>269</v>
+      </c>
+      <c r="H27" s="105" t="s">
+        <v>500</v>
+      </c>
+      <c r="I27" s="105" t="s">
+        <v>394</v>
+      </c>
+      <c r="J27" s="107"/>
+      <c r="K27" s="106"/>
+    </row>
+    <row r="28" spans="1:11" ht="30" customHeight="1">
+      <c r="A28" s="138"/>
+      <c r="B28" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="91" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="91" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="91" t="s">
+        <v>288</v>
+      </c>
+      <c r="F28" s="159"/>
+      <c r="G28" s="91" t="s">
+        <v>290</v>
+      </c>
+      <c r="H28" s="93" t="s">
+        <v>438</v>
+      </c>
+      <c r="J28" s="107"/>
+      <c r="K28" s="106"/>
+    </row>
+    <row r="29" spans="1:11" ht="30" customHeight="1">
+      <c r="A29" s="138"/>
+      <c r="B29" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" s="91" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" s="92" t="s">
+        <v>398</v>
+      </c>
+      <c r="E29" s="93" t="s">
+        <v>300</v>
+      </c>
+      <c r="F29" s="159"/>
+      <c r="H29" s="97"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="107"/>
+      <c r="K29" s="106"/>
+    </row>
+    <row r="30" spans="1:11" ht="30" customHeight="1">
+      <c r="A30" s="138"/>
+      <c r="B30" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="91" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="105" t="s">
+        <v>501</v>
+      </c>
+      <c r="E30" s="93" t="s">
+        <v>302</v>
+      </c>
+      <c r="F30" s="159"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="94"/>
+      <c r="J30" s="107"/>
+      <c r="K30" s="106"/>
+    </row>
+    <row r="31" spans="1:11" ht="30" customHeight="1">
+      <c r="A31" s="138"/>
+      <c r="B31" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="91" t="s">
         <v>192</v>
       </c>
-      <c r="D23" s="92" t="s">
-        <v>440</v>
-      </c>
-      <c r="E23" s="92" t="s">
-        <v>206</v>
-      </c>
-      <c r="F23" s="99" t="s">
-        <v>214</v>
-      </c>
-      <c r="G23" s="92" t="s">
-        <v>165</v>
-      </c>
-      <c r="H23" s="92" t="s">
-        <v>174</v>
-      </c>
-      <c r="I23" s="92" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="30" customHeight="1">
-      <c r="A24" s="127"/>
-      <c r="B24" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="C24" s="92" t="s">
+      <c r="D31" s="93" t="s">
+        <v>441</v>
+      </c>
+      <c r="F31" s="159"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="144" t="s">
+        <v>458</v>
+      </c>
+      <c r="I31" s="144"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="106"/>
+    </row>
+    <row r="32" spans="1:11" ht="30" customHeight="1">
+      <c r="A32" s="138"/>
+      <c r="B32" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="91" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="108" t="s">
+        <v>301</v>
+      </c>
+      <c r="E32" s="97"/>
+      <c r="F32" s="159"/>
+      <c r="G32" s="147" t="s">
+        <v>137</v>
+      </c>
+      <c r="H32" s="147"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="107"/>
+      <c r="K32" s="106"/>
+    </row>
+    <row r="33" spans="1:11" ht="30" customHeight="1">
+      <c r="A33" s="138"/>
+      <c r="B33" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="91" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>436</v>
+      </c>
+      <c r="E33" s="97"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="147" t="s">
+        <v>136</v>
+      </c>
+      <c r="H33" s="147"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="107"/>
+      <c r="K33" s="106"/>
+    </row>
+    <row r="34" spans="1:11" ht="27" customHeight="1">
+      <c r="A34" s="138"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="91" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="147" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="147"/>
+      <c r="F34" s="159"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="107"/>
+      <c r="K34" s="106"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="138"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="91" t="s">
         <v>193</v>
       </c>
-      <c r="D24" s="92" t="s">
-        <v>207</v>
-      </c>
-      <c r="E24" s="92" t="s">
-        <v>208</v>
-      </c>
-      <c r="F24" s="99" t="s">
-        <v>469</v>
-      </c>
-      <c r="G24" s="102"/>
-      <c r="I24" s="92" t="s">
-        <v>161</v>
-      </c>
-      <c r="J24" s="105" t="s">
-        <v>181</v>
-      </c>
-      <c r="K24" s="108"/>
-    </row>
-    <row r="25" spans="1:11" ht="30" customHeight="1">
-      <c r="A25" s="127"/>
-      <c r="B25" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" s="92" t="s">
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="159"/>
+      <c r="G35" s="157" t="s">
+        <v>142</v>
+      </c>
+      <c r="H35" s="157"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="107"/>
+      <c r="K35" s="106"/>
+    </row>
+    <row r="36" spans="1:11" ht="26.25" customHeight="1">
+      <c r="A36" s="139"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="91" t="s">
         <v>194</v>
       </c>
-      <c r="D25" s="92" t="s">
-        <v>209</v>
-      </c>
-      <c r="E25" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="F25" s="99" t="s">
-        <v>215</v>
-      </c>
-      <c r="G25" s="92" t="s">
-        <v>167</v>
-      </c>
-      <c r="H25" s="94" t="s">
-        <v>477</v>
-      </c>
-      <c r="I25" s="92" t="s">
-        <v>219</v>
-      </c>
-      <c r="J25" s="109"/>
-      <c r="K25" s="108"/>
-    </row>
-    <row r="26" spans="1:11" s="17" customFormat="1" ht="30" customHeight="1">
-      <c r="A26" s="127"/>
-      <c r="B26" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="C26" s="92" t="s">
-        <v>195</v>
-      </c>
-      <c r="D26" s="92" t="s">
-        <v>211</v>
-      </c>
-      <c r="E26" s="92" t="s">
-        <v>212</v>
-      </c>
-      <c r="F26" s="163" t="s">
-        <v>415</v>
-      </c>
-      <c r="G26" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="H26" s="94" t="s">
-        <v>323</v>
-      </c>
-      <c r="I26" s="92" t="s">
-        <v>220</v>
-      </c>
-      <c r="J26" s="109"/>
-      <c r="K26" s="108"/>
-    </row>
-    <row r="27" spans="1:11" s="17" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="127"/>
-      <c r="B27" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="92" t="s">
-        <v>196</v>
-      </c>
-      <c r="D27" s="92" t="s">
-        <v>180</v>
-      </c>
-      <c r="E27" s="94" t="s">
-        <v>213</v>
-      </c>
-      <c r="F27" s="164"/>
-      <c r="G27" s="92" t="s">
-        <v>285</v>
-      </c>
-      <c r="H27" s="94" t="s">
-        <v>417</v>
-      </c>
-      <c r="I27" s="92" t="s">
-        <v>474</v>
-      </c>
-      <c r="J27" s="109"/>
-      <c r="K27" s="108"/>
-    </row>
-    <row r="28" spans="1:11" ht="30" customHeight="1">
-      <c r="A28" s="127"/>
-      <c r="B28" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="92" t="s">
-        <v>199</v>
-      </c>
-      <c r="D28" s="94" t="s">
-        <v>423</v>
-      </c>
-      <c r="E28" s="92" t="s">
-        <v>304</v>
-      </c>
-      <c r="F28" s="164"/>
-      <c r="G28" s="92" t="s">
-        <v>306</v>
-      </c>
-      <c r="H28" s="94" t="s">
-        <v>475</v>
-      </c>
-      <c r="I28" s="95"/>
-      <c r="J28" s="109"/>
-      <c r="K28" s="108"/>
-    </row>
-    <row r="29" spans="1:11" ht="30" customHeight="1">
-      <c r="A29" s="127"/>
-      <c r="B29" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" s="92" t="s">
-        <v>200</v>
-      </c>
-      <c r="D29" s="92" t="s">
-        <v>305</v>
-      </c>
-      <c r="E29" s="94" t="s">
-        <v>318</v>
-      </c>
-      <c r="F29" s="164"/>
-      <c r="G29" s="94" t="s">
-        <v>322</v>
-      </c>
-      <c r="H29" s="98"/>
-      <c r="I29" s="95"/>
-      <c r="J29" s="109"/>
-      <c r="K29" s="108"/>
-    </row>
-    <row r="30" spans="1:11" ht="30" customHeight="1">
-      <c r="A30" s="127"/>
-      <c r="B30" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="C30" s="92" t="s">
-        <v>201</v>
-      </c>
-      <c r="D30" s="93" t="s">
-        <v>422</v>
-      </c>
-      <c r="E30" s="94" t="s">
-        <v>320</v>
-      </c>
-      <c r="F30" s="164"/>
-      <c r="G30" s="94" t="s">
-        <v>321</v>
-      </c>
-      <c r="H30" s="98"/>
-      <c r="I30" s="95"/>
-      <c r="J30" s="109"/>
-      <c r="K30" s="108"/>
-    </row>
-    <row r="31" spans="1:11" ht="30" customHeight="1">
-      <c r="A31" s="127"/>
-      <c r="B31" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="C31" s="92" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="94" t="s">
-        <v>478</v>
-      </c>
-      <c r="E31" s="95"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="102"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="108"/>
-      <c r="J31" s="109"/>
-      <c r="K31" s="108"/>
-    </row>
-    <row r="32" spans="1:11" ht="30" customHeight="1">
-      <c r="A32" s="127"/>
-      <c r="B32" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C32" s="92" t="s">
-        <v>202</v>
-      </c>
-      <c r="D32" s="110" t="s">
-        <v>319</v>
-      </c>
-      <c r="E32" s="98"/>
-      <c r="F32" s="164"/>
-      <c r="G32" s="142" t="s">
-        <v>143</v>
-      </c>
-      <c r="H32" s="142"/>
-      <c r="I32" s="98"/>
-      <c r="J32" s="109"/>
-      <c r="K32" s="108"/>
-    </row>
-    <row r="33" spans="1:11" ht="30" customHeight="1">
-      <c r="A33" s="127"/>
-      <c r="B33" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="C33" s="92" t="s">
-        <v>198</v>
-      </c>
-      <c r="D33" s="94" t="s">
-        <v>472</v>
-      </c>
-      <c r="E33" s="98"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="142" t="s">
-        <v>142</v>
-      </c>
-      <c r="H33" s="142"/>
-      <c r="I33" s="108"/>
-      <c r="J33" s="109"/>
-      <c r="K33" s="108"/>
-    </row>
-    <row r="34" spans="1:11" ht="27" customHeight="1">
-      <c r="A34" s="127"/>
-      <c r="B34" s="55"/>
-      <c r="C34" s="92" t="s">
-        <v>197</v>
-      </c>
-      <c r="D34" s="142" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="142"/>
-      <c r="F34" s="164"/>
-      <c r="G34" s="133" t="s">
-        <v>496</v>
-      </c>
-      <c r="H34" s="133"/>
-      <c r="I34" s="108"/>
-      <c r="J34" s="109"/>
-      <c r="K34" s="108"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="127"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="92" t="s">
-        <v>204</v>
-      </c>
-      <c r="D35" s="95"/>
-      <c r="E35" s="95"/>
-      <c r="F35" s="164"/>
-      <c r="G35" s="151" t="s">
-        <v>148</v>
-      </c>
-      <c r="H35" s="151"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="109"/>
-      <c r="K35" s="108"/>
-    </row>
-    <row r="36" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A36" s="169"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="92" t="s">
-        <v>205</v>
-      </c>
-      <c r="D36" s="125" t="s">
-        <v>441</v>
-      </c>
-      <c r="E36" s="125"/>
-      <c r="F36" s="164"/>
-      <c r="G36" s="98"/>
-      <c r="H36" s="142" t="s">
-        <v>144</v>
-      </c>
-      <c r="I36" s="142"/>
-      <c r="J36" s="105"/>
-      <c r="K36" s="92"/>
+      <c r="D36" s="143" t="s">
+        <v>414</v>
+      </c>
+      <c r="E36" s="143"/>
+      <c r="F36" s="159"/>
+      <c r="G36" s="97"/>
+      <c r="H36" s="147" t="s">
+        <v>138</v>
+      </c>
+      <c r="I36" s="147"/>
+      <c r="J36" s="104"/>
+      <c r="K36" s="91"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="14"/>
       <c r="B37" s="81"/>
-      <c r="C37" s="95"/>
-      <c r="D37" s="125"/>
-      <c r="E37" s="125"/>
-      <c r="F37" s="164"/>
-      <c r="G37" s="97"/>
-      <c r="H37" s="137" t="s">
-        <v>443</v>
-      </c>
-      <c r="I37" s="137"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="105"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="143"/>
+      <c r="E37" s="143"/>
+      <c r="F37" s="159"/>
+      <c r="G37" s="96"/>
+      <c r="H37" s="163" t="s">
+        <v>416</v>
+      </c>
+      <c r="I37" s="163"/>
+      <c r="J37" s="104"/>
+      <c r="K37" s="104"/>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="14"/>
       <c r="B38" s="81"/>
-      <c r="C38" s="95"/>
-      <c r="D38" s="125" t="s">
-        <v>442</v>
-      </c>
-      <c r="E38" s="125"/>
-      <c r="F38" s="164"/>
-      <c r="G38" s="95"/>
-      <c r="H38" s="125" t="s">
-        <v>444</v>
-      </c>
-      <c r="I38" s="125"/>
-      <c r="J38" s="105"/>
-      <c r="K38" s="105"/>
+      <c r="C38" s="94"/>
+      <c r="D38" s="143" t="s">
+        <v>415</v>
+      </c>
+      <c r="E38" s="143"/>
+      <c r="F38" s="159"/>
+      <c r="G38" s="94"/>
+      <c r="H38" s="144" t="s">
+        <v>503</v>
+      </c>
+      <c r="I38" s="144"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="104"/>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="14"/>
       <c r="B39" s="64"/>
-      <c r="C39" s="111"/>
-      <c r="D39" s="143" t="s">
-        <v>91</v>
-      </c>
-      <c r="E39" s="144"/>
-      <c r="F39" s="165"/>
-      <c r="G39" s="101"/>
-      <c r="H39" s="131" t="s">
-        <v>447</v>
-      </c>
-      <c r="I39" s="132"/>
-      <c r="J39" s="105"/>
-      <c r="K39" s="105"/>
+      <c r="C39" s="109"/>
+      <c r="D39" s="176" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="177"/>
+      <c r="F39" s="160"/>
+      <c r="G39" s="100"/>
+      <c r="H39" s="155" t="s">
+        <v>419</v>
+      </c>
+      <c r="I39" s="156"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="13"/>
       <c r="B40" s="18"/>
       <c r="C40" s="34"/>
-      <c r="D40" s="140" t="s">
-        <v>152</v>
-      </c>
-      <c r="E40" s="141"/>
+      <c r="D40" s="174" t="s">
+        <v>479</v>
+      </c>
+      <c r="E40" s="175"/>
       <c r="F40" s="81"/>
       <c r="G40" s="81"/>
       <c r="J40" s="82"/>
@@ -3786,321 +3807,320 @@
       <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:11" ht="25.5">
-      <c r="A42" s="138" t="s">
+      <c r="A42" s="183" t="s">
         <v>14</v>
       </c>
       <c r="B42" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="E42" s="91" t="s">
+        <v>408</v>
+      </c>
+      <c r="F42" s="162" t="s">
+        <v>392</v>
+      </c>
+      <c r="G42" s="91" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="143" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="143"/>
+      <c r="J42" s="161" t="s">
+        <v>28</v>
+      </c>
+      <c r="K42" s="156"/>
+    </row>
+    <row r="43" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A43" s="183"/>
+      <c r="B43" s="65" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="91" t="s">
+        <v>211</v>
+      </c>
+      <c r="D43" s="91" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" s="91" t="s">
+        <v>164</v>
+      </c>
+      <c r="F43" s="162"/>
+      <c r="G43" s="91" t="s">
+        <v>205</v>
+      </c>
+      <c r="H43" s="93" t="s">
+        <v>224</v>
+      </c>
+      <c r="I43" s="91" t="s">
+        <v>227</v>
+      </c>
+      <c r="J43" s="104" t="s">
+        <v>229</v>
+      </c>
+      <c r="K43" s="91"/>
+    </row>
+    <row r="44" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A44" s="183"/>
+      <c r="B44" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="91" t="s">
+        <v>212</v>
+      </c>
+      <c r="D44" s="110" t="s">
+        <v>449</v>
+      </c>
+      <c r="E44" s="93" t="s">
+        <v>220</v>
+      </c>
+      <c r="F44" s="162"/>
+      <c r="G44" s="92" t="s">
+        <v>444</v>
+      </c>
+      <c r="H44" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="I44" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="J44" s="104"/>
+      <c r="K44" s="91"/>
+    </row>
+    <row r="45" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A45" s="183"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="91" t="s">
+        <v>417</v>
+      </c>
+      <c r="D45" s="91" t="s">
+        <v>406</v>
+      </c>
+      <c r="E45" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="F45" s="162"/>
+      <c r="G45" s="91" t="s">
         <v>222</v>
       </c>
-      <c r="C42" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="D42" s="92" t="s">
-        <v>164</v>
-      </c>
-      <c r="E42" s="92" t="s">
-        <v>435</v>
-      </c>
-      <c r="F42" s="139" t="s">
-        <v>414</v>
-      </c>
-      <c r="G42" s="92" t="s">
-        <v>177</v>
-      </c>
-      <c r="H42" s="125" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="125"/>
-      <c r="J42" s="148" t="s">
-        <v>28</v>
-      </c>
-      <c r="K42" s="132"/>
-    </row>
-    <row r="43" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A43" s="138"/>
-      <c r="B43" s="65" t="s">
+      <c r="H45" s="92" t="s">
+        <v>226</v>
+      </c>
+      <c r="I45" s="93" t="s">
+        <v>306</v>
+      </c>
+      <c r="J45" s="104"/>
+      <c r="K45" s="91"/>
+    </row>
+    <row r="46" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A46" s="183"/>
+      <c r="B46" s="61"/>
+      <c r="C46" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" s="131"/>
+      <c r="E46" s="91" t="s">
+        <v>418</v>
+      </c>
+      <c r="F46" s="162"/>
+      <c r="G46" s="91" t="s">
         <v>223</v>
       </c>
-      <c r="C43" s="92" t="s">
-        <v>224</v>
-      </c>
-      <c r="D43" s="92" t="s">
-        <v>165</v>
-      </c>
-      <c r="E43" s="92" t="s">
-        <v>174</v>
-      </c>
-      <c r="F43" s="139"/>
-      <c r="G43" s="92" t="s">
+      <c r="H46" s="94"/>
+      <c r="I46" s="94"/>
+    </row>
+    <row r="47" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A47" s="183"/>
+      <c r="B47" s="61"/>
+      <c r="C47" s="91" t="s">
+        <v>214</v>
+      </c>
+      <c r="D47" s="91" t="s">
+        <v>291</v>
+      </c>
+      <c r="E47" s="91" t="s">
+        <v>292</v>
+      </c>
+      <c r="F47" s="162"/>
+      <c r="G47" s="101"/>
+      <c r="H47" s="94"/>
+      <c r="I47" s="94"/>
+    </row>
+    <row r="48" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A48" s="183"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="91" t="s">
+        <v>215</v>
+      </c>
+      <c r="D48" s="93" t="s">
+        <v>303</v>
+      </c>
+      <c r="E48" s="128" t="s">
+        <v>460</v>
+      </c>
+      <c r="F48" s="162"/>
+      <c r="H48" s="94"/>
+      <c r="I48" s="96"/>
+      <c r="J48" s="104"/>
+      <c r="K48" s="91"/>
+    </row>
+    <row r="49" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A49" s="183"/>
+      <c r="B49" s="83"/>
+      <c r="C49" s="91" t="s">
+        <v>446</v>
+      </c>
+      <c r="D49" s="93" t="s">
+        <v>305</v>
+      </c>
+      <c r="E49" s="93" t="s">
+        <v>304</v>
+      </c>
+      <c r="F49" s="162"/>
+      <c r="G49" s="97"/>
+      <c r="H49" s="147" t="s">
+        <v>465</v>
+      </c>
+      <c r="I49" s="147"/>
+      <c r="J49" s="104"/>
+      <c r="K49" s="91"/>
+    </row>
+    <row r="50" spans="1:11" s="17" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A50" s="183"/>
+      <c r="B50" s="83"/>
+      <c r="C50" s="123"/>
+      <c r="D50" s="93" t="s">
+        <v>505</v>
+      </c>
+      <c r="E50" s="105" t="s">
+        <v>504</v>
+      </c>
+      <c r="F50" s="162"/>
+      <c r="G50" s="97"/>
+      <c r="H50" s="124"/>
+      <c r="I50" s="124"/>
+      <c r="J50" s="125"/>
+      <c r="K50" s="123"/>
+    </row>
+    <row r="51" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A51" s="183"/>
+      <c r="B51" s="83"/>
+      <c r="C51" s="91" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51" s="164" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="164"/>
+      <c r="F51" s="162"/>
+      <c r="G51" s="91"/>
+      <c r="H51" s="143" t="s">
+        <v>453</v>
+      </c>
+      <c r="I51" s="143"/>
+      <c r="J51" s="104"/>
+      <c r="K51" s="91"/>
+    </row>
+    <row r="52" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A52" s="183"/>
+      <c r="B52" s="83"/>
+      <c r="C52" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="D52" s="164" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" s="164"/>
+      <c r="F52" s="91" t="s">
+        <v>434</v>
+      </c>
+      <c r="G52" s="91"/>
+      <c r="H52" s="143" t="s">
+        <v>386</v>
+      </c>
+      <c r="I52" s="143"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="91"/>
+    </row>
+    <row r="53" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A53" s="183"/>
+      <c r="B53" s="83"/>
+      <c r="C53" s="91" t="s">
+        <v>450</v>
+      </c>
+      <c r="D53" s="143" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="143"/>
+      <c r="F53" s="91" t="s">
+        <v>202</v>
+      </c>
+      <c r="G53" s="94"/>
+      <c r="H53" s="144" t="s">
+        <v>485</v>
+      </c>
+      <c r="I53" s="144"/>
+      <c r="J53" s="91"/>
+      <c r="K53" s="91"/>
+    </row>
+    <row r="54" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A54" s="183"/>
+      <c r="B54" s="83"/>
+      <c r="C54" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="H43" s="94" t="s">
-        <v>238</v>
-      </c>
-      <c r="I43" s="92" t="s">
-        <v>241</v>
-      </c>
-      <c r="J43" s="105" t="s">
-        <v>243</v>
-      </c>
-      <c r="K43" s="92"/>
-    </row>
-    <row r="44" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A44" s="138"/>
-      <c r="B44" s="65" t="s">
-        <v>221</v>
-      </c>
-      <c r="C44" s="92" t="s">
-        <v>225</v>
-      </c>
-      <c r="D44" s="112" t="s">
-        <v>486</v>
-      </c>
-      <c r="E44" s="94" t="s">
-        <v>234</v>
-      </c>
-      <c r="F44" s="139"/>
-      <c r="G44" s="93" t="s">
-        <v>481</v>
-      </c>
-      <c r="H44" s="92" t="s">
-        <v>239</v>
-      </c>
-      <c r="I44" s="92" t="s">
-        <v>242</v>
-      </c>
-      <c r="J44" s="105"/>
-      <c r="K44" s="92"/>
-    </row>
-    <row r="45" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A45" s="138"/>
-      <c r="B45" s="61"/>
-      <c r="C45" s="92" t="s">
-        <v>445</v>
-      </c>
-      <c r="D45" s="92" t="s">
-        <v>430</v>
-      </c>
-      <c r="E45" s="92" t="s">
-        <v>235</v>
-      </c>
-      <c r="F45" s="139"/>
-      <c r="G45" s="92" t="s">
-        <v>236</v>
-      </c>
-      <c r="H45" s="93" t="s">
-        <v>240</v>
-      </c>
-      <c r="I45" s="94" t="s">
-        <v>328</v>
-      </c>
-      <c r="J45" s="105"/>
-      <c r="K45" s="92"/>
-    </row>
-    <row r="46" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A46" s="138"/>
-      <c r="B46" s="61"/>
-      <c r="C46" s="92" t="s">
-        <v>226</v>
-      </c>
-      <c r="D46" s="92" t="s">
-        <v>233</v>
-      </c>
-      <c r="E46" s="92" t="s">
-        <v>446</v>
-      </c>
-      <c r="F46" s="139"/>
-      <c r="G46" s="92" t="s">
-        <v>237</v>
-      </c>
-      <c r="H46" s="95"/>
-      <c r="I46" s="95"/>
-    </row>
-    <row r="47" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A47" s="138"/>
-      <c r="B47" s="61"/>
-      <c r="C47" s="92" t="s">
-        <v>227</v>
-      </c>
-      <c r="D47" s="92" t="s">
-        <v>307</v>
-      </c>
-      <c r="E47" s="92" t="s">
-        <v>308</v>
-      </c>
-      <c r="F47" s="139"/>
-      <c r="G47" s="102"/>
-      <c r="H47" s="95"/>
-      <c r="I47" s="95"/>
-    </row>
-    <row r="48" spans="1:11" s="17" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A48" s="138"/>
-      <c r="B48" s="61"/>
-      <c r="C48" s="124"/>
-      <c r="D48" s="124"/>
-      <c r="E48" s="94" t="s">
-        <v>510</v>
-      </c>
-      <c r="F48" s="139"/>
-      <c r="G48" s="102"/>
-      <c r="H48" s="95"/>
-      <c r="I48" s="173"/>
-    </row>
-    <row r="49" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A49" s="138"/>
-      <c r="B49" s="59"/>
-      <c r="C49" s="92" t="s">
-        <v>228</v>
-      </c>
-      <c r="D49" s="94" t="s">
-        <v>324</v>
-      </c>
-      <c r="E49" s="107" t="s">
-        <v>498</v>
-      </c>
-      <c r="F49" s="139"/>
-      <c r="G49" s="94" t="s">
-        <v>327</v>
-      </c>
-      <c r="H49" s="95"/>
-      <c r="I49" s="97"/>
-      <c r="J49" s="105"/>
-      <c r="K49" s="92"/>
-    </row>
-    <row r="50" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A50" s="138"/>
-      <c r="B50" s="83"/>
-      <c r="C50" s="92" t="s">
-        <v>483</v>
-      </c>
-      <c r="D50" s="94" t="s">
-        <v>326</v>
-      </c>
-      <c r="E50" s="94" t="s">
-        <v>325</v>
-      </c>
-      <c r="F50" s="139"/>
-      <c r="G50" s="98"/>
-      <c r="H50" s="142" t="s">
-        <v>508</v>
-      </c>
-      <c r="I50" s="142"/>
-      <c r="J50" s="105"/>
-      <c r="K50" s="92"/>
-    </row>
-    <row r="51" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A51" s="138"/>
-      <c r="B51" s="83"/>
-      <c r="C51" s="92" t="s">
-        <v>229</v>
-      </c>
-      <c r="D51" s="145" t="s">
-        <v>81</v>
-      </c>
-      <c r="E51" s="145"/>
-      <c r="F51" s="139"/>
-      <c r="G51" s="92"/>
-      <c r="H51" s="125" t="s">
-        <v>490</v>
-      </c>
-      <c r="I51" s="125"/>
-      <c r="J51" s="105"/>
-      <c r="K51" s="92"/>
-    </row>
-    <row r="52" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A52" s="138"/>
-      <c r="B52" s="83"/>
-      <c r="C52" s="92" t="s">
-        <v>230</v>
-      </c>
-      <c r="D52" s="145" t="s">
-        <v>86</v>
-      </c>
-      <c r="E52" s="145"/>
-      <c r="F52" s="92" t="s">
-        <v>469</v>
-      </c>
-      <c r="G52" s="92"/>
-      <c r="H52" s="125" t="s">
-        <v>408</v>
-      </c>
-      <c r="I52" s="125"/>
-      <c r="J52" s="105"/>
-      <c r="K52" s="92"/>
-    </row>
-    <row r="53" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A53" s="138"/>
-      <c r="B53" s="83"/>
-      <c r="C53" s="92" t="s">
-        <v>487</v>
-      </c>
-      <c r="D53" s="125" t="s">
-        <v>88</v>
-      </c>
-      <c r="E53" s="125"/>
-      <c r="F53" s="92" t="s">
-        <v>215</v>
-      </c>
-      <c r="G53" s="95"/>
-      <c r="H53" s="125" t="s">
-        <v>95</v>
-      </c>
-      <c r="I53" s="125"/>
-      <c r="J53" s="92"/>
-      <c r="K53" s="92"/>
-    </row>
-    <row r="54" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A54" s="138"/>
-      <c r="B54" s="83"/>
-      <c r="C54" s="92" t="s">
-        <v>231</v>
-      </c>
-      <c r="D54" s="125" t="s">
-        <v>155</v>
-      </c>
-      <c r="E54" s="125"/>
-      <c r="F54" s="125" t="s">
+      <c r="D54" s="143" t="s">
+        <v>147</v>
+      </c>
+      <c r="E54" s="143"/>
+      <c r="F54" s="143" t="s">
         <v>74</v>
       </c>
-      <c r="G54" s="125"/>
-      <c r="H54" s="125" t="s">
-        <v>156</v>
-      </c>
-      <c r="I54" s="125"/>
-      <c r="J54" s="92"/>
-      <c r="K54" s="92"/>
+      <c r="G54" s="143"/>
+      <c r="H54" s="144" t="s">
+        <v>478</v>
+      </c>
+      <c r="I54" s="144"/>
+      <c r="J54" s="91"/>
+      <c r="K54" s="91"/>
     </row>
     <row r="55" spans="1:11" s="17" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A55" s="138"/>
+      <c r="A55" s="183"/>
       <c r="B55" s="83"/>
-      <c r="C55" s="92"/>
-      <c r="D55" s="142" t="s">
-        <v>507</v>
-      </c>
-      <c r="E55" s="142"/>
-      <c r="F55" s="92"/>
-      <c r="G55" s="92"/>
-      <c r="H55" s="92"/>
-      <c r="I55" s="92"/>
-      <c r="J55" s="92"/>
-      <c r="K55" s="92"/>
+      <c r="C55" s="91"/>
+      <c r="D55" s="147" t="s">
+        <v>464</v>
+      </c>
+      <c r="E55" s="147"/>
+      <c r="F55" s="91"/>
+      <c r="G55" s="91"/>
+      <c r="H55" s="91"/>
+      <c r="I55" s="91"/>
+      <c r="J55" s="91"/>
+      <c r="K55" s="91"/>
     </row>
     <row r="56" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A56" s="138"/>
+      <c r="A56" s="183"/>
       <c r="B56" s="83"/>
-      <c r="C56" s="92" t="s">
-        <v>232</v>
-      </c>
-      <c r="D56" s="125" t="s">
-        <v>448</v>
-      </c>
-      <c r="E56" s="125"/>
-      <c r="F56" s="98"/>
-      <c r="G56" s="92"/>
-      <c r="H56" s="95"/>
-      <c r="I56" s="95"/>
-      <c r="J56" s="92"/>
-      <c r="K56" s="92"/>
+      <c r="C56" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="D56" s="143" t="s">
+        <v>420</v>
+      </c>
+      <c r="E56" s="143"/>
+      <c r="F56" s="97"/>
+      <c r="G56" s="91"/>
+      <c r="H56" s="94"/>
+      <c r="I56" s="94"/>
+      <c r="J56" s="91"/>
+      <c r="K56" s="91"/>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="8"/>
@@ -4115,394 +4135,392 @@
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
     </row>
-    <row r="58" spans="1:11" ht="26.25" thickBot="1">
-      <c r="A58" s="126" t="s">
+    <row r="58" spans="1:11" ht="25.5">
+      <c r="A58" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B58" s="92" t="s">
+      <c r="B58" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="92" t="s">
+      <c r="C58" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="D58" s="101"/>
-      <c r="E58" s="101"/>
-      <c r="F58" s="157" t="s">
-        <v>414</v>
-      </c>
-      <c r="G58" s="92" t="s">
-        <v>258</v>
-      </c>
-      <c r="H58" s="93" t="s">
-        <v>259</v>
-      </c>
-      <c r="I58" s="92" t="s">
-        <v>260</v>
-      </c>
-      <c r="J58" s="148" t="s">
+      <c r="D58" s="100"/>
+      <c r="E58" s="100"/>
+      <c r="F58" s="172" t="s">
+        <v>392</v>
+      </c>
+      <c r="G58" s="123" t="s">
+        <v>243</v>
+      </c>
+      <c r="H58" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="I58" s="123" t="s">
+        <v>245</v>
+      </c>
+      <c r="J58" s="161" t="s">
         <v>28</v>
       </c>
-      <c r="K58" s="132"/>
+      <c r="K58" s="156"/>
     </row>
     <row r="59" spans="1:11" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A59" s="127"/>
-      <c r="B59" s="92"/>
-      <c r="C59" s="113" t="s">
+      <c r="A59" s="138"/>
+      <c r="B59" s="91"/>
+      <c r="C59" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D59" s="151" t="s">
-        <v>149</v>
-      </c>
-      <c r="E59" s="151"/>
-      <c r="F59" s="158"/>
-      <c r="G59" s="92" t="s">
-        <v>261</v>
-      </c>
-      <c r="H59" s="92" t="s">
-        <v>262</v>
-      </c>
-      <c r="I59" s="92" t="s">
-        <v>263</v>
-      </c>
-      <c r="J59" s="155" t="s">
-        <v>471</v>
-      </c>
-      <c r="K59" s="156"/>
+      <c r="D59" s="157" t="s">
+        <v>143</v>
+      </c>
+      <c r="E59" s="157"/>
+      <c r="F59" s="141"/>
+      <c r="H59" s="123" t="s">
+        <v>246</v>
+      </c>
+      <c r="I59" s="123" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="60" spans="1:11" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A60" s="127"/>
-      <c r="B60" s="92" t="s">
-        <v>224</v>
-      </c>
-      <c r="C60" s="113" t="s">
-        <v>185</v>
-      </c>
-      <c r="D60" s="92" t="s">
-        <v>440</v>
-      </c>
-      <c r="E60" s="92" t="s">
+      <c r="A60" s="138"/>
+      <c r="B60" s="91" t="s">
+        <v>211</v>
+      </c>
+      <c r="C60" s="111" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60" s="123" t="s">
+        <v>413</v>
+      </c>
+      <c r="E60" s="129" t="s">
+        <v>495</v>
+      </c>
+      <c r="F60" s="141"/>
+      <c r="G60" s="128" t="s">
+        <v>220</v>
+      </c>
+      <c r="I60" s="123" t="s">
+        <v>165</v>
+      </c>
+      <c r="J60" s="150" t="s">
+        <v>145</v>
+      </c>
+      <c r="K60" s="151"/>
+    </row>
+    <row r="61" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A61" s="138"/>
+      <c r="B61" s="91" t="s">
+        <v>212</v>
+      </c>
+      <c r="C61" s="111" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" s="123" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" s="123" t="s">
+        <v>196</v>
+      </c>
+      <c r="F61" s="141"/>
+      <c r="G61" s="123" t="s">
         <v>206</v>
       </c>
-      <c r="F60" s="158"/>
-      <c r="G60" s="94" t="s">
+      <c r="H61" s="123" t="s">
+        <v>249</v>
+      </c>
+      <c r="I61" s="113" t="s">
+        <v>250</v>
+      </c>
+      <c r="J61" s="112"/>
+      <c r="K61" s="103"/>
+    </row>
+    <row r="62" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A62" s="138"/>
+      <c r="B62" s="91" t="s">
+        <v>417</v>
+      </c>
+      <c r="C62" s="111" t="s">
+        <v>173</v>
+      </c>
+      <c r="D62" s="128" t="s">
+        <v>248</v>
+      </c>
+      <c r="E62" s="123" t="s">
+        <v>509</v>
+      </c>
+      <c r="F62" s="141"/>
+      <c r="G62" s="128" t="s">
+        <v>310</v>
+      </c>
+      <c r="H62" s="128" t="s">
+        <v>311</v>
+      </c>
+      <c r="I62" s="128" t="s">
+        <v>312</v>
+      </c>
+      <c r="J62" s="112"/>
+      <c r="K62" s="103"/>
+    </row>
+    <row r="63" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A63" s="138"/>
+      <c r="B63" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="111" t="s">
+        <v>235</v>
+      </c>
+      <c r="D63" s="128" t="s">
+        <v>240</v>
+      </c>
+      <c r="E63" s="101"/>
+      <c r="F63" s="141"/>
+      <c r="G63" s="128" t="s">
+        <v>391</v>
+      </c>
+      <c r="H63" s="147" t="s">
+        <v>442</v>
+      </c>
+      <c r="I63" s="147"/>
+      <c r="J63" s="112"/>
+      <c r="K63" s="103"/>
+    </row>
+    <row r="64" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A64" s="138"/>
+      <c r="B64" s="91" t="s">
+        <v>214</v>
+      </c>
+      <c r="C64" s="111" t="s">
+        <v>239</v>
+      </c>
+      <c r="D64" s="123" t="s">
+        <v>203</v>
+      </c>
+      <c r="E64" s="123" t="s">
+        <v>241</v>
+      </c>
+      <c r="F64" s="141"/>
+      <c r="G64" s="164" t="s">
+        <v>85</v>
+      </c>
+      <c r="H64" s="164"/>
+      <c r="I64" s="123" t="s">
+        <v>422</v>
+      </c>
+      <c r="J64" s="112"/>
+      <c r="K64" s="103"/>
+    </row>
+    <row r="65" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A65" s="138"/>
+      <c r="B65" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D65" s="123" t="s">
+        <v>242</v>
+      </c>
+      <c r="E65" s="128" t="s">
+        <v>309</v>
+      </c>
+      <c r="F65" s="141"/>
+      <c r="G65" s="164" t="s">
+        <v>82</v>
+      </c>
+      <c r="H65" s="164"/>
+      <c r="I65" s="94"/>
+      <c r="J65" s="112"/>
+      <c r="K65" s="103"/>
+    </row>
+    <row r="66" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A66" s="138"/>
+      <c r="B66" s="91" t="s">
+        <v>231</v>
+      </c>
+      <c r="C66" s="111" t="s">
+        <v>466</v>
+      </c>
+      <c r="D66" s="123" t="s">
+        <v>389</v>
+      </c>
+      <c r="E66" s="123" t="s">
+        <v>421</v>
+      </c>
+      <c r="F66" s="141"/>
+      <c r="G66" s="123" t="s">
+        <v>437</v>
+      </c>
+      <c r="H66" s="110" t="s">
+        <v>449</v>
+      </c>
+      <c r="I66" s="114"/>
+      <c r="J66" s="112"/>
+      <c r="K66" s="103"/>
+    </row>
+    <row r="67" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A67" s="138"/>
+      <c r="B67" s="91" t="s">
+        <v>232</v>
+      </c>
+      <c r="C67" s="111" t="s">
+        <v>179</v>
+      </c>
+      <c r="D67" s="123" t="s">
+        <v>390</v>
+      </c>
+      <c r="E67" s="105" t="s">
+        <v>475</v>
+      </c>
+      <c r="F67" s="141"/>
+      <c r="G67" s="105" t="s">
+        <v>476</v>
+      </c>
+      <c r="H67" s="122" t="s">
+        <v>493</v>
+      </c>
+      <c r="I67" s="114"/>
+      <c r="J67" s="112"/>
+      <c r="K67" s="103"/>
+    </row>
+    <row r="68" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A68" s="138"/>
+      <c r="B68" s="91" t="s">
+        <v>451</v>
+      </c>
+      <c r="C68" s="111" t="s">
+        <v>238</v>
+      </c>
+      <c r="D68" s="128" t="s">
+        <v>307</v>
+      </c>
+      <c r="E68" s="94"/>
+      <c r="F68" s="142"/>
+      <c r="G68" s="130" t="s">
+        <v>494</v>
+      </c>
+      <c r="H68" s="174" t="s">
+        <v>499</v>
+      </c>
+      <c r="I68" s="181"/>
+      <c r="J68" s="112"/>
+      <c r="K68" s="103"/>
+    </row>
+    <row r="69" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A69" s="138"/>
+      <c r="B69" s="91" t="s">
+        <v>233</v>
+      </c>
+      <c r="C69" s="111" t="s">
+        <v>463</v>
+      </c>
+      <c r="D69" s="93" t="s">
+        <v>506</v>
+      </c>
+      <c r="E69" s="94"/>
+      <c r="F69" s="123" t="s">
+        <v>201</v>
+      </c>
+      <c r="G69" s="97"/>
+      <c r="H69" s="143"/>
+      <c r="I69" s="143"/>
+      <c r="J69" s="112"/>
+      <c r="K69" s="103"/>
+    </row>
+    <row r="70" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A70" s="138"/>
+      <c r="B70" s="91" t="s">
         <v>234</v>
       </c>
-      <c r="H60" s="94" t="s">
-        <v>264</v>
-      </c>
-      <c r="I60" s="92" t="s">
-        <v>175</v>
-      </c>
-      <c r="J60" s="155" t="s">
-        <v>153</v>
-      </c>
-      <c r="K60" s="156"/>
-    </row>
-    <row r="61" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A61" s="127"/>
-      <c r="B61" s="92" t="s">
-        <v>225</v>
-      </c>
-      <c r="C61" s="113" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" s="92" t="s">
-        <v>207</v>
-      </c>
-      <c r="E61" s="92" t="s">
-        <v>208</v>
-      </c>
-      <c r="F61" s="158"/>
-      <c r="G61" s="92" t="s">
-        <v>219</v>
-      </c>
-      <c r="H61" s="92" t="s">
-        <v>265</v>
-      </c>
-      <c r="I61" s="115" t="s">
-        <v>266</v>
-      </c>
-      <c r="J61" s="114"/>
-      <c r="K61" s="104"/>
-    </row>
-    <row r="62" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A62" s="127"/>
-      <c r="B62" s="92" t="s">
-        <v>445</v>
-      </c>
-      <c r="C62" s="113" t="s">
-        <v>183</v>
-      </c>
-      <c r="D62" s="112" t="s">
-        <v>486</v>
-      </c>
-      <c r="E62" s="92" t="s">
-        <v>254</v>
-      </c>
-      <c r="F62" s="158"/>
-      <c r="G62" s="94" t="s">
-        <v>332</v>
-      </c>
-      <c r="H62" s="94" t="s">
-        <v>333</v>
-      </c>
-      <c r="I62" s="94" t="s">
-        <v>334</v>
-      </c>
-      <c r="J62" s="114"/>
-      <c r="K62" s="104"/>
-    </row>
-    <row r="63" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A63" s="127"/>
-      <c r="B63" s="92" t="s">
-        <v>226</v>
-      </c>
-      <c r="C63" s="113" t="s">
-        <v>249</v>
-      </c>
-      <c r="D63" s="94" t="s">
-        <v>255</v>
-      </c>
-      <c r="E63" s="102"/>
-      <c r="F63" s="158"/>
-      <c r="G63" s="94" t="s">
-        <v>413</v>
-      </c>
-      <c r="H63" s="142" t="s">
-        <v>479</v>
-      </c>
-      <c r="I63" s="142"/>
-      <c r="J63" s="114"/>
-      <c r="K63" s="104"/>
-    </row>
-    <row r="64" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A64" s="127"/>
-      <c r="B64" s="92" t="s">
-        <v>227</v>
-      </c>
-      <c r="C64" s="113" t="s">
-        <v>253</v>
-      </c>
-      <c r="D64" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="E64" s="92" t="s">
-        <v>256</v>
-      </c>
-      <c r="F64" s="158"/>
-      <c r="G64" s="145" t="s">
-        <v>85</v>
-      </c>
-      <c r="H64" s="145"/>
-      <c r="I64" s="92" t="s">
-        <v>450</v>
-      </c>
-      <c r="J64" s="114"/>
-      <c r="K64" s="104"/>
-    </row>
-    <row r="65" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A65" s="127"/>
-      <c r="B65" s="92" t="s">
-        <v>244</v>
-      </c>
-      <c r="C65" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="D65" s="92" t="s">
-        <v>257</v>
-      </c>
-      <c r="E65" s="94" t="s">
-        <v>331</v>
-      </c>
-      <c r="F65" s="158"/>
-      <c r="G65" s="145" t="s">
-        <v>82</v>
-      </c>
-      <c r="H65" s="145"/>
-      <c r="I65" s="95"/>
-      <c r="J65" s="114"/>
-      <c r="K65" s="104"/>
-    </row>
-    <row r="66" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A66" s="127"/>
-      <c r="B66" s="92" t="s">
-        <v>245</v>
-      </c>
-      <c r="C66" s="113" t="s">
-        <v>509</v>
-      </c>
-      <c r="D66" s="92" t="s">
-        <v>411</v>
-      </c>
-      <c r="E66" s="92" t="s">
-        <v>449</v>
-      </c>
-      <c r="F66" s="158"/>
-      <c r="G66" s="92" t="s">
-        <v>473</v>
-      </c>
-      <c r="H66" s="116"/>
-      <c r="I66" s="116"/>
-      <c r="J66" s="114"/>
-      <c r="K66" s="104"/>
-    </row>
-    <row r="67" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A67" s="127"/>
-      <c r="B67" s="92" t="s">
-        <v>246</v>
-      </c>
-      <c r="C67" s="113" t="s">
-        <v>189</v>
-      </c>
-      <c r="D67" s="92" t="s">
-        <v>412</v>
-      </c>
-      <c r="E67" s="95"/>
-      <c r="F67" s="158"/>
-      <c r="G67" s="98"/>
-      <c r="H67" s="116"/>
-      <c r="I67" s="116"/>
-      <c r="J67" s="114"/>
-      <c r="K67" s="104"/>
-    </row>
-    <row r="68" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A68" s="127"/>
-      <c r="B68" s="92" t="s">
-        <v>488</v>
-      </c>
-      <c r="C68" s="113" t="s">
-        <v>252</v>
-      </c>
-      <c r="D68" s="94" t="s">
-        <v>329</v>
-      </c>
-      <c r="E68" s="95"/>
-      <c r="F68" s="159"/>
-      <c r="G68" s="92"/>
-      <c r="H68" s="134" t="s">
-        <v>502</v>
-      </c>
-      <c r="I68" s="135"/>
-      <c r="J68" s="114"/>
-      <c r="K68" s="104"/>
-    </row>
-    <row r="69" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A69" s="127"/>
-      <c r="B69" s="92" t="s">
-        <v>247</v>
-      </c>
-      <c r="C69" s="113" t="s">
-        <v>506</v>
-      </c>
-      <c r="E69" s="95"/>
-      <c r="F69" s="92" t="s">
-        <v>214</v>
-      </c>
-      <c r="G69" s="98"/>
-      <c r="H69" s="125" t="s">
-        <v>87</v>
-      </c>
-      <c r="I69" s="125"/>
-      <c r="J69" s="114"/>
-      <c r="K69" s="104"/>
-    </row>
-    <row r="70" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A70" s="127"/>
-      <c r="B70" s="92" t="s">
-        <v>248</v>
-      </c>
-      <c r="C70" s="94" t="s">
-        <v>504</v>
-      </c>
-      <c r="D70" s="125" t="s">
-        <v>451</v>
-      </c>
-      <c r="E70" s="125"/>
-      <c r="F70" s="115"/>
-      <c r="G70" s="98"/>
-      <c r="H70" s="125" t="s">
-        <v>454</v>
-      </c>
-      <c r="I70" s="125"/>
-      <c r="J70" s="114"/>
-      <c r="K70" s="104"/>
+      <c r="D70" s="144" t="s">
+        <v>483</v>
+      </c>
+      <c r="E70" s="144"/>
+      <c r="F70" s="113"/>
+      <c r="G70" s="97"/>
+      <c r="H70" s="143" t="s">
+        <v>424</v>
+      </c>
+      <c r="I70" s="143"/>
+      <c r="J70" s="112"/>
+      <c r="K70" s="103"/>
     </row>
     <row r="71" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A71" s="127"/>
-      <c r="B71" s="92" t="s">
-        <v>484</v>
-      </c>
-      <c r="C71" s="113"/>
-      <c r="D71" s="137" t="s">
-        <v>452</v>
-      </c>
-      <c r="E71" s="137"/>
-      <c r="F71" s="97"/>
-      <c r="G71" s="117"/>
-      <c r="H71" s="125" t="s">
-        <v>455</v>
-      </c>
-      <c r="I71" s="125"/>
-      <c r="J71" s="114"/>
-      <c r="K71" s="104"/>
+      <c r="A71" s="138"/>
+      <c r="B71" s="91" t="s">
+        <v>447</v>
+      </c>
+      <c r="C71" s="111"/>
+      <c r="D71" s="182" t="s">
+        <v>498</v>
+      </c>
+      <c r="E71" s="163"/>
+      <c r="F71" s="96"/>
+      <c r="G71" s="115"/>
+      <c r="H71" s="143" t="s">
+        <v>425</v>
+      </c>
+      <c r="I71" s="143"/>
+      <c r="J71" s="112"/>
+      <c r="K71" s="103"/>
     </row>
     <row r="72" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A72" s="127"/>
-      <c r="B72" s="101"/>
-      <c r="C72" s="113"/>
-      <c r="D72" s="125" t="s">
-        <v>157</v>
-      </c>
-      <c r="E72" s="125"/>
-      <c r="F72" s="118"/>
-      <c r="G72" s="95"/>
-      <c r="H72" s="125" t="s">
-        <v>456</v>
-      </c>
-      <c r="I72" s="125"/>
-      <c r="J72" s="114"/>
-      <c r="K72" s="104"/>
+      <c r="A72" s="138"/>
+      <c r="B72" s="100"/>
+      <c r="C72" s="111"/>
+      <c r="D72" s="143" t="s">
+        <v>148</v>
+      </c>
+      <c r="E72" s="143"/>
+      <c r="F72" s="116"/>
+      <c r="G72" s="94"/>
+      <c r="H72" s="143" t="s">
+        <v>426</v>
+      </c>
+      <c r="I72" s="143"/>
+      <c r="J72" s="112"/>
+      <c r="K72" s="103"/>
     </row>
     <row r="73" spans="1:11" s="17" customFormat="1">
-      <c r="A73" s="127"/>
-      <c r="B73" s="101"/>
-      <c r="C73" s="113"/>
-      <c r="D73" s="131" t="s">
-        <v>453</v>
-      </c>
-      <c r="E73" s="132"/>
-      <c r="F73" s="118"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="98"/>
-      <c r="I73" s="98"/>
-      <c r="J73" s="114"/>
-      <c r="K73" s="104"/>
+      <c r="A73" s="138"/>
+      <c r="B73" s="100"/>
+      <c r="C73" s="111"/>
+      <c r="D73" s="155" t="s">
+        <v>423</v>
+      </c>
+      <c r="E73" s="156"/>
+      <c r="F73" s="116"/>
+      <c r="G73" s="94"/>
+      <c r="H73" s="97"/>
+      <c r="I73" s="97"/>
+      <c r="J73" s="112"/>
+      <c r="K73" s="103"/>
     </row>
     <row r="74" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A74" s="127"/>
-      <c r="B74" s="92"/>
-      <c r="C74" s="113"/>
-      <c r="D74" s="116"/>
-      <c r="E74" s="116"/>
-      <c r="F74" s="118"/>
-      <c r="G74" s="95"/>
-      <c r="H74" s="98"/>
-      <c r="I74" s="98"/>
-      <c r="J74" s="114"/>
-      <c r="K74" s="104"/>
+      <c r="A74" s="138"/>
+      <c r="B74" s="91"/>
+      <c r="C74" s="111"/>
+      <c r="D74" s="114"/>
+      <c r="E74" s="114"/>
+      <c r="F74" s="116"/>
+      <c r="G74" s="94"/>
+      <c r="H74" s="97"/>
+      <c r="I74" s="97"/>
+      <c r="J74" s="112"/>
+      <c r="K74" s="103"/>
     </row>
     <row r="75" spans="1:11" s="17" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A75" s="127"/>
-      <c r="B75" s="92"/>
-      <c r="C75" s="113"/>
-      <c r="D75" s="116"/>
-      <c r="E75" s="116"/>
-      <c r="F75" s="118"/>
-      <c r="G75" s="95"/>
-      <c r="H75" s="98"/>
-      <c r="I75" s="98"/>
-      <c r="J75" s="114"/>
-      <c r="K75" s="104"/>
+      <c r="A75" s="138"/>
+      <c r="B75" s="91"/>
+      <c r="C75" s="111"/>
+      <c r="D75" s="114"/>
+      <c r="E75" s="114"/>
+      <c r="F75" s="116"/>
+      <c r="G75" s="94"/>
+      <c r="H75" s="97"/>
+      <c r="I75" s="97"/>
+      <c r="J75" s="112"/>
+      <c r="K75" s="103"/>
     </row>
     <row r="76" spans="1:11" s="17" customFormat="1">
       <c r="A76" s="8"/>
@@ -4518,7 +4536,7 @@
       <c r="K76" s="33"/>
     </row>
     <row r="77" spans="1:11" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A77" s="128" t="s">
+      <c r="A77" s="179" t="s">
         <v>17</v>
       </c>
       <c r="B77" s="81" t="s">
@@ -4531,325 +4549,328 @@
       <c r="E77" s="56"/>
       <c r="F77" s="85"/>
       <c r="G77" s="23" t="s">
-        <v>457</v>
-      </c>
-      <c r="H77" s="23" t="s">
-        <v>206</v>
+        <v>427</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="J77" s="149" t="s">
+        <v>270</v>
+      </c>
+      <c r="J77" s="167" t="s">
         <v>28</v>
       </c>
-      <c r="K77" s="150"/>
+      <c r="K77" s="168"/>
     </row>
     <row r="78" spans="1:11" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A78" s="129"/>
+      <c r="A78" s="180"/>
       <c r="B78" s="23" t="s">
         <v>41</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D78" s="88" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="E78" s="80" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="F78" s="77"/>
       <c r="G78" s="23" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="H78" s="23" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="I78" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="J78" s="155" t="s">
-        <v>154</v>
-      </c>
-      <c r="K78" s="156"/>
-    </row>
-    <row r="79" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A79" s="129"/>
+        <v>271</v>
+      </c>
+      <c r="J78" s="150" t="s">
+        <v>146</v>
+      </c>
+      <c r="K78" s="151"/>
+    </row>
+    <row r="79" spans="1:11" ht="28.5" customHeight="1" thickBot="1">
+      <c r="A79" s="180"/>
       <c r="B79" s="23" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="D79" s="92" t="s">
-        <v>277</v>
-      </c>
-      <c r="E79" s="92" t="s">
-        <v>278</v>
-      </c>
-      <c r="F79" s="119"/>
-      <c r="G79" s="92" t="s">
-        <v>209</v>
-      </c>
-      <c r="H79" s="92" t="s">
-        <v>210</v>
-      </c>
-      <c r="I79" s="92"/>
-      <c r="J79" s="15"/>
-      <c r="K79" s="15"/>
+        <v>183</v>
+      </c>
+      <c r="D79" s="91" t="s">
+        <v>261</v>
+      </c>
+      <c r="E79" s="91" t="s">
+        <v>262</v>
+      </c>
+      <c r="F79" s="117"/>
+      <c r="G79" s="123" t="s">
+        <v>197</v>
+      </c>
+      <c r="H79" s="122" t="s">
+        <v>474</v>
+      </c>
+      <c r="I79" s="130" t="s">
+        <v>491</v>
+      </c>
+      <c r="J79" s="148" t="s">
+        <v>481</v>
+      </c>
+      <c r="K79" s="149"/>
     </row>
     <row r="80" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A80" s="129"/>
+      <c r="A80" s="180"/>
       <c r="B80" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80" s="91" t="s">
+        <v>406</v>
+      </c>
+      <c r="E80" s="91" t="s">
+        <v>397</v>
+      </c>
+      <c r="F80" s="117"/>
+      <c r="G80" s="91" t="s">
         <v>267</v>
       </c>
-      <c r="C80" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="D80" s="92" t="s">
-        <v>430</v>
-      </c>
-      <c r="E80" s="92" t="s">
-        <v>421</v>
-      </c>
-      <c r="F80" s="119"/>
-      <c r="G80" s="92" t="s">
-        <v>283</v>
-      </c>
-      <c r="H80" s="92" t="s">
-        <v>179</v>
-      </c>
-      <c r="I80" s="92"/>
+      <c r="H80" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="I80" s="130" t="s">
+        <v>496</v>
+      </c>
       <c r="J80" s="16"/>
       <c r="K80" s="15"/>
     </row>
     <row r="81" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A81" s="129"/>
+      <c r="A81" s="180"/>
       <c r="B81" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="D81" s="118" t="s">
+        <v>449</v>
+      </c>
+      <c r="E81" s="92" t="s">
+        <v>444</v>
+      </c>
+      <c r="F81" s="117" t="s">
+        <v>393</v>
+      </c>
+      <c r="G81" s="91" t="s">
         <v>268</v>
       </c>
-      <c r="C81" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="D81" s="120" t="s">
-        <v>486</v>
-      </c>
-      <c r="E81" s="93" t="s">
-        <v>481</v>
-      </c>
-      <c r="F81" s="119" t="s">
-        <v>415</v>
-      </c>
-      <c r="G81" s="92" t="s">
-        <v>284</v>
-      </c>
-      <c r="H81" s="125"/>
-      <c r="I81" s="125"/>
+      <c r="H81" s="143"/>
+      <c r="I81" s="143"/>
       <c r="J81" s="16"/>
       <c r="K81" s="15"/>
     </row>
     <row r="82" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A82" s="129"/>
+      <c r="A82" s="180"/>
       <c r="B82" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="C82" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="D82" s="92" t="s">
-        <v>279</v>
-      </c>
-      <c r="E82" s="92" t="s">
-        <v>280</v>
-      </c>
-      <c r="F82" s="119"/>
-      <c r="G82" s="93" t="s">
-        <v>285</v>
-      </c>
-      <c r="H82" s="125" t="s">
-        <v>462</v>
-      </c>
-      <c r="I82" s="125"/>
+        <v>235</v>
+      </c>
+      <c r="C82" s="130" t="s">
+        <v>488</v>
+      </c>
+      <c r="D82" s="91" t="s">
+        <v>263</v>
+      </c>
+      <c r="E82" s="91" t="s">
+        <v>264</v>
+      </c>
+      <c r="F82" s="117"/>
+      <c r="G82" s="92" t="s">
+        <v>269</v>
+      </c>
+      <c r="H82" s="144" t="s">
+        <v>508</v>
+      </c>
+      <c r="I82" s="144"/>
       <c r="J82" s="16"/>
       <c r="K82" s="15"/>
     </row>
     <row r="83" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A83" s="129"/>
+      <c r="A83" s="180"/>
       <c r="B83" s="23" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D83" s="92" t="s">
-        <v>281</v>
-      </c>
-      <c r="E83" s="96" t="s">
-        <v>282</v>
-      </c>
-      <c r="F83" s="119"/>
-      <c r="G83" s="94" t="s">
-        <v>339</v>
-      </c>
-      <c r="H83" s="125" t="s">
-        <v>463</v>
-      </c>
-      <c r="I83" s="125"/>
+        <v>188</v>
+      </c>
+      <c r="D83" s="91" t="s">
+        <v>265</v>
+      </c>
+      <c r="E83" s="95" t="s">
+        <v>266</v>
+      </c>
+      <c r="F83" s="117"/>
+      <c r="G83" s="93" t="s">
+        <v>317</v>
+      </c>
+      <c r="H83" s="143"/>
+      <c r="I83" s="143"/>
       <c r="J83" s="16"/>
       <c r="K83" s="15"/>
     </row>
     <row r="84" spans="1:11" ht="18" customHeight="1">
-      <c r="A84" s="129"/>
+      <c r="A84" s="180"/>
       <c r="B84" s="23" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="D84" s="95"/>
-      <c r="E84" s="94" t="s">
-        <v>418</v>
-      </c>
-      <c r="F84" s="119"/>
-      <c r="G84" s="94" t="s">
-        <v>340</v>
-      </c>
-      <c r="H84" s="97"/>
-      <c r="I84" s="92"/>
+        <v>189</v>
+      </c>
+      <c r="D84" s="105" t="s">
+        <v>469</v>
+      </c>
+      <c r="E84" s="105" t="s">
+        <v>473</v>
+      </c>
+      <c r="F84" s="117"/>
+      <c r="G84" s="93" t="s">
+        <v>318</v>
+      </c>
+      <c r="H84" s="96"/>
+      <c r="I84" s="91"/>
       <c r="J84" s="16"/>
       <c r="K84" s="15"/>
     </row>
     <row r="85" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A85" s="129"/>
+      <c r="A85" s="180"/>
       <c r="B85" s="23" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="D85" s="142" t="s">
-        <v>145</v>
-      </c>
-      <c r="E85" s="142"/>
-      <c r="F85" s="119"/>
-      <c r="G85" s="121" t="s">
-        <v>341</v>
-      </c>
-      <c r="H85" s="92"/>
-      <c r="I85" s="92"/>
+        <v>190</v>
+      </c>
+      <c r="D85" s="147" t="s">
+        <v>139</v>
+      </c>
+      <c r="E85" s="147"/>
+      <c r="F85" s="117"/>
+      <c r="G85" s="119" t="s">
+        <v>319</v>
+      </c>
+      <c r="H85" s="91"/>
+      <c r="I85" s="91"/>
       <c r="J85" s="16"/>
       <c r="K85" s="15"/>
     </row>
     <row r="86" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A86" s="129"/>
+      <c r="A86" s="180"/>
       <c r="B86" s="23" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="D86" s="94" t="s">
-        <v>335</v>
-      </c>
-      <c r="E86" s="94" t="s">
-        <v>336</v>
-      </c>
-      <c r="F86" s="119"/>
-      <c r="G86" s="125" t="s">
-        <v>464</v>
-      </c>
-      <c r="H86" s="125"/>
-      <c r="I86" s="92"/>
+        <v>258</v>
+      </c>
+      <c r="D86" s="93" t="s">
+        <v>313</v>
+      </c>
+      <c r="E86" s="105" t="s">
+        <v>314</v>
+      </c>
+      <c r="F86" s="117"/>
+      <c r="G86" s="143" t="s">
+        <v>430</v>
+      </c>
+      <c r="H86" s="143"/>
+      <c r="I86" s="91"/>
       <c r="J86" s="16"/>
       <c r="K86" s="15"/>
     </row>
     <row r="87" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A87" s="129"/>
+      <c r="A87" s="180"/>
       <c r="B87" s="23" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="D87" s="94" t="s">
-        <v>337</v>
-      </c>
-      <c r="F87" s="119"/>
-      <c r="G87" s="142" t="s">
-        <v>146</v>
-      </c>
-      <c r="H87" s="142"/>
-      <c r="I87" s="92"/>
+        <v>191</v>
+      </c>
+      <c r="D87" s="93" t="s">
+        <v>315</v>
+      </c>
+      <c r="F87" s="117"/>
+      <c r="G87" s="147" t="s">
+        <v>140</v>
+      </c>
+      <c r="H87" s="147"/>
+      <c r="I87" s="91"/>
       <c r="J87" s="16"/>
       <c r="K87" s="15"/>
     </row>
     <row r="88" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A88" s="129"/>
-      <c r="B88" s="123" t="s">
-        <v>505</v>
+      <c r="A88" s="180"/>
+      <c r="B88" s="121" t="s">
+        <v>462</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="D88" s="95"/>
-      <c r="E88" s="94" t="s">
-        <v>338</v>
-      </c>
-      <c r="F88" s="119"/>
-      <c r="G88" s="145" t="s">
+        <v>256</v>
+      </c>
+      <c r="D88" s="94"/>
+      <c r="E88" s="93" t="s">
+        <v>316</v>
+      </c>
+      <c r="F88" s="117"/>
+      <c r="G88" s="164" t="s">
         <v>83</v>
       </c>
-      <c r="H88" s="145"/>
-      <c r="I88" s="92"/>
+      <c r="H88" s="164"/>
+      <c r="I88" s="91"/>
       <c r="J88" s="16"/>
       <c r="K88" s="15"/>
     </row>
     <row r="89" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A89" s="129"/>
+      <c r="A89" s="180"/>
       <c r="B89" s="59"/>
       <c r="C89" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="D89" s="125" t="s">
-        <v>458</v>
-      </c>
-      <c r="E89" s="125"/>
-      <c r="F89" s="119"/>
-      <c r="G89" s="145" t="s">
+        <v>257</v>
+      </c>
+      <c r="D89" s="144" t="s">
+        <v>471</v>
+      </c>
+      <c r="E89" s="143"/>
+      <c r="F89" s="117"/>
+      <c r="G89" s="164" t="s">
         <v>84</v>
       </c>
-      <c r="H89" s="145"/>
-      <c r="I89" s="92"/>
+      <c r="H89" s="164"/>
+      <c r="I89" s="91"/>
       <c r="J89" s="16"/>
       <c r="K89" s="15"/>
     </row>
     <row r="90" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A90" s="129"/>
+      <c r="A90" s="180"/>
       <c r="B90" s="81"/>
       <c r="C90" s="79" t="s">
-        <v>276</v>
-      </c>
-      <c r="D90" s="125" t="s">
-        <v>460</v>
-      </c>
-      <c r="E90" s="125"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="97"/>
-      <c r="H90" s="97"/>
-      <c r="I90" s="92"/>
+        <v>260</v>
+      </c>
+      <c r="D90" s="143" t="s">
+        <v>429</v>
+      </c>
+      <c r="E90" s="143"/>
+      <c r="F90" s="117"/>
+      <c r="G90" s="130"/>
+      <c r="H90" s="96"/>
+      <c r="I90" s="91"/>
       <c r="J90" s="16"/>
       <c r="K90" s="15"/>
     </row>
     <row r="91" spans="1:11" s="17" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A91" s="129"/>
+      <c r="A91" s="180"/>
       <c r="B91" s="81"/>
       <c r="C91" s="79" t="s">
-        <v>275</v>
-      </c>
-      <c r="D91" s="130" t="s">
-        <v>459</v>
-      </c>
-      <c r="E91" s="130"/>
+        <v>259</v>
+      </c>
+      <c r="D91" s="178" t="s">
+        <v>428</v>
+      </c>
+      <c r="E91" s="178"/>
       <c r="F91" s="77"/>
       <c r="G91" s="61"/>
       <c r="H91" s="61"/>
@@ -4858,13 +4879,13 @@
       <c r="K91" s="15"/>
     </row>
     <row r="92" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A92" s="129"/>
+      <c r="A92" s="180"/>
       <c r="B92" s="60"/>
       <c r="C92" s="59"/>
-      <c r="D92" s="136" t="s">
-        <v>497</v>
-      </c>
-      <c r="E92" s="136"/>
+      <c r="D92" s="169" t="s">
+        <v>459</v>
+      </c>
+      <c r="E92" s="169"/>
       <c r="F92" s="77"/>
       <c r="G92" s="61"/>
       <c r="H92" s="78"/>
@@ -4873,13 +4894,13 @@
       <c r="K92" s="15"/>
     </row>
     <row r="93" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A93" s="129"/>
+      <c r="A93" s="180"/>
       <c r="B93" s="86"/>
       <c r="C93" s="59"/>
-      <c r="D93" s="152" t="s">
-        <v>461</v>
-      </c>
-      <c r="E93" s="152"/>
+      <c r="D93" s="169" t="s">
+        <v>507</v>
+      </c>
+      <c r="E93" s="169"/>
       <c r="F93" s="77"/>
       <c r="G93" s="61"/>
       <c r="H93" s="55"/>
@@ -4888,7 +4909,7 @@
       <c r="K93" s="15"/>
     </row>
     <row r="94" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A94" s="129"/>
+      <c r="A94" s="180"/>
       <c r="B94" s="60"/>
       <c r="C94" s="59"/>
       <c r="D94" s="89"/>
@@ -4914,7 +4935,7 @@
       <c r="K95" s="9"/>
     </row>
     <row r="96" spans="1:11" ht="21.75" customHeight="1">
-      <c r="A96" s="128" t="s">
+      <c r="A96" s="179" t="s">
         <v>19</v>
       </c>
       <c r="B96" s="81" t="s">
@@ -4925,261 +4946,261 @@
       </c>
       <c r="D96" s="56"/>
       <c r="E96" s="56"/>
-      <c r="F96" s="153" t="s">
-        <v>495</v>
-      </c>
-      <c r="G96" s="154"/>
+      <c r="F96" s="170" t="s">
+        <v>467</v>
+      </c>
+      <c r="G96" s="171"/>
       <c r="H96" s="19"/>
-      <c r="I96" s="146"/>
-      <c r="J96" s="147"/>
+      <c r="I96" s="165"/>
+      <c r="J96" s="166"/>
       <c r="K96" s="20"/>
     </row>
     <row r="97" spans="1:11" ht="30" customHeight="1">
-      <c r="A97" s="129"/>
-      <c r="B97" s="92" t="s">
-        <v>288</v>
-      </c>
-      <c r="C97" s="92" t="s">
-        <v>289</v>
-      </c>
-      <c r="D97" s="93" t="s">
-        <v>259</v>
-      </c>
-      <c r="E97" s="94" t="s">
-        <v>342</v>
-      </c>
-      <c r="F97" s="101"/>
-      <c r="G97" s="122"/>
+      <c r="A97" s="180"/>
+      <c r="B97" s="91" t="s">
+        <v>272</v>
+      </c>
+      <c r="C97" s="91" t="s">
+        <v>273</v>
+      </c>
+      <c r="D97" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="E97" s="93" t="s">
+        <v>320</v>
+      </c>
+      <c r="F97" s="100"/>
+      <c r="G97" s="120"/>
       <c r="H97" s="19"/>
       <c r="I97" s="22"/>
       <c r="J97" s="20"/>
       <c r="K97" s="20"/>
     </row>
     <row r="98" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A98" s="129"/>
-      <c r="B98" s="92" t="s">
-        <v>290</v>
-      </c>
-      <c r="C98" s="92" t="s">
-        <v>485</v>
-      </c>
-      <c r="D98" s="93" t="s">
-        <v>291</v>
-      </c>
-      <c r="E98" s="92"/>
-      <c r="F98" s="101"/>
-      <c r="G98" s="108"/>
+      <c r="A98" s="180"/>
+      <c r="B98" s="91" t="s">
+        <v>274</v>
+      </c>
+      <c r="C98" s="91" t="s">
+        <v>448</v>
+      </c>
+      <c r="D98" s="92" t="s">
+        <v>275</v>
+      </c>
+      <c r="E98" s="91"/>
+      <c r="F98" s="100"/>
+      <c r="G98" s="106"/>
       <c r="H98" s="19"/>
       <c r="I98" s="22"/>
       <c r="J98" s="20"/>
       <c r="K98" s="20"/>
     </row>
     <row r="99" spans="1:11" ht="30" customHeight="1">
-      <c r="A99" s="129"/>
-      <c r="B99" s="92" t="s">
-        <v>292</v>
-      </c>
-      <c r="C99" s="92" t="s">
-        <v>293</v>
-      </c>
-      <c r="D99" s="93" t="s">
-        <v>424</v>
-      </c>
-      <c r="E99" s="92"/>
-      <c r="F99" s="101"/>
-      <c r="G99" s="108"/>
+      <c r="A99" s="180"/>
+      <c r="B99" s="91" t="s">
+        <v>276</v>
+      </c>
+      <c r="C99" s="91" t="s">
+        <v>277</v>
+      </c>
+      <c r="D99" s="92" t="s">
+        <v>400</v>
+      </c>
+      <c r="E99" s="91"/>
+      <c r="F99" s="100"/>
+      <c r="G99" s="106"/>
       <c r="H99" s="19"/>
       <c r="I99" s="22"/>
       <c r="J99" s="20"/>
       <c r="K99" s="20"/>
     </row>
     <row r="100" spans="1:11" ht="30" customHeight="1">
-      <c r="A100" s="129"/>
-      <c r="B100" s="92" t="s">
-        <v>294</v>
-      </c>
-      <c r="C100" s="92" t="s">
-        <v>295</v>
-      </c>
-      <c r="D100" s="95"/>
-      <c r="E100" s="97"/>
-      <c r="F100" s="101"/>
-      <c r="G100" s="108"/>
+      <c r="A100" s="180"/>
+      <c r="B100" s="91" t="s">
+        <v>278</v>
+      </c>
+      <c r="C100" s="91" t="s">
+        <v>279</v>
+      </c>
+      <c r="D100" s="94"/>
+      <c r="E100" s="96"/>
+      <c r="F100" s="100"/>
+      <c r="G100" s="106"/>
       <c r="H100" s="19"/>
       <c r="I100" s="22"/>
       <c r="J100" s="20"/>
       <c r="K100" s="20"/>
     </row>
     <row r="101" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A101" s="129"/>
-      <c r="B101" s="92" t="s">
-        <v>296</v>
-      </c>
-      <c r="C101" s="92" t="s">
-        <v>489</v>
-      </c>
-      <c r="D101" s="139" t="s">
-        <v>482</v>
-      </c>
-      <c r="E101" s="139"/>
-      <c r="F101" s="101"/>
-      <c r="G101" s="108"/>
+      <c r="A101" s="180"/>
+      <c r="B101" s="91" t="s">
+        <v>280</v>
+      </c>
+      <c r="C101" s="91" t="s">
+        <v>452</v>
+      </c>
+      <c r="D101" s="162" t="s">
+        <v>445</v>
+      </c>
+      <c r="E101" s="162"/>
+      <c r="F101" s="100"/>
+      <c r="G101" s="106"/>
       <c r="H101" s="19"/>
       <c r="I101" s="22"/>
       <c r="J101" s="20"/>
       <c r="K101" s="20"/>
     </row>
     <row r="102" spans="1:11" ht="27" customHeight="1">
-      <c r="A102" s="129"/>
-      <c r="B102" s="92" t="s">
-        <v>297</v>
-      </c>
-      <c r="C102" s="92" t="s">
-        <v>298</v>
-      </c>
-      <c r="D102" s="142" t="s">
-        <v>147</v>
-      </c>
-      <c r="E102" s="142"/>
-      <c r="F102" s="105"/>
-      <c r="G102" s="92"/>
+      <c r="A102" s="180"/>
+      <c r="B102" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="C102" s="91" t="s">
+        <v>282</v>
+      </c>
+      <c r="D102" s="147" t="s">
+        <v>141</v>
+      </c>
+      <c r="E102" s="147"/>
+      <c r="F102" s="104"/>
+      <c r="G102" s="91"/>
       <c r="H102" s="19"/>
       <c r="I102" s="22"/>
       <c r="J102" s="20"/>
       <c r="K102" s="20"/>
     </row>
     <row r="103" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A103" s="129"/>
-      <c r="B103" s="92" t="s">
-        <v>299</v>
-      </c>
-      <c r="C103" s="92" t="s">
-        <v>300</v>
-      </c>
-      <c r="D103" s="125" t="s">
-        <v>425</v>
-      </c>
-      <c r="E103" s="125"/>
-      <c r="F103" s="105"/>
-      <c r="G103" s="92"/>
+      <c r="A103" s="180"/>
+      <c r="B103" s="91" t="s">
+        <v>283</v>
+      </c>
+      <c r="C103" s="91" t="s">
+        <v>284</v>
+      </c>
+      <c r="D103" s="143" t="s">
+        <v>401</v>
+      </c>
+      <c r="E103" s="143"/>
+      <c r="F103" s="104"/>
+      <c r="G103" s="91"/>
       <c r="H103" s="18"/>
       <c r="I103" s="22"/>
       <c r="J103" s="22"/>
       <c r="K103" s="22"/>
     </row>
     <row r="104" spans="1:11" ht="29.25" customHeight="1">
-      <c r="A104" s="129"/>
-      <c r="B104" s="92" t="s">
-        <v>301</v>
-      </c>
-      <c r="C104" s="95"/>
-      <c r="D104" s="102"/>
-      <c r="E104" s="102"/>
-      <c r="F104" s="105"/>
-      <c r="G104" s="92"/>
+      <c r="A104" s="180"/>
+      <c r="B104" s="91" t="s">
+        <v>285</v>
+      </c>
+      <c r="C104" s="94"/>
+      <c r="D104" s="101"/>
+      <c r="E104" s="101"/>
+      <c r="F104" s="104"/>
+      <c r="G104" s="91"/>
       <c r="H104" s="18"/>
       <c r="I104" s="22"/>
       <c r="J104" s="22"/>
       <c r="K104" s="22"/>
     </row>
     <row r="105" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A105" s="129"/>
-      <c r="B105" s="92" t="s">
-        <v>302</v>
-      </c>
-      <c r="C105" s="95"/>
-      <c r="D105" s="125" t="s">
-        <v>466</v>
-      </c>
-      <c r="E105" s="125"/>
-      <c r="F105" s="105"/>
-      <c r="G105" s="101"/>
+      <c r="A105" s="180"/>
+      <c r="B105" s="91" t="s">
+        <v>286</v>
+      </c>
+      <c r="C105" s="94"/>
+      <c r="D105" s="173" t="s">
+        <v>432</v>
+      </c>
+      <c r="E105" s="173"/>
+      <c r="F105" s="104"/>
+      <c r="G105" s="100"/>
       <c r="H105" s="18"/>
       <c r="I105" s="22"/>
       <c r="J105" s="22"/>
       <c r="K105" s="22"/>
     </row>
     <row r="106" spans="1:11" ht="15" customHeight="1">
-      <c r="A106" s="129"/>
-      <c r="B106" s="95"/>
-      <c r="C106" s="92"/>
-      <c r="D106" s="131" t="s">
-        <v>491</v>
-      </c>
-      <c r="E106" s="132"/>
-      <c r="F106" s="105"/>
-      <c r="G106" s="92"/>
+      <c r="A106" s="180"/>
+      <c r="B106" s="94"/>
+      <c r="C106" s="91"/>
+      <c r="D106" s="155" t="s">
+        <v>454</v>
+      </c>
+      <c r="E106" s="156"/>
+      <c r="F106" s="104"/>
+      <c r="G106" s="91"/>
       <c r="H106" s="18"/>
       <c r="I106" s="22"/>
       <c r="J106" s="22"/>
       <c r="K106" s="22"/>
     </row>
     <row r="107" spans="1:11" ht="15" customHeight="1">
-      <c r="A107" s="129"/>
-      <c r="B107" s="92"/>
-      <c r="C107" s="92"/>
-      <c r="D107" s="131" t="s">
-        <v>492</v>
-      </c>
-      <c r="E107" s="132"/>
-      <c r="F107" s="105"/>
-      <c r="G107" s="92"/>
+      <c r="A107" s="180"/>
+      <c r="B107" s="91"/>
+      <c r="C107" s="91"/>
+      <c r="D107" s="155" t="s">
+        <v>455</v>
+      </c>
+      <c r="E107" s="156"/>
+      <c r="F107" s="104"/>
+      <c r="G107" s="91"/>
       <c r="H107" s="18"/>
       <c r="I107" s="22"/>
       <c r="J107" s="22"/>
       <c r="K107" s="22"/>
     </row>
     <row r="108" spans="1:11" ht="15" customHeight="1">
-      <c r="A108" s="129"/>
-      <c r="B108" s="131" t="s">
+      <c r="A108" s="180"/>
+      <c r="B108" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="C108" s="132"/>
-      <c r="F108" s="105"/>
-      <c r="G108" s="92"/>
+      <c r="C108" s="156"/>
+      <c r="F108" s="104"/>
+      <c r="G108" s="91"/>
       <c r="H108" s="18"/>
       <c r="I108" s="22"/>
       <c r="J108" s="22"/>
       <c r="K108" s="22"/>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" s="129"/>
-      <c r="B109" s="125" t="s">
-        <v>467</v>
-      </c>
-      <c r="C109" s="125"/>
-      <c r="D109" s="131" t="s">
-        <v>465</v>
-      </c>
-      <c r="E109" s="132"/>
-      <c r="F109" s="105"/>
-      <c r="G109" s="92"/>
+      <c r="A109" s="180"/>
+      <c r="B109" s="143" t="s">
+        <v>433</v>
+      </c>
+      <c r="C109" s="143"/>
+      <c r="D109" s="155" t="s">
+        <v>431</v>
+      </c>
+      <c r="E109" s="156"/>
+      <c r="F109" s="104"/>
+      <c r="G109" s="91"/>
       <c r="H109" s="18"/>
       <c r="I109" s="22"/>
       <c r="J109" s="22"/>
       <c r="K109" s="22"/>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" s="129"/>
-      <c r="B110" s="125" t="s">
-        <v>150</v>
-      </c>
-      <c r="C110" s="125"/>
-      <c r="D110" s="95"/>
-      <c r="E110" s="92"/>
-      <c r="F110" s="105"/>
-      <c r="G110" s="92"/>
+      <c r="A110" s="180"/>
+      <c r="B110" s="143" t="s">
+        <v>144</v>
+      </c>
+      <c r="C110" s="143"/>
+      <c r="D110" s="94"/>
+      <c r="E110" s="91"/>
+      <c r="F110" s="104"/>
+      <c r="G110" s="91"/>
       <c r="H110" s="18"/>
       <c r="I110" s="22"/>
       <c r="J110" s="22"/>
       <c r="K110" s="22"/>
     </row>
     <row r="111" spans="1:11">
-      <c r="A111" s="129"/>
-      <c r="B111" s="130" t="s">
-        <v>96</v>
-      </c>
-      <c r="C111" s="130"/>
+      <c r="A111" s="180"/>
+      <c r="B111" s="143" t="s">
+        <v>91</v>
+      </c>
+      <c r="C111" s="143"/>
       <c r="D111" s="55"/>
       <c r="E111" s="23"/>
       <c r="F111" s="87"/>
@@ -5190,14 +5211,14 @@
       <c r="K111" s="22"/>
     </row>
     <row r="112" spans="1:11" s="17" customFormat="1">
-      <c r="A112" s="129"/>
-      <c r="B112" s="136" t="s">
-        <v>500</v>
-      </c>
-      <c r="C112" s="136"/>
+      <c r="A112" s="180"/>
+      <c r="B112" s="143" t="s">
+        <v>461</v>
+      </c>
+      <c r="C112" s="143"/>
       <c r="D112" s="56"/>
       <c r="E112" s="76" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="F112" s="87"/>
       <c r="G112" s="81"/>
@@ -5207,11 +5228,11 @@
       <c r="K112" s="22"/>
     </row>
     <row r="113" spans="1:11" s="17" customFormat="1">
-      <c r="A113" s="129"/>
-      <c r="B113" s="130" t="s">
-        <v>468</v>
-      </c>
-      <c r="C113" s="130"/>
+      <c r="A113" s="180"/>
+      <c r="B113" s="144" t="s">
+        <v>470</v>
+      </c>
+      <c r="C113" s="143"/>
       <c r="D113" s="56"/>
       <c r="E113" s="76"/>
       <c r="F113" s="87"/>
@@ -5222,11 +5243,11 @@
       <c r="K113" s="22"/>
     </row>
     <row r="114" spans="1:11" s="17" customFormat="1">
-      <c r="A114" s="129"/>
-      <c r="B114" s="130" t="s">
-        <v>151</v>
-      </c>
-      <c r="C114" s="130"/>
+      <c r="A114" s="180"/>
+      <c r="B114" s="144" t="s">
+        <v>468</v>
+      </c>
+      <c r="C114" s="144"/>
       <c r="D114" s="56"/>
       <c r="E114" s="76"/>
       <c r="F114" s="87"/>
@@ -5237,11 +5258,11 @@
       <c r="K114" s="22"/>
     </row>
     <row r="115" spans="1:11" s="17" customFormat="1" ht="15" customHeight="1">
-      <c r="A115" s="129"/>
-      <c r="B115" s="136" t="s">
-        <v>501</v>
-      </c>
-      <c r="C115" s="136"/>
+      <c r="A115" s="180"/>
+      <c r="B115" s="144" t="s">
+        <v>487</v>
+      </c>
+      <c r="C115" s="144"/>
       <c r="D115" s="56"/>
       <c r="E115" s="76"/>
       <c r="F115" s="87"/>
@@ -5252,11 +5273,11 @@
       <c r="K115" s="22"/>
     </row>
     <row r="116" spans="1:11" s="17" customFormat="1">
-      <c r="A116" s="129"/>
-      <c r="B116" s="130" t="s">
-        <v>97</v>
-      </c>
-      <c r="C116" s="130"/>
+      <c r="A116" s="180"/>
+      <c r="B116" s="173" t="s">
+        <v>486</v>
+      </c>
+      <c r="C116" s="173"/>
       <c r="D116" s="56"/>
       <c r="E116" s="76"/>
       <c r="F116" s="87"/>
@@ -5266,7 +5287,7 @@
       <c r="J116" s="22"/>
       <c r="K116" s="22"/>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" ht="7.5" customHeight="1">
       <c r="A117" s="8"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -5294,33 +5315,33 @@
     </row>
     <row r="119" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B119" s="48" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="C119" s="48" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="E119" s="49" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="F119" s="49" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="H119" s="49" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="I119" s="49" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
     </row>
     <row r="120" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B120" s="55" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C120" s="55" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E120" s="50" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="F120" s="66" t="s">
         <v>58</v>
@@ -5334,33 +5355,33 @@
     </row>
     <row r="121" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B121" s="55" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C121" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="E121" s="50" t="s">
-        <v>363</v>
+        <v>95</v>
+      </c>
+      <c r="E121" s="133" t="s">
+        <v>341</v>
       </c>
       <c r="F121" s="66" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="H121" s="39" t="s">
         <v>79</v>
       </c>
       <c r="I121" s="68" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
     </row>
     <row r="122" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B122" s="55" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C122" s="55" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E122" s="50" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="F122" s="66" t="s">
         <v>59</v>
@@ -5374,16 +5395,16 @@
     </row>
     <row r="123" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B123" s="55" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C123" s="55" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E123" s="50" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="F123" s="66" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="H123" s="39" t="s">
         <v>76</v>
@@ -5394,10 +5415,10 @@
     </row>
     <row r="124" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B124" s="55" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C124" s="55" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E124" s="50" t="s">
         <v>60</v>
@@ -5407,295 +5428,295 @@
       </c>
       <c r="H124" s="51"/>
       <c r="I124" s="69" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
       <c r="B125" s="55" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C125" s="55" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E125" s="50" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="F125" s="66" t="s">
         <v>62</v>
       </c>
       <c r="H125" s="41" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="I125" s="70" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
       <c r="B126" s="55" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C126" s="55" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E126" s="50" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="F126" s="66" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="H126" s="41" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="I126" s="70" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
     </row>
     <row r="127" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
       <c r="B127" s="55" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C127" s="55" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E127" s="50" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="F127" s="66" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="H127" s="52"/>
       <c r="I127" s="71" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B128" s="55" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C128" s="55" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E128" s="50" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="F128" s="66" t="s">
         <v>63</v>
       </c>
       <c r="H128" s="53"/>
       <c r="I128" s="68" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
     </row>
     <row r="129" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B129" s="55" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C129" s="55" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E129" s="50" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="F129" s="66" t="s">
         <v>64</v>
       </c>
       <c r="H129" s="40" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="I129" s="68" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
     </row>
     <row r="130" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B130" s="55" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C130" s="55" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E130" s="50" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="F130" s="66" t="s">
         <v>65</v>
       </c>
       <c r="H130" s="40" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="I130" s="68" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
     </row>
     <row r="131" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B131" s="55" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C131" s="55" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E131" s="50" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="F131" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H131" s="53"/>
       <c r="I131" s="68" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
     </row>
     <row r="132" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B132" s="55" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C132" s="55" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E132" s="50" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="F132" s="66" t="s">
         <v>67</v>
       </c>
       <c r="H132" s="54" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="I132" s="72" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
     </row>
     <row r="133" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B133" s="55" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C133" s="55" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E133" s="50" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="F133" s="66" t="s">
         <v>68</v>
       </c>
       <c r="H133" s="54" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="I133" s="72" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="55" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C134" s="55" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E134" s="50" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="F134" s="66" t="s">
         <v>69</v>
       </c>
       <c r="H134" s="55" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="I134" s="66" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="55" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C135" s="55" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E135" s="50" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="F135" s="66" t="s">
         <v>70</v>
       </c>
       <c r="H135" s="55" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="I135" s="66" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="55" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C136" s="55" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E136" s="50" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="F136" s="66" t="s">
         <v>71</v>
       </c>
       <c r="H136" s="55" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="I136" s="66" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="2:9">
       <c r="B137" s="55" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C137" s="55" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E137" s="50" t="s">
         <v>72</v>
       </c>
       <c r="F137" s="66" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="H137" s="50" t="s">
         <v>73</v>
       </c>
       <c r="I137" s="56" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
     </row>
     <row r="138" spans="2:9">
       <c r="B138" s="55" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C138" s="55" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E138" s="50" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="F138" s="66" t="s">
+        <v>362</v>
+      </c>
+      <c r="H138" s="50" t="s">
         <v>384</v>
       </c>
-      <c r="H138" s="50" t="s">
-        <v>406</v>
-      </c>
       <c r="I138" s="56" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="2:9">
       <c r="B139" s="58" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C139" s="58" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E139" s="55" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="F139" s="66" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="H139" s="46" t="s">
         <v>52</v>
@@ -5712,10 +5733,10 @@
         <v>43</v>
       </c>
       <c r="E140" s="55" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="F140" s="66" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="H140" s="45" t="s">
         <v>54</v>
@@ -5732,10 +5753,10 @@
         <v>45</v>
       </c>
       <c r="E141" s="55" t="s">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="F141" s="66" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="H141" s="46" t="s">
         <v>56</v>
@@ -5752,10 +5773,10 @@
         <v>47</v>
       </c>
       <c r="E142" s="55" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="F142" s="66" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="H142" s="47" t="s">
         <v>29</v>
@@ -5772,10 +5793,10 @@
         <v>49</v>
       </c>
       <c r="E143" s="55" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="F143" s="66" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="H143" s="47" t="s">
         <v>30</v>
@@ -5792,10 +5813,10 @@
         <v>51</v>
       </c>
       <c r="E144" s="55" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="F144" s="66" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="H144" s="47" t="s">
         <v>31</v>
@@ -5812,10 +5833,10 @@
         <v>40</v>
       </c>
       <c r="E145" s="55" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="F145" s="66" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="H145" s="47" t="s">
         <v>32</v>
@@ -6022,57 +6043,47 @@
     </row>
   </sheetData>
   <mergeCells count="116">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A22:A36"/>
-    <mergeCell ref="F5:F16"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="A5:A20"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="F26:F39"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="F42:F51"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="A58:A75"/>
+    <mergeCell ref="A77:A94"/>
+    <mergeCell ref="A96:A116"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="A42:A56"/>
+    <mergeCell ref="D101:E101"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="D109:E109"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
     <mergeCell ref="G86:H86"/>
     <mergeCell ref="D54:E54"/>
     <mergeCell ref="I96:J96"/>
@@ -6097,47 +6108,57 @@
     <mergeCell ref="H71:I71"/>
     <mergeCell ref="D72:E72"/>
     <mergeCell ref="H82:I82"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D102:E102"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="D105:E105"/>
-    <mergeCell ref="D109:E109"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="A58:A75"/>
-    <mergeCell ref="A77:A94"/>
-    <mergeCell ref="A96:A116"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D92:E92"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="D103:E103"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="A42:A56"/>
-    <mergeCell ref="D101:E101"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="D106:E106"/>
-    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="A5:A20"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="F26:F39"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="F42:F51"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A22:A36"/>
+    <mergeCell ref="F5:F16"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <pageMargins left="0.24" right="0.17" top="0.17" bottom="0.28000000000000003" header="0.17" footer="0.16"/>
   <pageSetup scale="60" orientation="landscape" r:id="rId1"/>

--- a/raw/time_tables/B.Tech 62 (btech-62)/5/1.xlsx
+++ b/raw/time_tables/B.Tech 62 (btech-62)/5/1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508FB2A6-4CF7-40F9-98AC-E9A3D6F5038B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B15C18-EEF3-469D-9E25-C6338952D675}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="511">
   <si>
     <t>8-9AM</t>
   </si>
@@ -237,9 +237,6 @@
   </si>
   <si>
     <t>24B11CS353</t>
-  </si>
-  <si>
-    <t>P(25BT312)-/NF1, RD</t>
   </si>
   <si>
     <t>Genetic Engineering Lab</t>
@@ -496,9 +493,6 @@
     <t>Lminor(24B11CS353)-CS3/AMS</t>
   </si>
   <si>
-    <t>L(25BT311)-CS4/NF1, DKP</t>
-  </si>
-  <si>
     <t>LB7,B8, B14(HS311)- G2/NAM</t>
   </si>
   <si>
@@ -622,9 +616,6 @@
     <t>LA15-A16(25HS311)-CS4/MSU</t>
   </si>
   <si>
-    <t>L(25BT311)-CS1/NF1, DKP</t>
-  </si>
-  <si>
     <t>Lminor(24B11CS353)-CS4/AMS</t>
   </si>
   <si>
@@ -1220,9 +1211,6 @@
   </si>
   <si>
     <t>LA7-A8-A10(EC312)-G9/RB</t>
-  </si>
-  <si>
-    <t>P(25BT312)-Bioinfo/NF1, RD</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -1559,6 +1547,21 @@
   </si>
   <si>
     <t>LA15,A16(HS311)-F8 /NAM</t>
+  </si>
+  <si>
+    <t>L(25BT311)-CS4/SN, DKP</t>
+  </si>
+  <si>
+    <t>L(25BT311)-CS1/SN, DKP</t>
+  </si>
+  <si>
+    <t>P(25BT312)-/SN, RD</t>
+  </si>
+  <si>
+    <t>L(25BT311)-CS1/SN1, DKP</t>
+  </si>
+  <si>
+    <t>P(25BT312)-Bioinfo/SN, RD</t>
   </si>
 </sst>
 </file>
@@ -3049,22 +3052,22 @@
       </c>
       <c r="C5" s="143"/>
       <c r="D5" s="123" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E5" s="123" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F5" s="140" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="123" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H5" s="123" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="I5" s="123" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J5" s="143" t="s">
         <v>28</v>
@@ -3075,26 +3078,26 @@
       <c r="A6" s="153"/>
       <c r="B6" s="123"/>
       <c r="C6" s="123" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D6" s="123" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E6" s="123" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F6" s="141"/>
       <c r="G6" s="123" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H6" s="123" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I6" s="123" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J6" s="123" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K6" s="123"/>
     </row>
@@ -3102,20 +3105,20 @@
       <c r="A7" s="153"/>
       <c r="B7" s="94"/>
       <c r="C7" s="126" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D7" s="123" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F7" s="141"/>
       <c r="G7" s="123" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H7" s="123" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I7" s="123" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J7" s="123"/>
       <c r="K7" s="123"/>
@@ -3123,24 +3126,24 @@
     <row r="8" spans="1:11" ht="27.75" customHeight="1">
       <c r="A8" s="153"/>
       <c r="B8" s="144" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C8" s="144"/>
       <c r="D8" s="123" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E8" s="123" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8" s="141"/>
       <c r="G8" s="92" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H8" s="92" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I8" s="123" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J8" s="123"/>
       <c r="K8" s="123"/>
@@ -3148,24 +3151,24 @@
     <row r="9" spans="1:11" ht="27.75" customHeight="1">
       <c r="A9" s="153"/>
       <c r="B9" s="143" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="143"/>
       <c r="D9" s="123" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E9" s="92" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F9" s="141"/>
       <c r="G9" s="130" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H9" s="128" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I9" s="123" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J9" s="123"/>
       <c r="K9" s="123"/>
@@ -3173,22 +3176,22 @@
     <row r="10" spans="1:11" ht="27.75" customHeight="1">
       <c r="A10" s="153"/>
       <c r="B10" s="143" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C10" s="143"/>
       <c r="D10" s="123" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E10" s="92" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F10" s="141"/>
       <c r="G10" s="94"/>
       <c r="H10" s="128" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I10" s="128" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="J10" s="123"/>
       <c r="K10" s="123"/>
@@ -3196,18 +3199,18 @@
     <row r="11" spans="1:11" ht="27.75" customHeight="1">
       <c r="A11" s="153"/>
       <c r="B11" s="144" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C11" s="144"/>
       <c r="D11" s="123" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E11" s="128" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F11" s="141"/>
       <c r="G11" s="143" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="H11" s="143"/>
       <c r="J11" s="123"/>
@@ -3216,22 +3219,22 @@
     <row r="12" spans="1:11" ht="27.75" customHeight="1">
       <c r="A12" s="153"/>
       <c r="B12" s="143" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="143"/>
       <c r="D12" s="128" t="s">
+        <v>290</v>
+      </c>
+      <c r="E12" s="128" t="s">
         <v>293</v>
-      </c>
-      <c r="E12" s="128" t="s">
-        <v>296</v>
       </c>
       <c r="F12" s="141"/>
       <c r="G12" s="155" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="H12" s="156"/>
       <c r="I12" s="145" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J12" s="146"/>
       <c r="K12" s="123"/>
@@ -3239,19 +3242,19 @@
     <row r="13" spans="1:11" ht="27.75" customHeight="1">
       <c r="A13" s="153"/>
       <c r="B13" s="144" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C13" s="143"/>
       <c r="E13" s="128" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F13" s="141"/>
       <c r="G13" s="145" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H13" s="146"/>
       <c r="I13" s="145" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J13" s="146"/>
       <c r="K13" s="123"/>
@@ -3259,18 +3262,18 @@
     <row r="14" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
       <c r="A14" s="153"/>
       <c r="B14" s="144" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C14" s="144"/>
       <c r="D14" s="128" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E14" s="128" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F14" s="141"/>
       <c r="G14" s="155" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H14" s="156"/>
       <c r="I14" s="96"/>
@@ -3280,11 +3283,11 @@
     <row r="15" spans="1:11" s="17" customFormat="1" ht="27.75" customHeight="1">
       <c r="A15" s="153"/>
       <c r="B15" s="144" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C15" s="144"/>
       <c r="D15" s="155" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E15" s="156"/>
       <c r="F15" s="141"/>
@@ -3297,17 +3300,17 @@
     <row r="16" spans="1:11" ht="27.75" customHeight="1">
       <c r="A16" s="153"/>
       <c r="B16" s="144" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C16" s="144"/>
       <c r="D16" s="144" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E16" s="144"/>
       <c r="F16" s="142"/>
       <c r="G16" s="97"/>
       <c r="H16" s="143" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="I16" s="143"/>
       <c r="J16" s="123"/>
@@ -3320,7 +3323,7 @@
       <c r="D17" s="155"/>
       <c r="E17" s="156"/>
       <c r="F17" s="127" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="G17" s="97"/>
       <c r="H17" s="143"/>
@@ -3333,14 +3336,14 @@
       <c r="B18" s="94"/>
       <c r="C18" s="94"/>
       <c r="D18" s="147" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E18" s="147"/>
       <c r="F18" s="127" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G18" s="143" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H18" s="143"/>
       <c r="I18" s="96"/>
@@ -3352,11 +3355,11 @@
       <c r="B19" s="94"/>
       <c r="C19" s="94"/>
       <c r="D19" s="144" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E19" s="144"/>
       <c r="F19" s="127" t="s">
-        <v>159</v>
+        <v>506</v>
       </c>
       <c r="G19" s="143"/>
       <c r="H19" s="143"/>
@@ -3369,7 +3372,7 @@
       <c r="B20" s="99"/>
       <c r="C20" s="99"/>
       <c r="D20" s="144" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E20" s="144"/>
       <c r="F20" s="100"/>
@@ -3405,16 +3408,16 @@
       <c r="D22" s="94"/>
       <c r="E22" s="94"/>
       <c r="F22" s="93" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G22" s="91" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H22" s="91" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="I22" s="91" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
@@ -3423,80 +3426,80 @@
         <v>41</v>
       </c>
       <c r="C23" s="91" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D23" s="91" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E23" s="129" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F23" s="98" t="s">
-        <v>201</v>
+        <v>507</v>
       </c>
       <c r="G23" s="91" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H23" s="91" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I23" s="91" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
       <c r="A24" s="138"/>
       <c r="B24" s="23" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C24" s="91" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D24" s="91" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" s="91" t="s">
+        <v>194</v>
+      </c>
+      <c r="F24" s="98" t="s">
+        <v>430</v>
+      </c>
+      <c r="G24" s="132" t="s">
         <v>195</v>
       </c>
-      <c r="E24" s="91" t="s">
-        <v>196</v>
-      </c>
-      <c r="F24" s="98" t="s">
-        <v>434</v>
-      </c>
-      <c r="G24" s="132" t="s">
-        <v>197</v>
-      </c>
       <c r="H24" s="132" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J24" s="104" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K24" s="106"/>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
       <c r="A25" s="138"/>
       <c r="B25" s="23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C25" s="91" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D25" s="91" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E25" s="122" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F25" s="98" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G25" s="91" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H25" s="93" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="I25" s="91" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J25" s="107"/>
       <c r="K25" s="106"/>
@@ -3504,25 +3507,25 @@
     <row r="26" spans="1:11" s="17" customFormat="1" ht="30" customHeight="1">
       <c r="A26" s="138"/>
       <c r="B26" s="23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C26" s="91" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D26" s="91" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E26" s="91" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F26" s="158" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G26" s="91" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I26" s="91" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J26" s="107"/>
       <c r="K26" s="106"/>
@@ -3530,26 +3533,26 @@
     <row r="27" spans="1:11" s="17" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="138"/>
       <c r="B27" s="23" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C27" s="129" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D27" s="93" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E27" s="93" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F27" s="159"/>
       <c r="G27" s="91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H27" s="105" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="I27" s="105" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J27" s="107"/>
       <c r="K27" s="106"/>
@@ -3557,23 +3560,23 @@
     <row r="28" spans="1:11" ht="30" customHeight="1">
       <c r="A28" s="138"/>
       <c r="B28" s="23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C28" s="91" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D28" s="91" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E28" s="91" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F28" s="159"/>
       <c r="G28" s="91" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H28" s="93" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J28" s="107"/>
       <c r="K28" s="106"/>
@@ -3581,16 +3584,16 @@
     <row r="29" spans="1:11" ht="30" customHeight="1">
       <c r="A29" s="138"/>
       <c r="B29" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C29" s="91" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D29" s="92" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E29" s="93" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F29" s="159"/>
       <c r="H29" s="97"/>
@@ -3601,16 +3604,16 @@
     <row r="30" spans="1:11" ht="30" customHeight="1">
       <c r="A30" s="138"/>
       <c r="B30" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C30" s="91" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D30" s="105" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E30" s="93" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F30" s="159"/>
       <c r="H30" s="97"/>
@@ -3621,18 +3624,18 @@
     <row r="31" spans="1:11" ht="30" customHeight="1">
       <c r="A31" s="138"/>
       <c r="B31" s="23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C31" s="91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D31" s="93" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F31" s="159"/>
       <c r="G31" s="101"/>
       <c r="H31" s="144" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="I31" s="144"/>
       <c r="J31" s="107"/>
@@ -3641,18 +3644,18 @@
     <row r="32" spans="1:11" ht="30" customHeight="1">
       <c r="A32" s="138"/>
       <c r="B32" s="23" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C32" s="91" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D32" s="108" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E32" s="97"/>
       <c r="F32" s="159"/>
       <c r="G32" s="147" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H32" s="147"/>
       <c r="I32" s="97"/>
@@ -3662,18 +3665,18 @@
     <row r="33" spans="1:11" ht="30" customHeight="1">
       <c r="A33" s="138"/>
       <c r="B33" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C33" s="91" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D33" s="93" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E33" s="97"/>
       <c r="F33" s="159"/>
       <c r="G33" s="147" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H33" s="147"/>
       <c r="I33" s="106"/>
@@ -3684,10 +3687,10 @@
       <c r="A34" s="138"/>
       <c r="B34" s="55"/>
       <c r="C34" s="91" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D34" s="147" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E34" s="147"/>
       <c r="F34" s="159"/>
@@ -3699,13 +3702,13 @@
       <c r="A35" s="138"/>
       <c r="B35" s="55"/>
       <c r="C35" s="91" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D35" s="94"/>
       <c r="E35" s="94"/>
       <c r="F35" s="159"/>
       <c r="G35" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H35" s="157"/>
       <c r="I35" s="97"/>
@@ -3716,16 +3719,16 @@
       <c r="A36" s="139"/>
       <c r="B36" s="23"/>
       <c r="C36" s="91" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D36" s="143" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E36" s="143"/>
       <c r="F36" s="159"/>
       <c r="G36" s="97"/>
       <c r="H36" s="147" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I36" s="147"/>
       <c r="J36" s="104"/>
@@ -3740,7 +3743,7 @@
       <c r="F37" s="159"/>
       <c r="G37" s="96"/>
       <c r="H37" s="163" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="I37" s="163"/>
       <c r="J37" s="104"/>
@@ -3751,13 +3754,13 @@
       <c r="B38" s="81"/>
       <c r="C38" s="94"/>
       <c r="D38" s="143" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E38" s="143"/>
       <c r="F38" s="159"/>
       <c r="G38" s="94"/>
       <c r="H38" s="144" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="I38" s="144"/>
       <c r="J38" s="104"/>
@@ -3768,13 +3771,13 @@
       <c r="B39" s="64"/>
       <c r="C39" s="109"/>
       <c r="D39" s="176" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E39" s="177"/>
       <c r="F39" s="160"/>
       <c r="G39" s="100"/>
       <c r="H39" s="155" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="I39" s="156"/>
       <c r="J39" s="104"/>
@@ -3785,7 +3788,7 @@
       <c r="B40" s="18"/>
       <c r="C40" s="34"/>
       <c r="D40" s="174" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E40" s="175"/>
       <c r="F40" s="81"/>
@@ -3811,22 +3814,22 @@
         <v>14</v>
       </c>
       <c r="B42" s="65" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C42" s="91" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="91" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E42" s="91" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F42" s="162" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G42" s="91" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H42" s="143" t="s">
         <v>24</v>
@@ -3840,55 +3843,55 @@
     <row r="43" spans="1:11" ht="28.5" customHeight="1">
       <c r="A43" s="183"/>
       <c r="B43" s="65" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C43" s="91" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D43" s="91" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E43" s="91" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F43" s="162"/>
       <c r="G43" s="91" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H43" s="93" t="s">
+        <v>221</v>
+      </c>
+      <c r="I43" s="91" t="s">
         <v>224</v>
       </c>
-      <c r="I43" s="91" t="s">
-        <v>227</v>
-      </c>
       <c r="J43" s="104" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K43" s="91"/>
     </row>
     <row r="44" spans="1:11" ht="28.5" customHeight="1">
       <c r="A44" s="183"/>
       <c r="B44" s="65" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C44" s="91" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D44" s="110" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E44" s="93" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F44" s="162"/>
       <c r="G44" s="92" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H44" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="I44" s="91" t="s">
         <v>225</v>
-      </c>
-      <c r="I44" s="91" t="s">
-        <v>228</v>
       </c>
       <c r="J44" s="104"/>
       <c r="K44" s="91"/>
@@ -3897,23 +3900,23 @@
       <c r="A45" s="183"/>
       <c r="B45" s="61"/>
       <c r="C45" s="91" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D45" s="91" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E45" s="91" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F45" s="162"/>
       <c r="G45" s="91" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H45" s="92" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I45" s="93" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J45" s="104"/>
       <c r="K45" s="91"/>
@@ -3922,15 +3925,15 @@
       <c r="A46" s="183"/>
       <c r="B46" s="61"/>
       <c r="C46" s="91" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D46" s="131"/>
       <c r="E46" s="91" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F46" s="162"/>
       <c r="G46" s="91" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H46" s="94"/>
       <c r="I46" s="94"/>
@@ -3939,13 +3942,13 @@
       <c r="A47" s="183"/>
       <c r="B47" s="61"/>
       <c r="C47" s="91" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D47" s="91" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E47" s="91" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F47" s="162"/>
       <c r="G47" s="101"/>
@@ -3956,13 +3959,13 @@
       <c r="A48" s="183"/>
       <c r="B48" s="59"/>
       <c r="C48" s="91" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D48" s="93" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E48" s="128" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F48" s="162"/>
       <c r="H48" s="94"/>
@@ -3974,18 +3977,18 @@
       <c r="A49" s="183"/>
       <c r="B49" s="83"/>
       <c r="C49" s="91" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D49" s="93" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E49" s="93" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F49" s="162"/>
       <c r="G49" s="97"/>
       <c r="H49" s="147" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="I49" s="147"/>
       <c r="J49" s="104"/>
@@ -3996,10 +3999,10 @@
       <c r="B50" s="83"/>
       <c r="C50" s="123"/>
       <c r="D50" s="93" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="E50" s="105" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F50" s="162"/>
       <c r="G50" s="97"/>
@@ -4012,16 +4015,16 @@
       <c r="A51" s="183"/>
       <c r="B51" s="83"/>
       <c r="C51" s="91" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E51" s="164"/>
       <c r="F51" s="162"/>
       <c r="G51" s="91"/>
       <c r="H51" s="143" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="I51" s="143"/>
       <c r="J51" s="104"/>
@@ -4031,18 +4034,18 @@
       <c r="A52" s="183"/>
       <c r="B52" s="83"/>
       <c r="C52" s="91" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D52" s="164" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E52" s="164"/>
       <c r="F52" s="91" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="G52" s="91"/>
       <c r="H52" s="143" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I52" s="143"/>
       <c r="J52" s="104"/>
@@ -4052,18 +4055,18 @@
       <c r="A53" s="183"/>
       <c r="B53" s="83"/>
       <c r="C53" s="91" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D53" s="143" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E53" s="143"/>
       <c r="F53" s="91" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G53" s="94"/>
       <c r="H53" s="144" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="I53" s="144"/>
       <c r="J53" s="91"/>
@@ -4073,18 +4076,18 @@
       <c r="A54" s="183"/>
       <c r="B54" s="83"/>
       <c r="C54" s="91" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D54" s="143" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E54" s="143"/>
       <c r="F54" s="143" t="s">
-        <v>74</v>
+        <v>508</v>
       </c>
       <c r="G54" s="143"/>
       <c r="H54" s="144" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="I54" s="144"/>
       <c r="J54" s="91"/>
@@ -4095,7 +4098,7 @@
       <c r="B55" s="83"/>
       <c r="C55" s="91"/>
       <c r="D55" s="147" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E55" s="147"/>
       <c r="F55" s="91"/>
@@ -4109,10 +4112,10 @@
       <c r="A56" s="183"/>
       <c r="B56" s="83"/>
       <c r="C56" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D56" s="143" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E56" s="143"/>
       <c r="F56" s="97"/>
@@ -4148,16 +4151,16 @@
       <c r="D58" s="100"/>
       <c r="E58" s="100"/>
       <c r="F58" s="172" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G58" s="123" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H58" s="92" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I58" s="123" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J58" s="161" t="s">
         <v>28</v>
@@ -4171,66 +4174,66 @@
         <v>41</v>
       </c>
       <c r="D59" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E59" s="157"/>
       <c r="F59" s="141"/>
       <c r="H59" s="123" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I59" s="123" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="29.25" customHeight="1" thickBot="1">
       <c r="A60" s="138"/>
       <c r="B60" s="91" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C60" s="111" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D60" s="123" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E60" s="129" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F60" s="141"/>
       <c r="G60" s="128" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I60" s="123" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J60" s="150" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K60" s="151"/>
     </row>
     <row r="61" spans="1:11" ht="29.25" customHeight="1">
       <c r="A61" s="138"/>
       <c r="B61" s="91" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C61" s="111" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D61" s="123" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E61" s="123" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F61" s="141"/>
       <c r="G61" s="123" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H61" s="123" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I61" s="113" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J61" s="112"/>
       <c r="K61" s="103"/>
@@ -4238,26 +4241,26 @@
     <row r="62" spans="1:11" ht="29.25" customHeight="1">
       <c r="A62" s="138"/>
       <c r="B62" s="91" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C62" s="111" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D62" s="128" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E62" s="123" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="F62" s="141"/>
       <c r="G62" s="128" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H62" s="128" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I62" s="128" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J62" s="112"/>
       <c r="K62" s="103"/>
@@ -4265,21 +4268,21 @@
     <row r="63" spans="1:11" ht="29.25" customHeight="1">
       <c r="A63" s="138"/>
       <c r="B63" s="91" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C63" s="111" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D63" s="128" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E63" s="101"/>
       <c r="F63" s="141"/>
       <c r="G63" s="128" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H63" s="147" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="I63" s="147"/>
       <c r="J63" s="112"/>
@@ -4288,24 +4291,24 @@
     <row r="64" spans="1:11" ht="29.25" customHeight="1">
       <c r="A64" s="138"/>
       <c r="B64" s="91" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C64" s="111" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D64" s="123" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E64" s="123" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F64" s="141"/>
       <c r="G64" s="164" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H64" s="164"/>
       <c r="I64" s="123" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="J64" s="112"/>
       <c r="K64" s="103"/>
@@ -4313,20 +4316,20 @@
     <row r="65" spans="1:11" ht="29.25" customHeight="1">
       <c r="A65" s="138"/>
       <c r="B65" s="91" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C65" s="111" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D65" s="123" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E65" s="128" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F65" s="141"/>
       <c r="G65" s="164" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H65" s="164"/>
       <c r="I65" s="94"/>
@@ -4336,23 +4339,23 @@
     <row r="66" spans="1:11" ht="29.25" customHeight="1">
       <c r="A66" s="138"/>
       <c r="B66" s="91" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C66" s="111" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D66" s="123" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E66" s="123" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F66" s="141"/>
       <c r="G66" s="123" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="H66" s="110" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I66" s="114"/>
       <c r="J66" s="112"/>
@@ -4361,23 +4364,23 @@
     <row r="67" spans="1:11" ht="29.25" customHeight="1">
       <c r="A67" s="138"/>
       <c r="B67" s="91" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C67" s="111" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D67" s="123" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E67" s="105" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F67" s="141"/>
       <c r="G67" s="105" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="H67" s="122" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="I67" s="114"/>
       <c r="J67" s="112"/>
@@ -4386,21 +4389,21 @@
     <row r="68" spans="1:11" ht="29.25" customHeight="1">
       <c r="A68" s="138"/>
       <c r="B68" s="91" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C68" s="111" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D68" s="128" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E68" s="94"/>
       <c r="F68" s="142"/>
       <c r="G68" s="130" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H68" s="174" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="I68" s="181"/>
       <c r="J68" s="112"/>
@@ -4409,17 +4412,17 @@
     <row r="69" spans="1:11" ht="29.25" customHeight="1">
       <c r="A69" s="138"/>
       <c r="B69" s="91" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C69" s="111" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D69" s="93" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E69" s="94"/>
       <c r="F69" s="123" t="s">
-        <v>201</v>
+        <v>509</v>
       </c>
       <c r="G69" s="97"/>
       <c r="H69" s="143"/>
@@ -4430,16 +4433,16 @@
     <row r="70" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
       <c r="A70" s="138"/>
       <c r="B70" s="91" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D70" s="144" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E70" s="144"/>
       <c r="F70" s="113"/>
       <c r="G70" s="97"/>
       <c r="H70" s="143" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="I70" s="143"/>
       <c r="J70" s="112"/>
@@ -4448,17 +4451,17 @@
     <row r="71" spans="1:11" ht="29.25" customHeight="1">
       <c r="A71" s="138"/>
       <c r="B71" s="91" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C71" s="111"/>
       <c r="D71" s="182" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E71" s="163"/>
       <c r="F71" s="96"/>
       <c r="G71" s="115"/>
       <c r="H71" s="143" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="I71" s="143"/>
       <c r="J71" s="112"/>
@@ -4469,13 +4472,13 @@
       <c r="B72" s="100"/>
       <c r="C72" s="111"/>
       <c r="D72" s="143" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E72" s="143"/>
       <c r="F72" s="116"/>
       <c r="G72" s="94"/>
       <c r="H72" s="143" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I72" s="143"/>
       <c r="J72" s="112"/>
@@ -4486,7 +4489,7 @@
       <c r="B73" s="100"/>
       <c r="C73" s="111"/>
       <c r="D73" s="155" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E73" s="156"/>
       <c r="F73" s="116"/>
@@ -4549,10 +4552,10 @@
       <c r="E77" s="56"/>
       <c r="F77" s="85"/>
       <c r="G77" s="23" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J77" s="167" t="s">
         <v>28</v>
@@ -4565,81 +4568,81 @@
         <v>41</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D78" s="88" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E78" s="80" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F78" s="77"/>
       <c r="G78" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H78" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I78" s="35" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="J78" s="150" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K78" s="151"/>
     </row>
     <row r="79" spans="1:11" ht="28.5" customHeight="1" thickBot="1">
       <c r="A79" s="180"/>
       <c r="B79" s="23" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D79" s="91" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E79" s="91" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F79" s="117"/>
       <c r="G79" s="123" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H79" s="122" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="I79" s="130" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="J79" s="148" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="K79" s="149"/>
     </row>
     <row r="80" spans="1:11" ht="29.25" customHeight="1">
       <c r="A80" s="180"/>
       <c r="B80" s="23" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D80" s="91" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E80" s="91" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F80" s="117"/>
       <c r="G80" s="91" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H80" s="91" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I80" s="130" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="J80" s="16"/>
       <c r="K80" s="15"/>
@@ -4647,22 +4650,22 @@
     <row r="81" spans="1:11" ht="29.25" customHeight="1">
       <c r="A81" s="180"/>
       <c r="B81" s="23" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D81" s="118" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E81" s="92" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F81" s="117" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G81" s="91" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H81" s="143"/>
       <c r="I81" s="143"/>
@@ -4672,23 +4675,23 @@
     <row r="82" spans="1:11" ht="29.25" customHeight="1">
       <c r="A82" s="180"/>
       <c r="B82" s="23" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C82" s="130" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D82" s="91" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E82" s="91" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F82" s="117"/>
       <c r="G82" s="92" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H82" s="144" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="I82" s="144"/>
       <c r="J82" s="16"/>
@@ -4697,20 +4700,20 @@
     <row r="83" spans="1:11" s="17" customFormat="1" ht="29.25" customHeight="1">
       <c r="A83" s="180"/>
       <c r="B83" s="23" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D83" s="91" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E83" s="95" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F83" s="117"/>
       <c r="G83" s="93" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H83" s="143"/>
       <c r="I83" s="143"/>
@@ -4720,20 +4723,20 @@
     <row r="84" spans="1:11" ht="18" customHeight="1">
       <c r="A84" s="180"/>
       <c r="B84" s="23" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D84" s="105" t="s">
+        <v>465</v>
+      </c>
+      <c r="E84" s="105" t="s">
         <v>469</v>
-      </c>
-      <c r="E84" s="105" t="s">
-        <v>473</v>
       </c>
       <c r="F84" s="117"/>
       <c r="G84" s="93" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="H84" s="96"/>
       <c r="I84" s="91"/>
@@ -4743,18 +4746,18 @@
     <row r="85" spans="1:11" ht="26.25" customHeight="1">
       <c r="A85" s="180"/>
       <c r="B85" s="23" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D85" s="147" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E85" s="147"/>
       <c r="F85" s="117"/>
       <c r="G85" s="119" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H85" s="91"/>
       <c r="I85" s="91"/>
@@ -4764,20 +4767,20 @@
     <row r="86" spans="1:11" ht="27.75" customHeight="1">
       <c r="A86" s="180"/>
       <c r="B86" s="23" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D86" s="93" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E86" s="105" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F86" s="117"/>
       <c r="G86" s="143" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="H86" s="143"/>
       <c r="I86" s="91"/>
@@ -4787,17 +4790,17 @@
     <row r="87" spans="1:11" ht="27.75" customHeight="1">
       <c r="A87" s="180"/>
       <c r="B87" s="23" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D87" s="93" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F87" s="117"/>
       <c r="G87" s="147" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H87" s="147"/>
       <c r="I87" s="91"/>
@@ -4807,18 +4810,18 @@
     <row r="88" spans="1:11" ht="27.75" customHeight="1">
       <c r="A88" s="180"/>
       <c r="B88" s="121" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D88" s="94"/>
       <c r="E88" s="93" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F88" s="117"/>
       <c r="G88" s="164" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H88" s="164"/>
       <c r="I88" s="91"/>
@@ -4829,15 +4832,15 @@
       <c r="A89" s="180"/>
       <c r="B89" s="59"/>
       <c r="C89" s="23" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D89" s="144" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E89" s="143"/>
       <c r="F89" s="117"/>
       <c r="G89" s="164" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H89" s="164"/>
       <c r="I89" s="91"/>
@@ -4848,10 +4851,10 @@
       <c r="A90" s="180"/>
       <c r="B90" s="81"/>
       <c r="C90" s="79" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D90" s="143" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E90" s="143"/>
       <c r="F90" s="117"/>
@@ -4865,10 +4868,10 @@
       <c r="A91" s="180"/>
       <c r="B91" s="81"/>
       <c r="C91" s="79" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D91" s="178" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E91" s="178"/>
       <c r="F91" s="77"/>
@@ -4883,7 +4886,7 @@
       <c r="B92" s="60"/>
       <c r="C92" s="59"/>
       <c r="D92" s="169" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E92" s="169"/>
       <c r="F92" s="77"/>
@@ -4898,7 +4901,7 @@
       <c r="B93" s="86"/>
       <c r="C93" s="59"/>
       <c r="D93" s="169" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E93" s="169"/>
       <c r="F93" s="77"/>
@@ -4947,7 +4950,7 @@
       <c r="D96" s="56"/>
       <c r="E96" s="56"/>
       <c r="F96" s="170" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G96" s="171"/>
       <c r="H96" s="19"/>
@@ -4958,16 +4961,16 @@
     <row r="97" spans="1:11" ht="30" customHeight="1">
       <c r="A97" s="180"/>
       <c r="B97" s="91" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C97" s="91" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D97" s="92" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E97" s="93" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F97" s="100"/>
       <c r="G97" s="120"/>
@@ -4979,13 +4982,13 @@
     <row r="98" spans="1:11" ht="26.25" customHeight="1">
       <c r="A98" s="180"/>
       <c r="B98" s="91" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C98" s="91" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D98" s="92" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E98" s="91"/>
       <c r="F98" s="100"/>
@@ -4998,13 +5001,13 @@
     <row r="99" spans="1:11" ht="30" customHeight="1">
       <c r="A99" s="180"/>
       <c r="B99" s="91" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C99" s="91" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D99" s="92" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E99" s="91"/>
       <c r="F99" s="100"/>
@@ -5017,10 +5020,10 @@
     <row r="100" spans="1:11" ht="30" customHeight="1">
       <c r="A100" s="180"/>
       <c r="B100" s="91" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C100" s="91" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D100" s="94"/>
       <c r="E100" s="96"/>
@@ -5034,13 +5037,13 @@
     <row r="101" spans="1:11" ht="27.75" customHeight="1">
       <c r="A101" s="180"/>
       <c r="B101" s="91" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C101" s="91" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D101" s="162" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E101" s="162"/>
       <c r="F101" s="100"/>
@@ -5053,13 +5056,13 @@
     <row r="102" spans="1:11" ht="27" customHeight="1">
       <c r="A102" s="180"/>
       <c r="B102" s="91" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C102" s="91" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D102" s="147" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E102" s="147"/>
       <c r="F102" s="104"/>
@@ -5072,13 +5075,13 @@
     <row r="103" spans="1:11" ht="28.5" customHeight="1">
       <c r="A103" s="180"/>
       <c r="B103" s="91" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C103" s="91" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D103" s="143" t="s">
-        <v>401</v>
+        <v>510</v>
       </c>
       <c r="E103" s="143"/>
       <c r="F103" s="104"/>
@@ -5091,7 +5094,7 @@
     <row r="104" spans="1:11" ht="29.25" customHeight="1">
       <c r="A104" s="180"/>
       <c r="B104" s="91" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C104" s="94"/>
       <c r="D104" s="101"/>
@@ -5106,11 +5109,11 @@
     <row r="105" spans="1:11" ht="17.25" customHeight="1">
       <c r="A105" s="180"/>
       <c r="B105" s="91" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C105" s="94"/>
       <c r="D105" s="173" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E105" s="173"/>
       <c r="F105" s="104"/>
@@ -5125,7 +5128,7 @@
       <c r="B106" s="94"/>
       <c r="C106" s="91"/>
       <c r="D106" s="155" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E106" s="156"/>
       <c r="F106" s="104"/>
@@ -5140,7 +5143,7 @@
       <c r="B107" s="91"/>
       <c r="C107" s="91"/>
       <c r="D107" s="155" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E107" s="156"/>
       <c r="F107" s="104"/>
@@ -5166,11 +5169,11 @@
     <row r="109" spans="1:11">
       <c r="A109" s="180"/>
       <c r="B109" s="143" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C109" s="143"/>
       <c r="D109" s="155" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E109" s="156"/>
       <c r="F109" s="104"/>
@@ -5183,7 +5186,7 @@
     <row r="110" spans="1:11">
       <c r="A110" s="180"/>
       <c r="B110" s="143" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C110" s="143"/>
       <c r="D110" s="94"/>
@@ -5198,7 +5201,7 @@
     <row r="111" spans="1:11">
       <c r="A111" s="180"/>
       <c r="B111" s="143" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C111" s="143"/>
       <c r="D111" s="55"/>
@@ -5213,12 +5216,12 @@
     <row r="112" spans="1:11" s="17" customFormat="1">
       <c r="A112" s="180"/>
       <c r="B112" s="143" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C112" s="143"/>
       <c r="D112" s="56"/>
       <c r="E112" s="76" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F112" s="87"/>
       <c r="G112" s="81"/>
@@ -5230,7 +5233,7 @@
     <row r="113" spans="1:11" s="17" customFormat="1">
       <c r="A113" s="180"/>
       <c r="B113" s="144" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C113" s="143"/>
       <c r="D113" s="56"/>
@@ -5245,7 +5248,7 @@
     <row r="114" spans="1:11" s="17" customFormat="1">
       <c r="A114" s="180"/>
       <c r="B114" s="144" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C114" s="144"/>
       <c r="D114" s="56"/>
@@ -5260,7 +5263,7 @@
     <row r="115" spans="1:11" s="17" customFormat="1" ht="15" customHeight="1">
       <c r="A115" s="180"/>
       <c r="B115" s="144" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C115" s="144"/>
       <c r="D115" s="56"/>
@@ -5275,7 +5278,7 @@
     <row r="116" spans="1:11" s="17" customFormat="1">
       <c r="A116" s="180"/>
       <c r="B116" s="173" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C116" s="173"/>
       <c r="D116" s="56"/>
@@ -5315,110 +5318,110 @@
     </row>
     <row r="119" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B119" s="48" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C119" s="48" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E119" s="49" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F119" s="49" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H119" s="49" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I119" s="49" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="120" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B120" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="C120" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="C120" s="55" t="s">
-        <v>93</v>
-      </c>
       <c r="E120" s="50" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F120" s="66" t="s">
         <v>58</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I120" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="121" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B121" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="C121" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="C121" s="55" t="s">
-        <v>95</v>
-      </c>
       <c r="E121" s="133" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F121" s="66" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H121" s="39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I121" s="68" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="122" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B122" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="C122" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="C122" s="55" t="s">
-        <v>97</v>
-      </c>
       <c r="E122" s="50" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F122" s="66" t="s">
         <v>59</v>
       </c>
       <c r="H122" s="39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I122" s="68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="123" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B123" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="C123" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="C123" s="55" t="s">
-        <v>99</v>
-      </c>
       <c r="E123" s="50" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F123" s="66" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H123" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="I123" s="68" t="s">
         <v>76</v>
-      </c>
-      <c r="I123" s="68" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="124" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B124" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C124" s="55" t="s">
         <v>100</v>
-      </c>
-      <c r="C124" s="55" t="s">
-        <v>101</v>
       </c>
       <c r="E124" s="50" t="s">
         <v>60</v>
@@ -5428,295 +5431,295 @@
       </c>
       <c r="H124" s="51"/>
       <c r="I124" s="69" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
       <c r="B125" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="C125" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="C125" s="55" t="s">
-        <v>103</v>
-      </c>
       <c r="E125" s="50" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F125" s="66" t="s">
         <v>62</v>
       </c>
       <c r="H125" s="41" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I125" s="70" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="126" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
       <c r="B126" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="C126" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="C126" s="55" t="s">
-        <v>105</v>
-      </c>
       <c r="E126" s="50" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F126" s="66" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H126" s="41" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I126" s="70" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="127" spans="1:11" s="17" customFormat="1" ht="16.5" thickTop="1" thickBot="1">
       <c r="B127" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C127" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="C127" s="55" t="s">
-        <v>107</v>
-      </c>
       <c r="E127" s="50" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F127" s="66" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="H127" s="52"/>
       <c r="I127" s="71" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B128" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="C128" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="C128" s="55" t="s">
-        <v>109</v>
-      </c>
       <c r="E128" s="50" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F128" s="66" t="s">
         <v>63</v>
       </c>
       <c r="H128" s="53"/>
       <c r="I128" s="68" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="129" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B129" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="C129" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="C129" s="55" t="s">
-        <v>111</v>
-      </c>
       <c r="E129" s="50" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F129" s="66" t="s">
         <v>64</v>
       </c>
       <c r="H129" s="40" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I129" s="68" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="130" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B130" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="C130" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="C130" s="55" t="s">
-        <v>113</v>
-      </c>
       <c r="E130" s="50" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F130" s="66" t="s">
         <v>65</v>
       </c>
       <c r="H130" s="40" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I130" s="68" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="131" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B131" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="C131" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="C131" s="55" t="s">
-        <v>115</v>
-      </c>
       <c r="E131" s="50" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F131" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H131" s="53"/>
       <c r="I131" s="68" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="132" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B132" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="C132" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="C132" s="55" t="s">
-        <v>117</v>
-      </c>
       <c r="E132" s="50" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F132" s="66" t="s">
         <v>67</v>
       </c>
       <c r="H132" s="54" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I132" s="72" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="133" spans="2:9" s="17" customFormat="1" ht="15.75" thickBot="1">
       <c r="B133" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="C133" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="C133" s="55" t="s">
-        <v>119</v>
-      </c>
       <c r="E133" s="50" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F133" s="66" t="s">
         <v>68</v>
       </c>
       <c r="H133" s="54" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="I133" s="72" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C134" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="C134" s="55" t="s">
-        <v>121</v>
-      </c>
       <c r="E134" s="50" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F134" s="66" t="s">
         <v>69</v>
       </c>
       <c r="H134" s="55" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="I134" s="66" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C135" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="C135" s="55" t="s">
-        <v>123</v>
-      </c>
       <c r="E135" s="50" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F135" s="66" t="s">
         <v>70</v>
       </c>
       <c r="H135" s="55" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I135" s="66" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C136" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="C136" s="55" t="s">
-        <v>125</v>
-      </c>
       <c r="E136" s="50" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F136" s="66" t="s">
         <v>71</v>
       </c>
       <c r="H136" s="55" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I136" s="66" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="137" spans="2:9">
       <c r="B137" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="C137" s="55" t="s">
         <v>126</v>
-      </c>
-      <c r="C137" s="55" t="s">
-        <v>127</v>
       </c>
       <c r="E137" s="50" t="s">
         <v>72</v>
       </c>
       <c r="F137" s="66" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H137" s="50" t="s">
         <v>73</v>
       </c>
       <c r="I137" s="56" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="138" spans="2:9">
       <c r="B138" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="C138" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="C138" s="55" t="s">
-        <v>129</v>
-      </c>
       <c r="E138" s="50" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F138" s="66" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H138" s="50" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I138" s="56" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139" spans="2:9">
       <c r="B139" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C139" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="C139" s="58" t="s">
-        <v>131</v>
-      </c>
       <c r="E139" s="55" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F139" s="66" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H139" s="46" t="s">
         <v>52</v>
@@ -5733,10 +5736,10 @@
         <v>43</v>
       </c>
       <c r="E140" s="55" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F140" s="66" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H140" s="45" t="s">
         <v>54</v>
@@ -5753,10 +5756,10 @@
         <v>45</v>
       </c>
       <c r="E141" s="55" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F141" s="66" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H141" s="46" t="s">
         <v>56</v>
@@ -5773,10 +5776,10 @@
         <v>47</v>
       </c>
       <c r="E142" s="55" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F142" s="66" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H142" s="47" t="s">
         <v>29</v>
@@ -5793,10 +5796,10 @@
         <v>49</v>
       </c>
       <c r="E143" s="55" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F143" s="66" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H143" s="47" t="s">
         <v>30</v>
@@ -5813,10 +5816,10 @@
         <v>51</v>
       </c>
       <c r="E144" s="55" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F144" s="66" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H144" s="47" t="s">
         <v>31</v>
@@ -5833,10 +5836,10 @@
         <v>40</v>
       </c>
       <c r="E145" s="55" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F145" s="66" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H145" s="47" t="s">
         <v>32</v>
